--- a/downloads/KETS_Public_Insights_20261014.xlsx
+++ b/downloads/KETS_Public_Insights_20261014.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" r:id="R62309a80878a4b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석조건" sheetId="2" r:id="R019e7a01a821473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통계" sheetId="3" r:id="R2077571ead3e41e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방법론" sheetId="4" r:id="R0c080ecc44194269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="버전" sheetId="5" r:id="Re6627674d4b54644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" r:id="Rb9fa9150c1c04294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석조건" sheetId="2" r:id="R4adc4a8994664e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통계" sheetId="3" r:id="R285928f64f324ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방법론" sheetId="4" r:id="Rf3913bf229b94293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="버전" sheetId="5" r:id="R757bdf1763e94e84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,87 +27,88 @@
     <x:numFmt numFmtId="206" formatCode="&quot;  &quot;+0;&quot;  &quot;-0;&quot;  &quot;0"/>
     <x:numFmt numFmtId="207" formatCode="&quot;  &quot;0.0%"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="26">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:color rgb="FF475569"/>
+      <x:color rgb="FF33363D"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="16"/>
-      <x:color rgb="FF0B1739"/>
+      <x:color rgb="FF003675"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:color rgb="FF64748B"/>
+      <x:color rgb="FF6D7882"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="12"/>
-      <x:color rgb="FF0B1739"/>
+      <x:color rgb="FF003675"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FF003675"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="8"/>
-      <x:color rgb="FF2F62F0"/>
+      <x:color rgb="FFD3E1FB"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="20"/>
-      <x:color rgb="FF0B1739"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:sz val="9"/>
-      <x:color rgb="FF64748B"/>
+      <x:color rgb="FFD3E1FB"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10.5"/>
-      <x:color rgb="FF2F62F0"/>
+      <x:color rgb="FF0B50D0"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="12"/>
-      <x:color rgb="FF2F62F0"/>
+      <x:color rgb="FF0B50D0"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:sz val="8.5"/>
-      <x:color rgb="FF475569"/>
+      <x:color rgb="FF33363D"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
+      <x:b/>
       <x:sz val="9"/>
-      <x:color rgb="FFD2DCFA"/>
+      <x:color rgb="FF464C53"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="24"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FF1E2124"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:sz val="8"/>
-      <x:color rgb="FFAFC0EC"/>
+      <x:color rgb="FF6D7882"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
@@ -119,56 +120,63 @@
     <x:font>
       <x:b/>
       <x:sz val="14"/>
-      <x:color rgb="FF2F62F0"/>
+      <x:color rgb="FF246BEB"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10.5"/>
-      <x:color rgb="FF0B1739"/>
+      <x:color rgb="FF003675"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:sz val="9"/>
-      <x:color rgb="FF475569"/>
+      <x:color rgb="FF33363D"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="8"/>
+      <x:color rgb="FF6D7882"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="13"/>
-      <x:color rgb="FF0B1739"/>
+      <x:color rgb="FF003675"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:sz val="8.5"/>
-      <x:color rgb="FF64748B"/>
-      <x:name val="Malgun Gothic"/>
-    </x:font>
-    <x:font>
-      <x:sz val="8"/>
-      <x:color rgb="FF64748B"/>
+      <x:color rgb="FF6D7882"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="20"/>
-      <x:color rgb="FF2F62F0"/>
+      <x:color rgb="FF1E2124"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FF246BEB"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF64748B"/>
+      <x:color rgb="FF6D7882"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="9"/>
-      <x:color rgb="FF2F62F0"/>
+      <x:color rgb="FF246BEB"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -177,7 +185,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2F62F0"/>
+        <x:fgColor rgb="FF003675"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -187,22 +195,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0B1739"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF1F4F9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF6F8FC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF3F6FF"/>
+        <x:fgColor rgb="FFF4F5F6"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -210,76 +203,20 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFECF2FE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F8F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="25">
+  <x:borders count="36">
     <x:border>
       <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thick">
-        <x:color rgb="FF2F62F0"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFDFE7FF"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thick">
-        <x:color rgb="FF2F62F0"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF2A3A66"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thick">
-        <x:color rgb="FF2F62F0"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF2A3A66"/>
-      </x:left>
       <x:right/>
       <x:top/>
       <x:bottom/>
@@ -289,18 +226,57 @@
       <x:left/>
       <x:right/>
       <x:top style="medium">
-        <x:color rgb="FF0B1739"/>
+        <x:color rgb="FF003675"/>
       </x:top>
-      <x:bottom/>
+      <x:bottom style="thin">
+        <x:color rgb="FFCDD1D5"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF246BEB"/>
+      </x:left>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:bottom>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:left>
       <x:right/>
       <x:top style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:top>
       <x:bottom/>
       <x:diagonal/>
@@ -309,7 +285,7 @@
       <x:left/>
       <x:right/>
       <x:top style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:top>
       <x:bottom/>
       <x:diagonal/>
@@ -317,17 +293,17 @@
     <x:border>
       <x:left/>
       <x:right style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:top>
       <x:bottom/>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:left>
       <x:right/>
       <x:top/>
@@ -337,7 +313,7 @@
     <x:border>
       <x:left/>
       <x:right style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:right>
       <x:top/>
       <x:bottom/>
@@ -345,12 +321,12 @@
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:left>
       <x:right/>
       <x:top/>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
@@ -359,31 +335,173 @@
       <x:right/>
       <x:top/>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left/>
       <x:right style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:right>
       <x:top/>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF246BEB"/>
+      </x:left>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFE6E8EA"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF246BEB"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF246BEB"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6E8EA"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFD3E1FB"/>
       </x:left>
       <x:right/>
       <x:top style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFD3E1FB"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:right>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:right>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFD3E1FB"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6E8EA"/>
+      </x:left>
+      <x:right/>
+      <x:top style="medium">
+        <x:color rgb="FF003675"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="medium">
+        <x:color rgb="FF003675"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFE6E8EA"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF003675"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6E8EA"/>
+      </x:left>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFE6E8EA"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
@@ -391,33 +509,33 @@
       <x:left/>
       <x:right/>
       <x:top style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left/>
       <x:right style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E8F0"/>
+        <x:color rgb="FFE6E8EA"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:left>
       <x:right/>
       <x:top style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:top>
       <x:bottom/>
       <x:diagonal/>
@@ -426,7 +544,7 @@
       <x:left/>
       <x:right/>
       <x:top style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:top>
       <x:bottom/>
       <x:diagonal/>
@@ -434,22 +552,22 @@
     <x:border>
       <x:left/>
       <x:right style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:right>
       <x:top style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:top>
       <x:bottom/>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:left>
       <x:right/>
       <x:top/>
       <x:bottom style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
@@ -458,18 +576,18 @@
       <x:right/>
       <x:top/>
       <x:bottom style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
     <x:border>
       <x:left/>
       <x:right style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:right>
       <x:top/>
       <x:bottom style="dashed">
-        <x:color rgb="FF94A3B8"/>
+        <x:color rgb="FFB1B8BE"/>
       </x:bottom>
       <x:diagonal/>
     </x:border>
@@ -477,7 +595,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="134">
+  <x:cellXfs count="170">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -511,22 +629,22 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -537,333 +655,441 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="13" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="16" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="22" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="204" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="23" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="22" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="22" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="16" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="15" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="15" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="7" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="22" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="207" fontId="7" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="207" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -890,7 +1116,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2F62F0"/>
+              <a:srgbClr val="246BEB"/>
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -920,7 +1146,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="7B9BF7"/>
+              <a:srgbClr val="003675"/>
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1091,7 +1317,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2F62F0"/>
+              <a:srgbClr val="246BEB"/>
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1254,7 +1480,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfb63b042f6a24510"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c95fa8333394f66"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1284,7 +1510,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad1240c4365a44ad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28f667fe5e5b40de"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1531,7 +1757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF0B1739"/>
+    <x:tabColor rgb="FF003675"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1588,7 +1814,7 @@
       <x:c r="X1" s="3"/>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="28"/>
+      <x:c r="A2" s="3"/>
       <x:c r="B2" s="29" t="str">
         <x:v>PUBLIC DATA  ·  방법론 인사이트</x:v>
       </x:c>
@@ -1613,10 +1839,10 @@
       <x:c r="U2" s="29"/>
       <x:c r="V2" s="29"/>
       <x:c r="W2" s="29"/>
-      <x:c r="X2" s="28"/>
+      <x:c r="X2" s="3"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="28"/>
+      <x:c r="A3" s="3"/>
       <x:c r="B3" s="30" t="str">
         <x:v>공개 방법론의 흐름과 변화</x:v>
       </x:c>
@@ -1641,10 +1867,10 @@
       <x:c r="U3" s="30"/>
       <x:c r="V3" s="30"/>
       <x:c r="W3" s="30"/>
-      <x:c r="X3" s="28"/>
+      <x:c r="X3" s="3"/>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="28"/>
+      <x:c r="A4" s="3"/>
       <x:c r="B4" s="31" t="str">
         <x:v>ORS 공개 실자료  ·  2026-10-14 확인  ·  선택한 33개 코드의 확인분  ·  단위는 각 수치 옆에 표시</x:v>
       </x:c>
@@ -1669,7 +1895,7 @@
       <x:c r="U4" s="31"/>
       <x:c r="V4" s="31"/>
       <x:c r="W4" s="31"/>
-      <x:c r="X4" s="28"/>
+      <x:c r="X4" s="3"/>
     </x:row>
     <x:row r="5" ht="6" customHeight="1">
       <x:c r="A5" s="28"/>
@@ -1783,151 +2009,151 @@
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="28"/>
-      <x:c r="B9" s="41" t="str">
+      <x:c r="B9" s="62" t="str">
         <x:v>  공개 확인 방법론</x:v>
       </x:c>
-      <x:c r="C9" s="41"/>
-      <x:c r="D9" s="41"/>
-      <x:c r="E9" s="41"/>
-      <x:c r="F9" s="47" t="str">
+      <x:c r="C9" s="49"/>
+      <x:c r="D9" s="49"/>
+      <x:c r="E9" s="50"/>
+      <x:c r="F9" s="62" t="str">
         <x:v>  공개 버전 이력</x:v>
       </x:c>
-      <x:c r="G9" s="41"/>
-      <x:c r="H9" s="41"/>
-      <x:c r="I9" s="41"/>
-      <x:c r="J9" s="47" t="str">
+      <x:c r="G9" s="49"/>
+      <x:c r="H9" s="49"/>
+      <x:c r="I9" s="50"/>
+      <x:c r="J9" s="62" t="str">
         <x:v>  개정 경험 방법론</x:v>
       </x:c>
-      <x:c r="K9" s="41"/>
-      <x:c r="L9" s="41"/>
-      <x:c r="M9" s="41"/>
-      <x:c r="N9" s="47" t="str">
+      <x:c r="K9" s="49"/>
+      <x:c r="L9" s="49"/>
+      <x:c r="M9" s="50"/>
+      <x:c r="N9" s="62" t="str">
         <x:f>"  "&amp;('분석조건'!B6&amp;" 최초 버전")</x:f>
         <x:v>  2026 최초 버전</x:v>
       </x:c>
-      <x:c r="O9" s="41"/>
-      <x:c r="P9" s="41"/>
-      <x:c r="Q9" s="41"/>
-      <x:c r="R9" s="47" t="str">
+      <x:c r="O9" s="49"/>
+      <x:c r="P9" s="49"/>
+      <x:c r="Q9" s="50"/>
+      <x:c r="R9" s="62" t="str">
         <x:f>"  "&amp;('분석조건'!B6&amp;" 개정 버전")</x:f>
         <x:v>  2026 개정 버전</x:v>
       </x:c>
-      <x:c r="S9" s="41"/>
-      <x:c r="T9" s="41"/>
-      <x:c r="U9" s="47" t="str">
+      <x:c r="S9" s="49"/>
+      <x:c r="T9" s="50"/>
+      <x:c r="U9" s="62" t="str">
         <x:f>"  "&amp;("최근 "&amp;'분석조건'!B11&amp;"일 변경")</x:f>
         <x:v>  최근 365일 변경</x:v>
       </x:c>
-      <x:c r="V9" s="41"/>
-      <x:c r="W9" s="41"/>
+      <x:c r="V9" s="49"/>
+      <x:c r="W9" s="50"/>
       <x:c r="X9" s="28"/>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="28"/>
-      <x:c r="B10" s="45" t="n">
+      <x:c r="B10" s="63" t="n">
         <x:f>'통계'!B7</x:f>
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C10" s="46"/>
-      <x:c r="D10" s="46"/>
-      <x:c r="E10" s="46"/>
-      <x:c r="F10" s="48" t="n">
+      <x:c r="C10" s="59"/>
+      <x:c r="D10" s="59"/>
+      <x:c r="E10" s="60"/>
+      <x:c r="F10" s="63" t="n">
         <x:f>'통계'!B8</x:f>
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G10" s="46"/>
-      <x:c r="H10" s="46"/>
-      <x:c r="I10" s="46"/>
-      <x:c r="J10" s="48" t="n">
+      <x:c r="G10" s="59"/>
+      <x:c r="H10" s="59"/>
+      <x:c r="I10" s="60"/>
+      <x:c r="J10" s="63" t="n">
         <x:f>'통계'!B9</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K10" s="46"/>
-      <x:c r="L10" s="46"/>
-      <x:c r="M10" s="46"/>
-      <x:c r="N10" s="48" t="n">
+      <x:c r="K10" s="59"/>
+      <x:c r="L10" s="59"/>
+      <x:c r="M10" s="60"/>
+      <x:c r="N10" s="63" t="n">
         <x:f>'통계'!B10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O10" s="46"/>
-      <x:c r="P10" s="46"/>
-      <x:c r="Q10" s="46"/>
-      <x:c r="R10" s="48" t="n">
+      <x:c r="O10" s="59"/>
+      <x:c r="P10" s="59"/>
+      <x:c r="Q10" s="60"/>
+      <x:c r="R10" s="63" t="n">
         <x:f>'통계'!B11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="S10" s="46"/>
-      <x:c r="T10" s="46"/>
-      <x:c r="U10" s="48" t="n">
+      <x:c r="S10" s="59"/>
+      <x:c r="T10" s="60"/>
+      <x:c r="U10" s="63" t="n">
         <x:f>'통계'!B12</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="V10" s="46"/>
-      <x:c r="W10" s="46"/>
+      <x:c r="V10" s="59"/>
+      <x:c r="W10" s="60"/>
       <x:c r="X10" s="28"/>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="28"/>
-      <x:c r="B11" s="46"/>
-      <x:c r="C11" s="46"/>
-      <x:c r="D11" s="46"/>
-      <x:c r="E11" s="46"/>
-      <x:c r="F11" s="49"/>
-      <x:c r="G11" s="46"/>
-      <x:c r="H11" s="46"/>
-      <x:c r="I11" s="46"/>
-      <x:c r="J11" s="49"/>
-      <x:c r="K11" s="46"/>
-      <x:c r="L11" s="46"/>
-      <x:c r="M11" s="46"/>
-      <x:c r="N11" s="49"/>
-      <x:c r="O11" s="46"/>
-      <x:c r="P11" s="46"/>
-      <x:c r="Q11" s="46"/>
-      <x:c r="R11" s="49"/>
-      <x:c r="S11" s="46"/>
-      <x:c r="T11" s="46"/>
-      <x:c r="U11" s="49"/>
-      <x:c r="V11" s="46"/>
-      <x:c r="W11" s="46"/>
+      <x:c r="B11" s="64"/>
+      <x:c r="C11" s="59"/>
+      <x:c r="D11" s="59"/>
+      <x:c r="E11" s="60"/>
+      <x:c r="F11" s="64"/>
+      <x:c r="G11" s="59"/>
+      <x:c r="H11" s="59"/>
+      <x:c r="I11" s="60"/>
+      <x:c r="J11" s="64"/>
+      <x:c r="K11" s="59"/>
+      <x:c r="L11" s="59"/>
+      <x:c r="M11" s="60"/>
+      <x:c r="N11" s="64"/>
+      <x:c r="O11" s="59"/>
+      <x:c r="P11" s="59"/>
+      <x:c r="Q11" s="60"/>
+      <x:c r="R11" s="64"/>
+      <x:c r="S11" s="59"/>
+      <x:c r="T11" s="60"/>
+      <x:c r="U11" s="64"/>
+      <x:c r="V11" s="59"/>
+      <x:c r="W11" s="60"/>
       <x:c r="X11" s="28"/>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="28"/>
-      <x:c r="B12" s="44" t="str">
+      <x:c r="B12" s="65" t="str">
         <x:v>  방법론 · 선택 코드 확인분</x:v>
       </x:c>
-      <x:c r="C12" s="44"/>
-      <x:c r="D12" s="44"/>
-      <x:c r="E12" s="44"/>
-      <x:c r="F12" s="50" t="str">
+      <x:c r="C12" s="56"/>
+      <x:c r="D12" s="56"/>
+      <x:c r="E12" s="57"/>
+      <x:c r="F12" s="65" t="str">
         <x:v>  버전 · 최초·개정 버전 분리</x:v>
       </x:c>
-      <x:c r="G12" s="44"/>
-      <x:c r="H12" s="44"/>
-      <x:c r="I12" s="44"/>
-      <x:c r="J12" s="50" t="str">
+      <x:c r="G12" s="56"/>
+      <x:c r="H12" s="56"/>
+      <x:c r="I12" s="57"/>
+      <x:c r="J12" s="65" t="str">
         <x:v>  방법론 · 개정 이력 1회 이상</x:v>
       </x:c>
-      <x:c r="K12" s="44"/>
-      <x:c r="L12" s="44"/>
-      <x:c r="M12" s="44"/>
-      <x:c r="N12" s="50" t="str">
+      <x:c r="K12" s="56"/>
+      <x:c r="L12" s="56"/>
+      <x:c r="M12" s="57"/>
+      <x:c r="N12" s="65" t="str">
         <x:v>  버전 · 유효시작일 기준</x:v>
       </x:c>
-      <x:c r="O12" s="44"/>
-      <x:c r="P12" s="44"/>
-      <x:c r="Q12" s="44"/>
-      <x:c r="R12" s="50" t="str">
+      <x:c r="O12" s="56"/>
+      <x:c r="P12" s="56"/>
+      <x:c r="Q12" s="57"/>
+      <x:c r="R12" s="65" t="str">
         <x:v>  버전 · 유효시작일 기준</x:v>
       </x:c>
-      <x:c r="S12" s="44"/>
-      <x:c r="T12" s="44"/>
-      <x:c r="U12" s="50" t="str">
+      <x:c r="S12" s="56"/>
+      <x:c r="T12" s="57"/>
+      <x:c r="U12" s="65" t="str">
         <x:v>  버전 · 유효시작일</x:v>
       </x:c>
-      <x:c r="V12" s="44"/>
-      <x:c r="W12" s="44"/>
+      <x:c r="V12" s="56"/>
+      <x:c r="W12" s="57"/>
       <x:c r="X12" s="28"/>
     </x:row>
     <x:row r="13" ht="12" customHeight="1">
@@ -1958,131 +2184,131 @@
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="28"/>
-      <x:c r="B14" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="str">
+      <x:c r="B14" s="69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="70" t="str">
         <x:v>핵심 요약</x:v>
       </x:c>
-      <x:c r="D14" s="29"/>
-      <x:c r="E14" s="29"/>
-      <x:c r="F14" s="29"/>
-      <x:c r="G14" s="29"/>
-      <x:c r="H14" s="29"/>
-      <x:c r="I14" s="29"/>
-      <x:c r="J14" s="29"/>
-      <x:c r="K14" s="29"/>
-      <x:c r="L14" s="29"/>
-      <x:c r="M14" s="29"/>
-      <x:c r="N14" s="29"/>
-      <x:c r="O14" s="29"/>
-      <x:c r="P14" s="29"/>
-      <x:c r="Q14" s="29"/>
-      <x:c r="R14" s="29"/>
-      <x:c r="S14" s="29"/>
-      <x:c r="T14" s="29"/>
-      <x:c r="U14" s="29"/>
-      <x:c r="V14" s="29"/>
-      <x:c r="W14" s="29"/>
+      <x:c r="D14" s="70"/>
+      <x:c r="E14" s="70"/>
+      <x:c r="F14" s="70"/>
+      <x:c r="G14" s="70"/>
+      <x:c r="H14" s="70"/>
+      <x:c r="I14" s="70"/>
+      <x:c r="J14" s="70"/>
+      <x:c r="K14" s="70"/>
+      <x:c r="L14" s="70"/>
+      <x:c r="M14" s="70"/>
+      <x:c r="N14" s="70"/>
+      <x:c r="O14" s="70"/>
+      <x:c r="P14" s="70"/>
+      <x:c r="Q14" s="70"/>
+      <x:c r="R14" s="70"/>
+      <x:c r="S14" s="70"/>
+      <x:c r="T14" s="70"/>
+      <x:c r="U14" s="70"/>
+      <x:c r="V14" s="70"/>
+      <x:c r="W14" s="70"/>
       <x:c r="X14" s="28"/>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="28"/>
-      <x:c r="B15" s="58" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="59" t="str">
+      <x:c r="B15" s="81" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="82" t="str">
         <x:v>구성</x:v>
       </x:c>
-      <x:c r="D15" s="59"/>
-      <x:c r="E15" s="59"/>
-      <x:c r="F15" s="59"/>
-      <x:c r="G15" s="59"/>
-      <x:c r="H15" s="59"/>
+      <x:c r="D15" s="82"/>
+      <x:c r="E15" s="82"/>
+      <x:c r="F15" s="82"/>
+      <x:c r="G15" s="82"/>
+      <x:c r="H15" s="83"/>
       <x:c r="I15" s="28"/>
-      <x:c r="J15" s="58" t="n">
+      <x:c r="J15" s="81" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K15" s="59" t="str">
+      <x:c r="K15" s="82" t="str">
         <x:v>집중도</x:v>
       </x:c>
-      <x:c r="L15" s="59"/>
-      <x:c r="M15" s="59"/>
-      <x:c r="N15" s="59"/>
-      <x:c r="O15" s="59"/>
-      <x:c r="P15" s="59"/>
+      <x:c r="L15" s="82"/>
+      <x:c r="M15" s="82"/>
+      <x:c r="N15" s="82"/>
+      <x:c r="O15" s="82"/>
+      <x:c r="P15" s="83"/>
       <x:c r="Q15" s="28"/>
-      <x:c r="R15" s="58" t="n">
+      <x:c r="R15" s="81" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="S15" s="59" t="str">
+      <x:c r="S15" s="82" t="str">
         <x:v>다음 확인</x:v>
       </x:c>
-      <x:c r="T15" s="59"/>
-      <x:c r="U15" s="59"/>
-      <x:c r="V15" s="59"/>
-      <x:c r="W15" s="59"/>
+      <x:c r="T15" s="82"/>
+      <x:c r="U15" s="82"/>
+      <x:c r="V15" s="82"/>
+      <x:c r="W15" s="83"/>
       <x:c r="X15" s="28"/>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="28"/>
-      <x:c r="B16" s="55"/>
-      <x:c r="C16" s="62" t="str">
+      <x:c r="B16" s="75"/>
+      <x:c r="C16" s="92" t="str">
         <x:f>"방법론 "&amp;'통계'!B7&amp;"개에 버전 "&amp;'통계'!B8&amp;"개가 연결되며, 개정 경험은 "&amp;TEXT('통계'!B14,"0.0%")&amp;"입니다."</x:f>
         <x:v>방법론 33개에 버전 40개가 연결되며, 개정 경험은 18.2%입니다.</x:v>
       </x:c>
-      <x:c r="D16" s="62"/>
-      <x:c r="E16" s="62"/>
-      <x:c r="F16" s="62"/>
-      <x:c r="G16" s="62"/>
-      <x:c r="H16" s="62"/>
+      <x:c r="D16" s="92"/>
+      <x:c r="E16" s="92"/>
+      <x:c r="F16" s="92"/>
+      <x:c r="G16" s="92"/>
+      <x:c r="H16" s="93"/>
       <x:c r="I16" s="28"/>
-      <x:c r="J16" s="55"/>
-      <x:c r="K16" s="62" t="str">
+      <x:c r="J16" s="75"/>
+      <x:c r="K16" s="92" t="str">
         <x:f>"상위 3개 분야가 "&amp;TEXT('통계'!B20,"0.0%")&amp;"를 차지합니다. 선택한 포트폴리오의 구성으로 해석합니다."</x:f>
         <x:v>상위 3개 분야가 78.8%를 차지합니다. 선택한 포트폴리오의 구성으로 해석합니다.</x:v>
       </x:c>
-      <x:c r="L16" s="62"/>
-      <x:c r="M16" s="62"/>
-      <x:c r="N16" s="62"/>
-      <x:c r="O16" s="62"/>
-      <x:c r="P16" s="62"/>
+      <x:c r="L16" s="92"/>
+      <x:c r="M16" s="92"/>
+      <x:c r="N16" s="92"/>
+      <x:c r="O16" s="92"/>
+      <x:c r="P16" s="93"/>
       <x:c r="Q16" s="28"/>
-      <x:c r="R16" s="55"/>
-      <x:c r="S16" s="62" t="str">
+      <x:c r="R16" s="75"/>
+      <x:c r="S16" s="92" t="str">
         <x:f>"최근 "&amp;'분석조건'!B11&amp;"일 변경 "&amp;'통계'!B12&amp;"버전의 적용 문서를 대조합니다. 진행 중 신청·보완기한은 공개자료 미확보입니다."</x:f>
         <x:v>최근 365일 변경 4버전의 적용 문서를 대조합니다. 진행 중 신청·보완기한은 공개자료 미확보입니다.</x:v>
       </x:c>
-      <x:c r="T16" s="62"/>
-      <x:c r="U16" s="62"/>
-      <x:c r="V16" s="62"/>
-      <x:c r="W16" s="62"/>
+      <x:c r="T16" s="92"/>
+      <x:c r="U16" s="92"/>
+      <x:c r="V16" s="92"/>
+      <x:c r="W16" s="93"/>
       <x:c r="X16" s="28"/>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" s="28"/>
-      <x:c r="B17" s="55"/>
-      <x:c r="C17" s="62"/>
-      <x:c r="D17" s="62"/>
-      <x:c r="E17" s="62"/>
-      <x:c r="F17" s="62"/>
-      <x:c r="G17" s="62"/>
-      <x:c r="H17" s="62"/>
+      <x:c r="B17" s="77"/>
+      <x:c r="C17" s="94"/>
+      <x:c r="D17" s="94"/>
+      <x:c r="E17" s="94"/>
+      <x:c r="F17" s="94"/>
+      <x:c r="G17" s="94"/>
+      <x:c r="H17" s="95"/>
       <x:c r="I17" s="28"/>
-      <x:c r="J17" s="55"/>
-      <x:c r="K17" s="62"/>
-      <x:c r="L17" s="62"/>
-      <x:c r="M17" s="62"/>
-      <x:c r="N17" s="62"/>
-      <x:c r="O17" s="62"/>
-      <x:c r="P17" s="62"/>
+      <x:c r="J17" s="77"/>
+      <x:c r="K17" s="94"/>
+      <x:c r="L17" s="94"/>
+      <x:c r="M17" s="94"/>
+      <x:c r="N17" s="94"/>
+      <x:c r="O17" s="94"/>
+      <x:c r="P17" s="95"/>
       <x:c r="Q17" s="28"/>
-      <x:c r="R17" s="55"/>
-      <x:c r="S17" s="62"/>
-      <x:c r="T17" s="62"/>
-      <x:c r="U17" s="62"/>
-      <x:c r="V17" s="62"/>
-      <x:c r="W17" s="62"/>
+      <x:c r="R17" s="77"/>
+      <x:c r="S17" s="94"/>
+      <x:c r="T17" s="94"/>
+      <x:c r="U17" s="94"/>
+      <x:c r="V17" s="94"/>
+      <x:c r="W17" s="95"/>
       <x:c r="X17" s="28"/>
     </x:row>
     <x:row r="18" ht="14" customHeight="1">
@@ -2113,66 +2339,66 @@
     </x:row>
     <x:row r="19" ht="16" customHeight="1">
       <x:c r="A19" s="28"/>
-      <x:c r="B19" s="75" t="str">
+      <x:c r="B19" s="107" t="str">
         <x:v>01</x:v>
       </x:c>
-      <x:c r="C19" s="76" t="str">
+      <x:c r="C19" s="108" t="str">
         <x:v>TIME SERIES</x:v>
       </x:c>
-      <x:c r="D19" s="76"/>
-      <x:c r="E19" s="76"/>
-      <x:c r="F19" s="76"/>
-      <x:c r="G19" s="76"/>
-      <x:c r="H19" s="76"/>
-      <x:c r="I19" s="76"/>
-      <x:c r="J19" s="76"/>
-      <x:c r="K19" s="76"/>
-      <x:c r="L19" s="77"/>
+      <x:c r="D19" s="108"/>
+      <x:c r="E19" s="108"/>
+      <x:c r="F19" s="108"/>
+      <x:c r="G19" s="108"/>
+      <x:c r="H19" s="108"/>
+      <x:c r="I19" s="108"/>
+      <x:c r="J19" s="108"/>
+      <x:c r="K19" s="108"/>
+      <x:c r="L19" s="109"/>
       <x:c r="M19" s="28"/>
-      <x:c r="N19" s="75" t="str">
+      <x:c r="N19" s="107" t="str">
         <x:v>02</x:v>
       </x:c>
-      <x:c r="O19" s="76" t="str">
+      <x:c r="O19" s="108" t="str">
         <x:v>CHANGE WATCH</x:v>
       </x:c>
-      <x:c r="P19" s="76"/>
-      <x:c r="Q19" s="76"/>
-      <x:c r="R19" s="76"/>
-      <x:c r="S19" s="76"/>
-      <x:c r="T19" s="76"/>
-      <x:c r="U19" s="76"/>
-      <x:c r="V19" s="76"/>
-      <x:c r="W19" s="77"/>
+      <x:c r="P19" s="108"/>
+      <x:c r="Q19" s="108"/>
+      <x:c r="R19" s="108"/>
+      <x:c r="S19" s="108"/>
+      <x:c r="T19" s="108"/>
+      <x:c r="U19" s="108"/>
+      <x:c r="V19" s="108"/>
+      <x:c r="W19" s="109"/>
       <x:c r="X19" s="28"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="28"/>
-      <x:c r="B20" s="78" t="str">
+      <x:c r="B20" s="110" t="str">
         <x:v>  최초·개정 버전의 흐름</x:v>
       </x:c>
-      <x:c r="C20" s="79"/>
-      <x:c r="D20" s="79"/>
-      <x:c r="E20" s="79"/>
-      <x:c r="F20" s="79"/>
-      <x:c r="G20" s="79"/>
-      <x:c r="H20" s="79"/>
-      <x:c r="I20" s="79"/>
-      <x:c r="J20" s="79"/>
-      <x:c r="K20" s="79"/>
-      <x:c r="L20" s="80"/>
+      <x:c r="C20" s="111"/>
+      <x:c r="D20" s="111"/>
+      <x:c r="E20" s="111"/>
+      <x:c r="F20" s="111"/>
+      <x:c r="G20" s="111"/>
+      <x:c r="H20" s="111"/>
+      <x:c r="I20" s="111"/>
+      <x:c r="J20" s="111"/>
+      <x:c r="K20" s="111"/>
+      <x:c r="L20" s="112"/>
       <x:c r="M20" s="28"/>
-      <x:c r="N20" s="78" t="str">
+      <x:c r="N20" s="110" t="str">
         <x:v>  최신 버전 경과일 분포</x:v>
       </x:c>
-      <x:c r="O20" s="79"/>
-      <x:c r="P20" s="79"/>
-      <x:c r="Q20" s="79"/>
-      <x:c r="R20" s="79"/>
-      <x:c r="S20" s="79"/>
-      <x:c r="T20" s="79"/>
-      <x:c r="U20" s="79"/>
-      <x:c r="V20" s="79"/>
-      <x:c r="W20" s="80"/>
+      <x:c r="O20" s="111"/>
+      <x:c r="P20" s="111"/>
+      <x:c r="Q20" s="111"/>
+      <x:c r="R20" s="111"/>
+      <x:c r="S20" s="111"/>
+      <x:c r="T20" s="111"/>
+      <x:c r="U20" s="111"/>
+      <x:c r="V20" s="111"/>
+      <x:c r="W20" s="112"/>
       <x:c r="X20" s="28"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
@@ -2209,396 +2435,396 @@
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" s="28"/>
-      <x:c r="B22" s="67"/>
-      <x:c r="C22" s="63"/>
-      <x:c r="D22" s="63"/>
-      <x:c r="E22" s="63"/>
-      <x:c r="F22" s="63"/>
-      <x:c r="G22" s="63"/>
-      <x:c r="H22" s="63"/>
-      <x:c r="I22" s="63"/>
-      <x:c r="J22" s="63"/>
-      <x:c r="K22" s="63"/>
-      <x:c r="L22" s="68"/>
+      <x:c r="B22" s="43"/>
+      <x:c r="C22" s="28"/>
+      <x:c r="D22" s="28"/>
+      <x:c r="E22" s="28"/>
+      <x:c r="F22" s="28"/>
+      <x:c r="G22" s="28"/>
+      <x:c r="H22" s="28"/>
+      <x:c r="I22" s="28"/>
+      <x:c r="J22" s="28"/>
+      <x:c r="K22" s="28"/>
+      <x:c r="L22" s="44"/>
       <x:c r="M22" s="28"/>
-      <x:c r="N22" s="67"/>
-      <x:c r="O22" s="63"/>
-      <x:c r="P22" s="63"/>
-      <x:c r="Q22" s="63"/>
-      <x:c r="R22" s="63"/>
-      <x:c r="S22" s="63"/>
-      <x:c r="T22" s="63"/>
-      <x:c r="U22" s="63"/>
-      <x:c r="V22" s="63"/>
-      <x:c r="W22" s="68"/>
+      <x:c r="N22" s="43"/>
+      <x:c r="O22" s="28"/>
+      <x:c r="P22" s="28"/>
+      <x:c r="Q22" s="28"/>
+      <x:c r="R22" s="28"/>
+      <x:c r="S22" s="28"/>
+      <x:c r="T22" s="28"/>
+      <x:c r="U22" s="28"/>
+      <x:c r="V22" s="28"/>
+      <x:c r="W22" s="44"/>
       <x:c r="X22" s="28"/>
     </x:row>
     <x:row r="23" ht="20" customHeight="1">
       <x:c r="A23" s="28"/>
-      <x:c r="B23" s="67"/>
-      <x:c r="C23" s="63"/>
-      <x:c r="D23" s="63"/>
-      <x:c r="E23" s="63"/>
-      <x:c r="F23" s="63"/>
-      <x:c r="G23" s="63"/>
-      <x:c r="H23" s="63"/>
-      <x:c r="I23" s="63"/>
-      <x:c r="J23" s="63"/>
-      <x:c r="K23" s="63"/>
-      <x:c r="L23" s="68"/>
+      <x:c r="B23" s="43"/>
+      <x:c r="C23" s="28"/>
+      <x:c r="D23" s="28"/>
+      <x:c r="E23" s="28"/>
+      <x:c r="F23" s="28"/>
+      <x:c r="G23" s="28"/>
+      <x:c r="H23" s="28"/>
+      <x:c r="I23" s="28"/>
+      <x:c r="J23" s="28"/>
+      <x:c r="K23" s="28"/>
+      <x:c r="L23" s="44"/>
       <x:c r="M23" s="28"/>
-      <x:c r="N23" s="67"/>
-      <x:c r="O23" s="63"/>
-      <x:c r="P23" s="63"/>
-      <x:c r="Q23" s="63"/>
-      <x:c r="R23" s="63"/>
-      <x:c r="S23" s="63"/>
-      <x:c r="T23" s="63"/>
-      <x:c r="U23" s="63"/>
-      <x:c r="V23" s="63"/>
-      <x:c r="W23" s="68"/>
+      <x:c r="N23" s="43"/>
+      <x:c r="O23" s="28"/>
+      <x:c r="P23" s="28"/>
+      <x:c r="Q23" s="28"/>
+      <x:c r="R23" s="28"/>
+      <x:c r="S23" s="28"/>
+      <x:c r="T23" s="28"/>
+      <x:c r="U23" s="28"/>
+      <x:c r="V23" s="28"/>
+      <x:c r="W23" s="44"/>
       <x:c r="X23" s="28"/>
     </x:row>
     <x:row r="24" ht="20" customHeight="1">
       <x:c r="A24" s="28"/>
-      <x:c r="B24" s="67"/>
-      <x:c r="C24" s="63"/>
-      <x:c r="D24" s="63"/>
-      <x:c r="E24" s="63"/>
-      <x:c r="F24" s="63"/>
-      <x:c r="G24" s="63"/>
-      <x:c r="H24" s="63"/>
-      <x:c r="I24" s="63"/>
-      <x:c r="J24" s="63"/>
-      <x:c r="K24" s="63"/>
-      <x:c r="L24" s="68"/>
+      <x:c r="B24" s="43"/>
+      <x:c r="C24" s="28"/>
+      <x:c r="D24" s="28"/>
+      <x:c r="E24" s="28"/>
+      <x:c r="F24" s="28"/>
+      <x:c r="G24" s="28"/>
+      <x:c r="H24" s="28"/>
+      <x:c r="I24" s="28"/>
+      <x:c r="J24" s="28"/>
+      <x:c r="K24" s="28"/>
+      <x:c r="L24" s="44"/>
       <x:c r="M24" s="28"/>
-      <x:c r="N24" s="67"/>
-      <x:c r="O24" s="63"/>
-      <x:c r="P24" s="63"/>
-      <x:c r="Q24" s="63"/>
-      <x:c r="R24" s="63"/>
-      <x:c r="S24" s="63"/>
-      <x:c r="T24" s="63"/>
-      <x:c r="U24" s="63"/>
-      <x:c r="V24" s="63"/>
-      <x:c r="W24" s="68"/>
+      <x:c r="N24" s="43"/>
+      <x:c r="O24" s="28"/>
+      <x:c r="P24" s="28"/>
+      <x:c r="Q24" s="28"/>
+      <x:c r="R24" s="28"/>
+      <x:c r="S24" s="28"/>
+      <x:c r="T24" s="28"/>
+      <x:c r="U24" s="28"/>
+      <x:c r="V24" s="28"/>
+      <x:c r="W24" s="44"/>
       <x:c r="X24" s="28"/>
     </x:row>
     <x:row r="25" ht="20" customHeight="1">
       <x:c r="A25" s="28"/>
-      <x:c r="B25" s="67"/>
-      <x:c r="C25" s="63"/>
-      <x:c r="D25" s="63"/>
-      <x:c r="E25" s="63"/>
-      <x:c r="F25" s="63"/>
-      <x:c r="G25" s="63"/>
-      <x:c r="H25" s="63"/>
-      <x:c r="I25" s="63"/>
-      <x:c r="J25" s="63"/>
-      <x:c r="K25" s="63"/>
-      <x:c r="L25" s="68"/>
+      <x:c r="B25" s="43"/>
+      <x:c r="C25" s="28"/>
+      <x:c r="D25" s="28"/>
+      <x:c r="E25" s="28"/>
+      <x:c r="F25" s="28"/>
+      <x:c r="G25" s="28"/>
+      <x:c r="H25" s="28"/>
+      <x:c r="I25" s="28"/>
+      <x:c r="J25" s="28"/>
+      <x:c r="K25" s="28"/>
+      <x:c r="L25" s="44"/>
       <x:c r="M25" s="28"/>
-      <x:c r="N25" s="67"/>
-      <x:c r="O25" s="63"/>
-      <x:c r="P25" s="63"/>
-      <x:c r="Q25" s="63"/>
-      <x:c r="R25" s="63"/>
-      <x:c r="S25" s="63"/>
-      <x:c r="T25" s="63"/>
-      <x:c r="U25" s="63"/>
-      <x:c r="V25" s="63"/>
-      <x:c r="W25" s="68"/>
+      <x:c r="N25" s="43"/>
+      <x:c r="O25" s="28"/>
+      <x:c r="P25" s="28"/>
+      <x:c r="Q25" s="28"/>
+      <x:c r="R25" s="28"/>
+      <x:c r="S25" s="28"/>
+      <x:c r="T25" s="28"/>
+      <x:c r="U25" s="28"/>
+      <x:c r="V25" s="28"/>
+      <x:c r="W25" s="44"/>
       <x:c r="X25" s="28"/>
     </x:row>
     <x:row r="26" ht="20" customHeight="1">
       <x:c r="A26" s="28"/>
-      <x:c r="B26" s="67"/>
-      <x:c r="C26" s="63"/>
-      <x:c r="D26" s="63"/>
-      <x:c r="E26" s="63"/>
-      <x:c r="F26" s="63"/>
-      <x:c r="G26" s="63"/>
-      <x:c r="H26" s="63"/>
-      <x:c r="I26" s="63"/>
-      <x:c r="J26" s="63"/>
-      <x:c r="K26" s="63"/>
-      <x:c r="L26" s="68"/>
+      <x:c r="B26" s="43"/>
+      <x:c r="C26" s="28"/>
+      <x:c r="D26" s="28"/>
+      <x:c r="E26" s="28"/>
+      <x:c r="F26" s="28"/>
+      <x:c r="G26" s="28"/>
+      <x:c r="H26" s="28"/>
+      <x:c r="I26" s="28"/>
+      <x:c r="J26" s="28"/>
+      <x:c r="K26" s="28"/>
+      <x:c r="L26" s="44"/>
       <x:c r="M26" s="28"/>
-      <x:c r="N26" s="67"/>
-      <x:c r="O26" s="63"/>
-      <x:c r="P26" s="63"/>
-      <x:c r="Q26" s="63"/>
-      <x:c r="R26" s="63"/>
-      <x:c r="S26" s="63"/>
-      <x:c r="T26" s="63"/>
-      <x:c r="U26" s="63"/>
-      <x:c r="V26" s="63"/>
-      <x:c r="W26" s="68"/>
+      <x:c r="N26" s="43"/>
+      <x:c r="O26" s="28"/>
+      <x:c r="P26" s="28"/>
+      <x:c r="Q26" s="28"/>
+      <x:c r="R26" s="28"/>
+      <x:c r="S26" s="28"/>
+      <x:c r="T26" s="28"/>
+      <x:c r="U26" s="28"/>
+      <x:c r="V26" s="28"/>
+      <x:c r="W26" s="44"/>
       <x:c r="X26" s="28"/>
     </x:row>
     <x:row r="27" ht="20" customHeight="1">
       <x:c r="A27" s="28"/>
-      <x:c r="B27" s="67"/>
-      <x:c r="C27" s="63"/>
-      <x:c r="D27" s="63"/>
-      <x:c r="E27" s="63"/>
-      <x:c r="F27" s="63"/>
-      <x:c r="G27" s="63"/>
-      <x:c r="H27" s="63"/>
-      <x:c r="I27" s="63"/>
-      <x:c r="J27" s="63"/>
-      <x:c r="K27" s="63"/>
-      <x:c r="L27" s="68"/>
+      <x:c r="B27" s="43"/>
+      <x:c r="C27" s="28"/>
+      <x:c r="D27" s="28"/>
+      <x:c r="E27" s="28"/>
+      <x:c r="F27" s="28"/>
+      <x:c r="G27" s="28"/>
+      <x:c r="H27" s="28"/>
+      <x:c r="I27" s="28"/>
+      <x:c r="J27" s="28"/>
+      <x:c r="K27" s="28"/>
+      <x:c r="L27" s="44"/>
       <x:c r="M27" s="28"/>
-      <x:c r="N27" s="67"/>
-      <x:c r="O27" s="63"/>
-      <x:c r="P27" s="63"/>
-      <x:c r="Q27" s="63"/>
-      <x:c r="R27" s="63"/>
-      <x:c r="S27" s="63"/>
-      <x:c r="T27" s="63"/>
-      <x:c r="U27" s="63"/>
-      <x:c r="V27" s="63"/>
-      <x:c r="W27" s="68"/>
+      <x:c r="N27" s="43"/>
+      <x:c r="O27" s="28"/>
+      <x:c r="P27" s="28"/>
+      <x:c r="Q27" s="28"/>
+      <x:c r="R27" s="28"/>
+      <x:c r="S27" s="28"/>
+      <x:c r="T27" s="28"/>
+      <x:c r="U27" s="28"/>
+      <x:c r="V27" s="28"/>
+      <x:c r="W27" s="44"/>
       <x:c r="X27" s="28"/>
     </x:row>
     <x:row r="28" ht="20" customHeight="1">
       <x:c r="A28" s="28"/>
-      <x:c r="B28" s="67"/>
-      <x:c r="C28" s="63"/>
-      <x:c r="D28" s="63"/>
-      <x:c r="E28" s="63"/>
-      <x:c r="F28" s="63"/>
-      <x:c r="G28" s="63"/>
-      <x:c r="H28" s="63"/>
-      <x:c r="I28" s="63"/>
-      <x:c r="J28" s="63"/>
-      <x:c r="K28" s="63"/>
-      <x:c r="L28" s="68"/>
+      <x:c r="B28" s="43"/>
+      <x:c r="C28" s="28"/>
+      <x:c r="D28" s="28"/>
+      <x:c r="E28" s="28"/>
+      <x:c r="F28" s="28"/>
+      <x:c r="G28" s="28"/>
+      <x:c r="H28" s="28"/>
+      <x:c r="I28" s="28"/>
+      <x:c r="J28" s="28"/>
+      <x:c r="K28" s="28"/>
+      <x:c r="L28" s="44"/>
       <x:c r="M28" s="28"/>
-      <x:c r="N28" s="67"/>
-      <x:c r="O28" s="63"/>
-      <x:c r="P28" s="63"/>
-      <x:c r="Q28" s="63"/>
-      <x:c r="R28" s="63"/>
-      <x:c r="S28" s="63"/>
-      <x:c r="T28" s="63"/>
-      <x:c r="U28" s="63"/>
-      <x:c r="V28" s="63"/>
-      <x:c r="W28" s="68"/>
+      <x:c r="N28" s="43"/>
+      <x:c r="O28" s="28"/>
+      <x:c r="P28" s="28"/>
+      <x:c r="Q28" s="28"/>
+      <x:c r="R28" s="28"/>
+      <x:c r="S28" s="28"/>
+      <x:c r="T28" s="28"/>
+      <x:c r="U28" s="28"/>
+      <x:c r="V28" s="28"/>
+      <x:c r="W28" s="44"/>
       <x:c r="X28" s="28"/>
     </x:row>
     <x:row r="29" ht="20" customHeight="1">
       <x:c r="A29" s="28"/>
-      <x:c r="B29" s="67"/>
-      <x:c r="C29" s="63"/>
-      <x:c r="D29" s="63"/>
-      <x:c r="E29" s="63"/>
-      <x:c r="F29" s="63"/>
-      <x:c r="G29" s="63"/>
-      <x:c r="H29" s="63"/>
-      <x:c r="I29" s="63"/>
-      <x:c r="J29" s="63"/>
-      <x:c r="K29" s="63"/>
-      <x:c r="L29" s="68"/>
+      <x:c r="B29" s="43"/>
+      <x:c r="C29" s="28"/>
+      <x:c r="D29" s="28"/>
+      <x:c r="E29" s="28"/>
+      <x:c r="F29" s="28"/>
+      <x:c r="G29" s="28"/>
+      <x:c r="H29" s="28"/>
+      <x:c r="I29" s="28"/>
+      <x:c r="J29" s="28"/>
+      <x:c r="K29" s="28"/>
+      <x:c r="L29" s="44"/>
       <x:c r="M29" s="28"/>
-      <x:c r="N29" s="67"/>
-      <x:c r="O29" s="63"/>
-      <x:c r="P29" s="63"/>
-      <x:c r="Q29" s="63"/>
-      <x:c r="R29" s="63"/>
-      <x:c r="S29" s="63"/>
-      <x:c r="T29" s="63"/>
-      <x:c r="U29" s="63"/>
-      <x:c r="V29" s="63"/>
-      <x:c r="W29" s="68"/>
+      <x:c r="N29" s="43"/>
+      <x:c r="O29" s="28"/>
+      <x:c r="P29" s="28"/>
+      <x:c r="Q29" s="28"/>
+      <x:c r="R29" s="28"/>
+      <x:c r="S29" s="28"/>
+      <x:c r="T29" s="28"/>
+      <x:c r="U29" s="28"/>
+      <x:c r="V29" s="28"/>
+      <x:c r="W29" s="44"/>
       <x:c r="X29" s="28"/>
     </x:row>
     <x:row r="30" ht="20" customHeight="1">
       <x:c r="A30" s="28"/>
-      <x:c r="B30" s="67"/>
-      <x:c r="C30" s="63"/>
-      <x:c r="D30" s="63"/>
-      <x:c r="E30" s="63"/>
-      <x:c r="F30" s="63"/>
-      <x:c r="G30" s="63"/>
-      <x:c r="H30" s="63"/>
-      <x:c r="I30" s="63"/>
-      <x:c r="J30" s="63"/>
-      <x:c r="K30" s="63"/>
-      <x:c r="L30" s="68"/>
+      <x:c r="B30" s="43"/>
+      <x:c r="C30" s="28"/>
+      <x:c r="D30" s="28"/>
+      <x:c r="E30" s="28"/>
+      <x:c r="F30" s="28"/>
+      <x:c r="G30" s="28"/>
+      <x:c r="H30" s="28"/>
+      <x:c r="I30" s="28"/>
+      <x:c r="J30" s="28"/>
+      <x:c r="K30" s="28"/>
+      <x:c r="L30" s="44"/>
       <x:c r="M30" s="28"/>
-      <x:c r="N30" s="67"/>
-      <x:c r="O30" s="63"/>
-      <x:c r="P30" s="63"/>
-      <x:c r="Q30" s="63"/>
-      <x:c r="R30" s="63"/>
-      <x:c r="S30" s="63"/>
-      <x:c r="T30" s="63"/>
-      <x:c r="U30" s="63"/>
-      <x:c r="V30" s="63"/>
-      <x:c r="W30" s="68"/>
+      <x:c r="N30" s="43"/>
+      <x:c r="O30" s="28"/>
+      <x:c r="P30" s="28"/>
+      <x:c r="Q30" s="28"/>
+      <x:c r="R30" s="28"/>
+      <x:c r="S30" s="28"/>
+      <x:c r="T30" s="28"/>
+      <x:c r="U30" s="28"/>
+      <x:c r="V30" s="28"/>
+      <x:c r="W30" s="44"/>
       <x:c r="X30" s="28"/>
     </x:row>
     <x:row r="31" ht="20" customHeight="1">
       <x:c r="A31" s="28"/>
-      <x:c r="B31" s="67"/>
-      <x:c r="C31" s="63"/>
-      <x:c r="D31" s="63"/>
-      <x:c r="E31" s="63"/>
-      <x:c r="F31" s="63"/>
-      <x:c r="G31" s="63"/>
-      <x:c r="H31" s="63"/>
-      <x:c r="I31" s="63"/>
-      <x:c r="J31" s="63"/>
-      <x:c r="K31" s="63"/>
-      <x:c r="L31" s="68"/>
+      <x:c r="B31" s="43"/>
+      <x:c r="C31" s="28"/>
+      <x:c r="D31" s="28"/>
+      <x:c r="E31" s="28"/>
+      <x:c r="F31" s="28"/>
+      <x:c r="G31" s="28"/>
+      <x:c r="H31" s="28"/>
+      <x:c r="I31" s="28"/>
+      <x:c r="J31" s="28"/>
+      <x:c r="K31" s="28"/>
+      <x:c r="L31" s="44"/>
       <x:c r="M31" s="28"/>
-      <x:c r="N31" s="67"/>
-      <x:c r="O31" s="63"/>
-      <x:c r="P31" s="63"/>
-      <x:c r="Q31" s="63"/>
-      <x:c r="R31" s="63"/>
-      <x:c r="S31" s="63"/>
-      <x:c r="T31" s="63"/>
-      <x:c r="U31" s="63"/>
-      <x:c r="V31" s="63"/>
-      <x:c r="W31" s="68"/>
+      <x:c r="N31" s="43"/>
+      <x:c r="O31" s="28"/>
+      <x:c r="P31" s="28"/>
+      <x:c r="Q31" s="28"/>
+      <x:c r="R31" s="28"/>
+      <x:c r="S31" s="28"/>
+      <x:c r="T31" s="28"/>
+      <x:c r="U31" s="28"/>
+      <x:c r="V31" s="28"/>
+      <x:c r="W31" s="44"/>
       <x:c r="X31" s="28"/>
     </x:row>
     <x:row r="32" ht="20" customHeight="1">
       <x:c r="A32" s="28"/>
-      <x:c r="B32" s="67"/>
-      <x:c r="C32" s="63"/>
-      <x:c r="D32" s="63"/>
-      <x:c r="E32" s="63"/>
-      <x:c r="F32" s="63"/>
-      <x:c r="G32" s="63"/>
-      <x:c r="H32" s="63"/>
-      <x:c r="I32" s="63"/>
-      <x:c r="J32" s="63"/>
-      <x:c r="K32" s="63"/>
-      <x:c r="L32" s="68"/>
+      <x:c r="B32" s="43"/>
+      <x:c r="C32" s="28"/>
+      <x:c r="D32" s="28"/>
+      <x:c r="E32" s="28"/>
+      <x:c r="F32" s="28"/>
+      <x:c r="G32" s="28"/>
+      <x:c r="H32" s="28"/>
+      <x:c r="I32" s="28"/>
+      <x:c r="J32" s="28"/>
+      <x:c r="K32" s="28"/>
+      <x:c r="L32" s="44"/>
       <x:c r="M32" s="28"/>
-      <x:c r="N32" s="67"/>
-      <x:c r="O32" s="63"/>
-      <x:c r="P32" s="63"/>
-      <x:c r="Q32" s="63"/>
-      <x:c r="R32" s="63"/>
-      <x:c r="S32" s="63"/>
-      <x:c r="T32" s="63"/>
-      <x:c r="U32" s="63"/>
-      <x:c r="V32" s="63"/>
-      <x:c r="W32" s="68"/>
+      <x:c r="N32" s="43"/>
+      <x:c r="O32" s="28"/>
+      <x:c r="P32" s="28"/>
+      <x:c r="Q32" s="28"/>
+      <x:c r="R32" s="28"/>
+      <x:c r="S32" s="28"/>
+      <x:c r="T32" s="28"/>
+      <x:c r="U32" s="28"/>
+      <x:c r="V32" s="28"/>
+      <x:c r="W32" s="44"/>
       <x:c r="X32" s="28"/>
     </x:row>
     <x:row r="33" ht="20" customHeight="1">
       <x:c r="A33" s="28"/>
-      <x:c r="B33" s="67"/>
-      <x:c r="C33" s="63"/>
-      <x:c r="D33" s="63"/>
-      <x:c r="E33" s="63"/>
-      <x:c r="F33" s="63"/>
-      <x:c r="G33" s="63"/>
-      <x:c r="H33" s="63"/>
-      <x:c r="I33" s="63"/>
-      <x:c r="J33" s="63"/>
-      <x:c r="K33" s="63"/>
-      <x:c r="L33" s="68"/>
+      <x:c r="B33" s="43"/>
+      <x:c r="C33" s="28"/>
+      <x:c r="D33" s="28"/>
+      <x:c r="E33" s="28"/>
+      <x:c r="F33" s="28"/>
+      <x:c r="G33" s="28"/>
+      <x:c r="H33" s="28"/>
+      <x:c r="I33" s="28"/>
+      <x:c r="J33" s="28"/>
+      <x:c r="K33" s="28"/>
+      <x:c r="L33" s="44"/>
       <x:c r="M33" s="28"/>
-      <x:c r="N33" s="67"/>
-      <x:c r="O33" s="63"/>
-      <x:c r="P33" s="63"/>
-      <x:c r="Q33" s="63"/>
-      <x:c r="R33" s="63"/>
-      <x:c r="S33" s="63"/>
-      <x:c r="T33" s="63"/>
-      <x:c r="U33" s="63"/>
-      <x:c r="V33" s="63"/>
-      <x:c r="W33" s="68"/>
+      <x:c r="N33" s="43"/>
+      <x:c r="O33" s="28"/>
+      <x:c r="P33" s="28"/>
+      <x:c r="Q33" s="28"/>
+      <x:c r="R33" s="28"/>
+      <x:c r="S33" s="28"/>
+      <x:c r="T33" s="28"/>
+      <x:c r="U33" s="28"/>
+      <x:c r="V33" s="28"/>
+      <x:c r="W33" s="44"/>
       <x:c r="X33" s="28"/>
     </x:row>
     <x:row r="34" ht="20" customHeight="1">
       <x:c r="A34" s="28"/>
-      <x:c r="B34" s="67"/>
-      <x:c r="C34" s="63"/>
-      <x:c r="D34" s="63"/>
-      <x:c r="E34" s="63"/>
-      <x:c r="F34" s="63"/>
-      <x:c r="G34" s="63"/>
-      <x:c r="H34" s="63"/>
-      <x:c r="I34" s="63"/>
-      <x:c r="J34" s="63"/>
-      <x:c r="K34" s="63"/>
-      <x:c r="L34" s="68"/>
+      <x:c r="B34" s="43"/>
+      <x:c r="C34" s="28"/>
+      <x:c r="D34" s="28"/>
+      <x:c r="E34" s="28"/>
+      <x:c r="F34" s="28"/>
+      <x:c r="G34" s="28"/>
+      <x:c r="H34" s="28"/>
+      <x:c r="I34" s="28"/>
+      <x:c r="J34" s="28"/>
+      <x:c r="K34" s="28"/>
+      <x:c r="L34" s="44"/>
       <x:c r="M34" s="28"/>
-      <x:c r="N34" s="67"/>
-      <x:c r="O34" s="63"/>
-      <x:c r="P34" s="63"/>
-      <x:c r="Q34" s="63"/>
-      <x:c r="R34" s="63"/>
-      <x:c r="S34" s="63"/>
-      <x:c r="T34" s="63"/>
-      <x:c r="U34" s="63"/>
-      <x:c r="V34" s="63"/>
-      <x:c r="W34" s="68"/>
+      <x:c r="N34" s="43"/>
+      <x:c r="O34" s="28"/>
+      <x:c r="P34" s="28"/>
+      <x:c r="Q34" s="28"/>
+      <x:c r="R34" s="28"/>
+      <x:c r="S34" s="28"/>
+      <x:c r="T34" s="28"/>
+      <x:c r="U34" s="28"/>
+      <x:c r="V34" s="28"/>
+      <x:c r="W34" s="44"/>
       <x:c r="X34" s="28"/>
     </x:row>
     <x:row r="35" ht="20" customHeight="1">
       <x:c r="A35" s="28"/>
-      <x:c r="B35" s="67"/>
-      <x:c r="C35" s="63"/>
-      <x:c r="D35" s="63"/>
-      <x:c r="E35" s="63"/>
-      <x:c r="F35" s="63"/>
-      <x:c r="G35" s="63"/>
-      <x:c r="H35" s="63"/>
-      <x:c r="I35" s="63"/>
-      <x:c r="J35" s="63"/>
-      <x:c r="K35" s="63"/>
-      <x:c r="L35" s="68"/>
+      <x:c r="B35" s="43"/>
+      <x:c r="C35" s="28"/>
+      <x:c r="D35" s="28"/>
+      <x:c r="E35" s="28"/>
+      <x:c r="F35" s="28"/>
+      <x:c r="G35" s="28"/>
+      <x:c r="H35" s="28"/>
+      <x:c r="I35" s="28"/>
+      <x:c r="J35" s="28"/>
+      <x:c r="K35" s="28"/>
+      <x:c r="L35" s="44"/>
       <x:c r="M35" s="28"/>
-      <x:c r="N35" s="67"/>
-      <x:c r="O35" s="63"/>
-      <x:c r="P35" s="63"/>
-      <x:c r="Q35" s="63"/>
-      <x:c r="R35" s="63"/>
-      <x:c r="S35" s="63"/>
-      <x:c r="T35" s="63"/>
-      <x:c r="U35" s="63"/>
-      <x:c r="V35" s="63"/>
-      <x:c r="W35" s="68"/>
+      <x:c r="N35" s="43"/>
+      <x:c r="O35" s="28"/>
+      <x:c r="P35" s="28"/>
+      <x:c r="Q35" s="28"/>
+      <x:c r="R35" s="28"/>
+      <x:c r="S35" s="28"/>
+      <x:c r="T35" s="28"/>
+      <x:c r="U35" s="28"/>
+      <x:c r="V35" s="28"/>
+      <x:c r="W35" s="44"/>
       <x:c r="X35" s="28"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
       <x:c r="A36" s="28"/>
-      <x:c r="B36" s="94" t="str">
+      <x:c r="B36" s="125" t="str">
         <x:v>  ■ 출처 ORS 공개 이력 · 단위 버전 · 유효시작일 기준(등록일 아님) · 정확한 수치는 통계 시트 D~H열</x:v>
       </x:c>
-      <x:c r="C36" s="95"/>
-      <x:c r="D36" s="95"/>
-      <x:c r="E36" s="95"/>
-      <x:c r="F36" s="95"/>
-      <x:c r="G36" s="95"/>
-      <x:c r="H36" s="95"/>
-      <x:c r="I36" s="95"/>
-      <x:c r="J36" s="95"/>
-      <x:c r="K36" s="95"/>
-      <x:c r="L36" s="96"/>
+      <x:c r="C36" s="126"/>
+      <x:c r="D36" s="126"/>
+      <x:c r="E36" s="126"/>
+      <x:c r="F36" s="126"/>
+      <x:c r="G36" s="126"/>
+      <x:c r="H36" s="126"/>
+      <x:c r="I36" s="126"/>
+      <x:c r="J36" s="126"/>
+      <x:c r="K36" s="126"/>
+      <x:c r="L36" s="127"/>
       <x:c r="M36" s="28"/>
-      <x:c r="N36" s="94" t="str">
+      <x:c r="N36" s="125" t="str">
         <x:v>  ■ 경과일 = 유효시작일 상한 − 최신 버전 유효시작일 · 법정기한·효력 판단 아님 · 단위 방법론</x:v>
       </x:c>
-      <x:c r="O36" s="95"/>
-      <x:c r="P36" s="95"/>
-      <x:c r="Q36" s="95"/>
-      <x:c r="R36" s="95"/>
-      <x:c r="S36" s="95"/>
-      <x:c r="T36" s="95"/>
-      <x:c r="U36" s="95"/>
-      <x:c r="V36" s="95"/>
-      <x:c r="W36" s="96"/>
+      <x:c r="O36" s="126"/>
+      <x:c r="P36" s="126"/>
+      <x:c r="Q36" s="126"/>
+      <x:c r="R36" s="126"/>
+      <x:c r="S36" s="126"/>
+      <x:c r="T36" s="126"/>
+      <x:c r="U36" s="126"/>
+      <x:c r="V36" s="126"/>
+      <x:c r="W36" s="127"/>
       <x:c r="X36" s="28"/>
     </x:row>
     <x:row r="37" ht="14" customHeight="1">
@@ -2629,66 +2855,66 @@
     </x:row>
     <x:row r="38" ht="16" customHeight="1">
       <x:c r="A38" s="28"/>
-      <x:c r="B38" s="75" t="str">
+      <x:c r="B38" s="107" t="str">
         <x:v>03</x:v>
       </x:c>
-      <x:c r="C38" s="76" t="str">
+      <x:c r="C38" s="108" t="str">
         <x:v>SAME PERIOD</x:v>
       </x:c>
-      <x:c r="D38" s="76"/>
-      <x:c r="E38" s="76"/>
-      <x:c r="F38" s="76"/>
-      <x:c r="G38" s="76"/>
-      <x:c r="H38" s="76"/>
-      <x:c r="I38" s="76"/>
-      <x:c r="J38" s="76"/>
-      <x:c r="K38" s="76"/>
-      <x:c r="L38" s="77"/>
+      <x:c r="D38" s="108"/>
+      <x:c r="E38" s="108"/>
+      <x:c r="F38" s="108"/>
+      <x:c r="G38" s="108"/>
+      <x:c r="H38" s="108"/>
+      <x:c r="I38" s="108"/>
+      <x:c r="J38" s="108"/>
+      <x:c r="K38" s="108"/>
+      <x:c r="L38" s="109"/>
       <x:c r="M38" s="28"/>
-      <x:c r="N38" s="75" t="str">
+      <x:c r="N38" s="107" t="str">
         <x:v>04</x:v>
       </x:c>
-      <x:c r="O38" s="76" t="str">
+      <x:c r="O38" s="108" t="str">
         <x:v>REVISION</x:v>
       </x:c>
-      <x:c r="P38" s="76"/>
-      <x:c r="Q38" s="76"/>
-      <x:c r="R38" s="76"/>
-      <x:c r="S38" s="76"/>
-      <x:c r="T38" s="76"/>
-      <x:c r="U38" s="76"/>
-      <x:c r="V38" s="76"/>
-      <x:c r="W38" s="77"/>
+      <x:c r="P38" s="108"/>
+      <x:c r="Q38" s="108"/>
+      <x:c r="R38" s="108"/>
+      <x:c r="S38" s="108"/>
+      <x:c r="T38" s="108"/>
+      <x:c r="U38" s="108"/>
+      <x:c r="V38" s="108"/>
+      <x:c r="W38" s="109"/>
       <x:c r="X38" s="28"/>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
       <x:c r="A39" s="28"/>
-      <x:c r="B39" s="78" t="str">
+      <x:c r="B39" s="110" t="str">
         <x:v>  전년 같은 기간 비교</x:v>
       </x:c>
-      <x:c r="C39" s="79"/>
-      <x:c r="D39" s="79"/>
-      <x:c r="E39" s="79"/>
-      <x:c r="F39" s="79"/>
-      <x:c r="G39" s="79"/>
-      <x:c r="H39" s="79"/>
-      <x:c r="I39" s="79"/>
-      <x:c r="J39" s="79"/>
-      <x:c r="K39" s="79"/>
-      <x:c r="L39" s="80"/>
+      <x:c r="C39" s="111"/>
+      <x:c r="D39" s="111"/>
+      <x:c r="E39" s="111"/>
+      <x:c r="F39" s="111"/>
+      <x:c r="G39" s="111"/>
+      <x:c r="H39" s="111"/>
+      <x:c r="I39" s="111"/>
+      <x:c r="J39" s="111"/>
+      <x:c r="K39" s="111"/>
+      <x:c r="L39" s="112"/>
       <x:c r="M39" s="28"/>
-      <x:c r="N39" s="78" t="str">
+      <x:c r="N39" s="110" t="str">
         <x:v>  개정 경험·장기 관찰</x:v>
       </x:c>
-      <x:c r="O39" s="79"/>
-      <x:c r="P39" s="79"/>
-      <x:c r="Q39" s="79"/>
-      <x:c r="R39" s="79"/>
-      <x:c r="S39" s="79"/>
-      <x:c r="T39" s="79"/>
-      <x:c r="U39" s="79"/>
-      <x:c r="V39" s="79"/>
-      <x:c r="W39" s="80"/>
+      <x:c r="O39" s="111"/>
+      <x:c r="P39" s="111"/>
+      <x:c r="Q39" s="111"/>
+      <x:c r="R39" s="111"/>
+      <x:c r="S39" s="111"/>
+      <x:c r="T39" s="111"/>
+      <x:c r="U39" s="111"/>
+      <x:c r="V39" s="111"/>
+      <x:c r="W39" s="112"/>
       <x:c r="X39" s="28"/>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
@@ -2725,205 +2951,205 @@
     </x:row>
     <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="28"/>
-      <x:c r="B41" s="67"/>
-      <x:c r="C41" s="63"/>
-      <x:c r="D41" s="63"/>
-      <x:c r="E41" s="63"/>
-      <x:c r="F41" s="63"/>
-      <x:c r="G41" s="63"/>
-      <x:c r="H41" s="63"/>
-      <x:c r="I41" s="63"/>
-      <x:c r="J41" s="63"/>
-      <x:c r="K41" s="63"/>
-      <x:c r="L41" s="68"/>
+      <x:c r="B41" s="43"/>
+      <x:c r="C41" s="28"/>
+      <x:c r="D41" s="28"/>
+      <x:c r="E41" s="28"/>
+      <x:c r="F41" s="28"/>
+      <x:c r="G41" s="28"/>
+      <x:c r="H41" s="28"/>
+      <x:c r="I41" s="28"/>
+      <x:c r="J41" s="28"/>
+      <x:c r="K41" s="28"/>
+      <x:c r="L41" s="44"/>
       <x:c r="M41" s="28"/>
-      <x:c r="N41" s="67"/>
-      <x:c r="O41" s="63"/>
-      <x:c r="P41" s="63"/>
-      <x:c r="Q41" s="63"/>
-      <x:c r="R41" s="63"/>
-      <x:c r="S41" s="63"/>
-      <x:c r="T41" s="63"/>
-      <x:c r="U41" s="63"/>
-      <x:c r="V41" s="63"/>
-      <x:c r="W41" s="68"/>
+      <x:c r="N41" s="43"/>
+      <x:c r="O41" s="28"/>
+      <x:c r="P41" s="28"/>
+      <x:c r="Q41" s="28"/>
+      <x:c r="R41" s="28"/>
+      <x:c r="S41" s="28"/>
+      <x:c r="T41" s="28"/>
+      <x:c r="U41" s="28"/>
+      <x:c r="V41" s="28"/>
+      <x:c r="W41" s="44"/>
       <x:c r="X41" s="28"/>
     </x:row>
     <x:row r="42" ht="18" customHeight="1">
       <x:c r="A42" s="28"/>
-      <x:c r="B42" s="97" t="str">
+      <x:c r="B42" s="128" t="str">
         <x:v>  선택연도 누계</x:v>
       </x:c>
-      <x:c r="C42" s="98"/>
-      <x:c r="D42" s="98"/>
-      <x:c r="E42" s="98"/>
-      <x:c r="F42" s="98" t="str">
+      <x:c r="C42" s="129"/>
+      <x:c r="D42" s="129"/>
+      <x:c r="E42" s="129"/>
+      <x:c r="F42" s="129" t="str">
         <x:v>  전년 동기간</x:v>
       </x:c>
-      <x:c r="G42" s="98"/>
-      <x:c r="H42" s="98"/>
-      <x:c r="I42" s="98" t="str">
+      <x:c r="G42" s="129"/>
+      <x:c r="H42" s="129"/>
+      <x:c r="I42" s="129" t="str">
         <x:v>  증감</x:v>
       </x:c>
-      <x:c r="J42" s="98"/>
-      <x:c r="K42" s="98"/>
-      <x:c r="L42" s="107"/>
+      <x:c r="J42" s="129"/>
+      <x:c r="K42" s="129"/>
+      <x:c r="L42" s="138"/>
       <x:c r="M42" s="28"/>
-      <x:c r="N42" s="97" t="str">
+      <x:c r="N42" s="128" t="str">
         <x:v>  개정 경험 비중</x:v>
       </x:c>
-      <x:c r="O42" s="98"/>
-      <x:c r="P42" s="98"/>
-      <x:c r="Q42" s="98"/>
-      <x:c r="R42" s="98" t="str">
+      <x:c r="O42" s="129"/>
+      <x:c r="P42" s="129"/>
+      <x:c r="Q42" s="129"/>
+      <x:c r="R42" s="129" t="str">
         <x:v>  관찰 기준 초과</x:v>
       </x:c>
-      <x:c r="S42" s="98"/>
-      <x:c r="T42" s="98"/>
-      <x:c r="U42" s="98" t="str">
+      <x:c r="S42" s="129"/>
+      <x:c r="T42" s="129"/>
+      <x:c r="U42" s="129" t="str">
         <x:v>  경과일 중앙값</x:v>
       </x:c>
-      <x:c r="V42" s="98"/>
-      <x:c r="W42" s="107"/>
+      <x:c r="V42" s="129"/>
+      <x:c r="W42" s="138"/>
       <x:c r="X42" s="28"/>
     </x:row>
     <x:row r="43" ht="22" customHeight="1">
       <x:c r="A43" s="28"/>
-      <x:c r="B43" s="105" t="n">
+      <x:c r="B43" s="136" t="n">
         <x:f>'통계'!B15</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C43" s="106"/>
-      <x:c r="D43" s="106"/>
-      <x:c r="E43" s="106"/>
-      <x:c r="F43" s="106" t="n">
+      <x:c r="C43" s="137"/>
+      <x:c r="D43" s="137"/>
+      <x:c r="E43" s="137"/>
+      <x:c r="F43" s="137" t="n">
         <x:f>'통계'!B16</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G43" s="106"/>
-      <x:c r="H43" s="106"/>
-      <x:c r="I43" s="113" t="n">
+      <x:c r="G43" s="137"/>
+      <x:c r="H43" s="137"/>
+      <x:c r="I43" s="144" t="n">
         <x:f>'통계'!B17</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="J43" s="113"/>
-      <x:c r="K43" s="113"/>
-      <x:c r="L43" s="114"/>
+      <x:c r="J43" s="144"/>
+      <x:c r="K43" s="144"/>
+      <x:c r="L43" s="145"/>
       <x:c r="M43" s="28"/>
-      <x:c r="N43" s="115" t="n">
+      <x:c r="N43" s="146" t="n">
         <x:f>'통계'!B14</x:f>
         <x:v>0.18181818181818182</x:v>
       </x:c>
-      <x:c r="O43" s="116"/>
-      <x:c r="P43" s="116"/>
-      <x:c r="Q43" s="116"/>
-      <x:c r="R43" s="106" t="n">
+      <x:c r="O43" s="147"/>
+      <x:c r="P43" s="147"/>
+      <x:c r="Q43" s="147"/>
+      <x:c r="R43" s="137" t="n">
         <x:f>'통계'!B13</x:f>
         <x:v>23</x:v>
       </x:c>
-      <x:c r="S43" s="106"/>
-      <x:c r="T43" s="106"/>
-      <x:c r="U43" s="106" t="n">
+      <x:c r="S43" s="137"/>
+      <x:c r="T43" s="137"/>
+      <x:c r="U43" s="137" t="n">
         <x:f>'통계'!B19</x:f>
         <x:v>2057</x:v>
       </x:c>
-      <x:c r="V43" s="106"/>
-      <x:c r="W43" s="119"/>
+      <x:c r="V43" s="137"/>
+      <x:c r="W43" s="150"/>
       <x:c r="X43" s="28"/>
     </x:row>
     <x:row r="44" ht="22" customHeight="1">
       <x:c r="A44" s="28"/>
-      <x:c r="B44" s="105"/>
-      <x:c r="C44" s="106"/>
-      <x:c r="D44" s="106"/>
-      <x:c r="E44" s="106"/>
-      <x:c r="F44" s="106"/>
-      <x:c r="G44" s="106"/>
-      <x:c r="H44" s="106"/>
-      <x:c r="I44" s="113"/>
-      <x:c r="J44" s="113"/>
-      <x:c r="K44" s="113"/>
-      <x:c r="L44" s="114"/>
+      <x:c r="B44" s="136"/>
+      <x:c r="C44" s="137"/>
+      <x:c r="D44" s="137"/>
+      <x:c r="E44" s="137"/>
+      <x:c r="F44" s="137"/>
+      <x:c r="G44" s="137"/>
+      <x:c r="H44" s="137"/>
+      <x:c r="I44" s="144"/>
+      <x:c r="J44" s="144"/>
+      <x:c r="K44" s="144"/>
+      <x:c r="L44" s="145"/>
       <x:c r="M44" s="28"/>
-      <x:c r="N44" s="115"/>
-      <x:c r="O44" s="116"/>
-      <x:c r="P44" s="116"/>
-      <x:c r="Q44" s="116"/>
-      <x:c r="R44" s="106"/>
-      <x:c r="S44" s="106"/>
-      <x:c r="T44" s="106"/>
-      <x:c r="U44" s="106"/>
-      <x:c r="V44" s="106"/>
-      <x:c r="W44" s="119"/>
+      <x:c r="N44" s="146"/>
+      <x:c r="O44" s="147"/>
+      <x:c r="P44" s="147"/>
+      <x:c r="Q44" s="147"/>
+      <x:c r="R44" s="137"/>
+      <x:c r="S44" s="137"/>
+      <x:c r="T44" s="137"/>
+      <x:c r="U44" s="137"/>
+      <x:c r="V44" s="137"/>
+      <x:c r="W44" s="150"/>
       <x:c r="X44" s="28"/>
     </x:row>
     <x:row r="45" ht="18" customHeight="1">
       <x:c r="A45" s="28"/>
-      <x:c r="B45" s="103" t="str">
+      <x:c r="B45" s="134" t="str">
         <x:v>  버전</x:v>
       </x:c>
-      <x:c r="C45" s="104"/>
-      <x:c r="D45" s="104"/>
-      <x:c r="E45" s="104"/>
-      <x:c r="F45" s="104" t="str">
+      <x:c r="C45" s="135"/>
+      <x:c r="D45" s="135"/>
+      <x:c r="E45" s="135"/>
+      <x:c r="F45" s="135" t="str">
         <x:v>  버전</x:v>
       </x:c>
-      <x:c r="G45" s="104"/>
-      <x:c r="H45" s="104"/>
-      <x:c r="I45" s="104" t="str">
+      <x:c r="G45" s="135"/>
+      <x:c r="H45" s="135"/>
+      <x:c r="I45" s="135" t="str">
         <x:v>  버전</x:v>
       </x:c>
-      <x:c r="J45" s="104"/>
-      <x:c r="K45" s="104"/>
-      <x:c r="L45" s="112"/>
+      <x:c r="J45" s="135"/>
+      <x:c r="K45" s="135"/>
+      <x:c r="L45" s="143"/>
       <x:c r="M45" s="28"/>
-      <x:c r="N45" s="103" t="str">
+      <x:c r="N45" s="134" t="str">
         <x:v>  고유 방법론 대비</x:v>
       </x:c>
-      <x:c r="O45" s="104"/>
-      <x:c r="P45" s="104"/>
-      <x:c r="Q45" s="104"/>
-      <x:c r="R45" s="104" t="str">
+      <x:c r="O45" s="135"/>
+      <x:c r="P45" s="135"/>
+      <x:c r="Q45" s="135"/>
+      <x:c r="R45" s="135" t="str">
         <x:v>  방법론</x:v>
       </x:c>
-      <x:c r="S45" s="104"/>
-      <x:c r="T45" s="104"/>
-      <x:c r="U45" s="104" t="str">
+      <x:c r="S45" s="135"/>
+      <x:c r="T45" s="135"/>
+      <x:c r="U45" s="135" t="str">
         <x:v>  일</x:v>
       </x:c>
-      <x:c r="V45" s="104"/>
-      <x:c r="W45" s="112"/>
+      <x:c r="V45" s="135"/>
+      <x:c r="W45" s="143"/>
       <x:c r="X45" s="28"/>
     </x:row>
     <x:row r="46" ht="30" customHeight="1">
       <x:c r="A46" s="28"/>
-      <x:c r="B46" s="94" t="str">
+      <x:c r="B46" s="125" t="str">
         <x:f>"  ■ 비교 기간 1월 1일~"&amp;TEXT('분석조건'!B14,"yyyy-mm-dd")&amp;" / 전년 1월 1일~"&amp;TEXT('분석조건'!B15,"yyyy-mm-dd")&amp;" · 단위 버전 · 선택한 코드 밖의 증가는 반영하지 않음"</x:f>
         <x:v>  ■ 비교 기간 1월 1일~2026-10-14 / 전년 1월 1일~2025-10-14 · 단위 버전 · 선택한 코드 밖의 증가는 반영하지 않음</x:v>
       </x:c>
-      <x:c r="C46" s="95"/>
-      <x:c r="D46" s="95"/>
-      <x:c r="E46" s="95"/>
-      <x:c r="F46" s="95"/>
-      <x:c r="G46" s="95"/>
-      <x:c r="H46" s="95"/>
-      <x:c r="I46" s="95"/>
-      <x:c r="J46" s="95"/>
-      <x:c r="K46" s="95"/>
-      <x:c r="L46" s="96"/>
+      <x:c r="C46" s="126"/>
+      <x:c r="D46" s="126"/>
+      <x:c r="E46" s="126"/>
+      <x:c r="F46" s="126"/>
+      <x:c r="G46" s="126"/>
+      <x:c r="H46" s="126"/>
+      <x:c r="I46" s="126"/>
+      <x:c r="J46" s="126"/>
+      <x:c r="K46" s="126"/>
+      <x:c r="L46" s="127"/>
       <x:c r="M46" s="28"/>
-      <x:c r="N46" s="94" t="str">
+      <x:c r="N46" s="125" t="str">
         <x:v>  ■ 개정 경험 = 공개 개정 이력 1회 이상 · 변경이 없다는 이유로 적용 불가로 판단하지 않음</x:v>
       </x:c>
-      <x:c r="O46" s="95"/>
-      <x:c r="P46" s="95"/>
-      <x:c r="Q46" s="95"/>
-      <x:c r="R46" s="95"/>
-      <x:c r="S46" s="95"/>
-      <x:c r="T46" s="95"/>
-      <x:c r="U46" s="95"/>
-      <x:c r="V46" s="95"/>
-      <x:c r="W46" s="96"/>
+      <x:c r="O46" s="126"/>
+      <x:c r="P46" s="126"/>
+      <x:c r="Q46" s="126"/>
+      <x:c r="R46" s="126"/>
+      <x:c r="S46" s="126"/>
+      <x:c r="T46" s="126"/>
+      <x:c r="U46" s="126"/>
+      <x:c r="V46" s="126"/>
+      <x:c r="W46" s="127"/>
       <x:c r="X46" s="28"/>
     </x:row>
     <x:row r="47" ht="14" customHeight="1">
@@ -2954,60 +3180,60 @@
     </x:row>
     <x:row r="48" ht="16" customHeight="1">
       <x:c r="A48" s="28"/>
-      <x:c r="B48" s="75" t="str">
+      <x:c r="B48" s="107" t="str">
         <x:v>05</x:v>
       </x:c>
-      <x:c r="C48" s="76" t="str">
+      <x:c r="C48" s="108" t="str">
         <x:v>WORK IN PROGRESS</x:v>
       </x:c>
-      <x:c r="D48" s="76"/>
-      <x:c r="E48" s="76"/>
-      <x:c r="F48" s="76"/>
-      <x:c r="G48" s="76"/>
-      <x:c r="H48" s="76"/>
-      <x:c r="I48" s="76"/>
-      <x:c r="J48" s="76"/>
-      <x:c r="K48" s="76"/>
-      <x:c r="L48" s="76"/>
-      <x:c r="M48" s="76"/>
-      <x:c r="N48" s="76"/>
-      <x:c r="O48" s="76"/>
-      <x:c r="P48" s="76"/>
-      <x:c r="Q48" s="76"/>
-      <x:c r="R48" s="76"/>
-      <x:c r="S48" s="76"/>
-      <x:c r="T48" s="76"/>
-      <x:c r="U48" s="76"/>
-      <x:c r="V48" s="76"/>
-      <x:c r="W48" s="77"/>
+      <x:c r="D48" s="108"/>
+      <x:c r="E48" s="108"/>
+      <x:c r="F48" s="108"/>
+      <x:c r="G48" s="108"/>
+      <x:c r="H48" s="108"/>
+      <x:c r="I48" s="108"/>
+      <x:c r="J48" s="108"/>
+      <x:c r="K48" s="108"/>
+      <x:c r="L48" s="108"/>
+      <x:c r="M48" s="108"/>
+      <x:c r="N48" s="108"/>
+      <x:c r="O48" s="108"/>
+      <x:c r="P48" s="108"/>
+      <x:c r="Q48" s="108"/>
+      <x:c r="R48" s="108"/>
+      <x:c r="S48" s="108"/>
+      <x:c r="T48" s="108"/>
+      <x:c r="U48" s="108"/>
+      <x:c r="V48" s="108"/>
+      <x:c r="W48" s="109"/>
       <x:c r="X48" s="28"/>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
       <x:c r="A49" s="28"/>
-      <x:c r="B49" s="78" t="str">
+      <x:c r="B49" s="110" t="str">
         <x:v>  진행 중 신청과 업무기한</x:v>
       </x:c>
-      <x:c r="C49" s="79"/>
-      <x:c r="D49" s="79"/>
-      <x:c r="E49" s="79"/>
-      <x:c r="F49" s="79"/>
-      <x:c r="G49" s="79"/>
-      <x:c r="H49" s="79"/>
-      <x:c r="I49" s="79"/>
-      <x:c r="J49" s="79"/>
-      <x:c r="K49" s="79"/>
-      <x:c r="L49" s="79"/>
-      <x:c r="M49" s="79"/>
-      <x:c r="N49" s="79"/>
-      <x:c r="O49" s="79"/>
-      <x:c r="P49" s="79"/>
-      <x:c r="Q49" s="79"/>
-      <x:c r="R49" s="79"/>
-      <x:c r="S49" s="79"/>
-      <x:c r="T49" s="79"/>
-      <x:c r="U49" s="79"/>
-      <x:c r="V49" s="79"/>
-      <x:c r="W49" s="80"/>
+      <x:c r="C49" s="111"/>
+      <x:c r="D49" s="111"/>
+      <x:c r="E49" s="111"/>
+      <x:c r="F49" s="111"/>
+      <x:c r="G49" s="111"/>
+      <x:c r="H49" s="111"/>
+      <x:c r="I49" s="111"/>
+      <x:c r="J49" s="111"/>
+      <x:c r="K49" s="111"/>
+      <x:c r="L49" s="111"/>
+      <x:c r="M49" s="111"/>
+      <x:c r="N49" s="111"/>
+      <x:c r="O49" s="111"/>
+      <x:c r="P49" s="111"/>
+      <x:c r="Q49" s="111"/>
+      <x:c r="R49" s="111"/>
+      <x:c r="S49" s="111"/>
+      <x:c r="T49" s="111"/>
+      <x:c r="U49" s="111"/>
+      <x:c r="V49" s="111"/>
+      <x:c r="W49" s="112"/>
       <x:c r="X49" s="28"/>
     </x:row>
     <x:row r="50" ht="30" customHeight="1">
@@ -3041,124 +3267,124 @@
     </x:row>
     <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="28"/>
-      <x:c r="B51" s="67"/>
-      <x:c r="C51" s="63"/>
-      <x:c r="D51" s="63"/>
-      <x:c r="E51" s="63"/>
-      <x:c r="F51" s="63"/>
-      <x:c r="G51" s="63"/>
-      <x:c r="H51" s="63"/>
-      <x:c r="I51" s="63"/>
-      <x:c r="J51" s="63"/>
-      <x:c r="K51" s="63"/>
-      <x:c r="L51" s="63"/>
-      <x:c r="M51" s="63"/>
-      <x:c r="N51" s="63"/>
-      <x:c r="O51" s="63"/>
-      <x:c r="P51" s="63"/>
-      <x:c r="Q51" s="63"/>
-      <x:c r="R51" s="63"/>
-      <x:c r="S51" s="63"/>
-      <x:c r="T51" s="63"/>
-      <x:c r="U51" s="63"/>
-      <x:c r="V51" s="63"/>
-      <x:c r="W51" s="68"/>
+      <x:c r="B51" s="43"/>
+      <x:c r="C51" s="28"/>
+      <x:c r="D51" s="28"/>
+      <x:c r="E51" s="28"/>
+      <x:c r="F51" s="28"/>
+      <x:c r="G51" s="28"/>
+      <x:c r="H51" s="28"/>
+      <x:c r="I51" s="28"/>
+      <x:c r="J51" s="28"/>
+      <x:c r="K51" s="28"/>
+      <x:c r="L51" s="28"/>
+      <x:c r="M51" s="28"/>
+      <x:c r="N51" s="28"/>
+      <x:c r="O51" s="28"/>
+      <x:c r="P51" s="28"/>
+      <x:c r="Q51" s="28"/>
+      <x:c r="R51" s="28"/>
+      <x:c r="S51" s="28"/>
+      <x:c r="T51" s="28"/>
+      <x:c r="U51" s="28"/>
+      <x:c r="V51" s="28"/>
+      <x:c r="W51" s="44"/>
       <x:c r="X51" s="28"/>
     </x:row>
     <x:row r="52" ht="20" customHeight="1">
       <x:c r="A52" s="28"/>
-      <x:c r="B52" s="122" t="str">
+      <x:c r="B52" s="157" t="str">
         <x:v>  신청·검토 중</x:v>
       </x:c>
-      <x:c r="C52" s="123"/>
-      <x:c r="D52" s="123"/>
-      <x:c r="E52" s="123"/>
-      <x:c r="F52" s="124"/>
-      <x:c r="G52" s="63"/>
-      <x:c r="H52" s="122" t="str">
+      <x:c r="C52" s="158"/>
+      <x:c r="D52" s="158"/>
+      <x:c r="E52" s="158"/>
+      <x:c r="F52" s="159"/>
+      <x:c r="G52" s="28"/>
+      <x:c r="H52" s="157" t="str">
         <x:v>  보완자료 제출기한</x:v>
       </x:c>
-      <x:c r="I52" s="123"/>
-      <x:c r="J52" s="123"/>
-      <x:c r="K52" s="123"/>
-      <x:c r="L52" s="124"/>
-      <x:c r="M52" s="63"/>
-      <x:c r="N52" s="122" t="str">
+      <x:c r="I52" s="158"/>
+      <x:c r="J52" s="158"/>
+      <x:c r="K52" s="158"/>
+      <x:c r="L52" s="159"/>
+      <x:c r="M52" s="28"/>
+      <x:c r="N52" s="157" t="str">
         <x:v>  심사 소요기간</x:v>
       </x:c>
-      <x:c r="O52" s="123"/>
-      <x:c r="P52" s="123"/>
-      <x:c r="Q52" s="123"/>
-      <x:c r="R52" s="124"/>
-      <x:c r="S52" s="63"/>
-      <x:c r="T52" s="122" t="str">
+      <x:c r="O52" s="158"/>
+      <x:c r="P52" s="158"/>
+      <x:c r="Q52" s="158"/>
+      <x:c r="R52" s="159"/>
+      <x:c r="S52" s="28"/>
+      <x:c r="T52" s="157" t="str">
         <x:v>  승인·반려율</x:v>
       </x:c>
-      <x:c r="U52" s="123"/>
-      <x:c r="V52" s="123"/>
-      <x:c r="W52" s="124"/>
+      <x:c r="U52" s="158"/>
+      <x:c r="V52" s="158"/>
+      <x:c r="W52" s="159"/>
       <x:c r="X52" s="28"/>
     </x:row>
     <x:row r="53" ht="26" customHeight="1">
       <x:c r="A53" s="28"/>
-      <x:c r="B53" s="125" t="str">
+      <x:c r="B53" s="160" t="str">
         <x:v>  공개자료 미확보</x:v>
       </x:c>
-      <x:c r="C53" s="126"/>
-      <x:c r="D53" s="126"/>
-      <x:c r="E53" s="126"/>
-      <x:c r="F53" s="127"/>
-      <x:c r="G53" s="63"/>
-      <x:c r="H53" s="125" t="str">
+      <x:c r="C53" s="161"/>
+      <x:c r="D53" s="161"/>
+      <x:c r="E53" s="161"/>
+      <x:c r="F53" s="162"/>
+      <x:c r="G53" s="28"/>
+      <x:c r="H53" s="160" t="str">
         <x:v>  공개자료 미확보</x:v>
       </x:c>
-      <x:c r="I53" s="126"/>
-      <x:c r="J53" s="126"/>
-      <x:c r="K53" s="126"/>
-      <x:c r="L53" s="127"/>
-      <x:c r="M53" s="63"/>
-      <x:c r="N53" s="125" t="str">
+      <x:c r="I53" s="161"/>
+      <x:c r="J53" s="161"/>
+      <x:c r="K53" s="161"/>
+      <x:c r="L53" s="162"/>
+      <x:c r="M53" s="28"/>
+      <x:c r="N53" s="160" t="str">
         <x:v>  공개자료 미확보</x:v>
       </x:c>
-      <x:c r="O53" s="126"/>
-      <x:c r="P53" s="126"/>
-      <x:c r="Q53" s="126"/>
-      <x:c r="R53" s="127"/>
-      <x:c r="S53" s="63"/>
-      <x:c r="T53" s="125" t="str">
+      <x:c r="O53" s="161"/>
+      <x:c r="P53" s="161"/>
+      <x:c r="Q53" s="161"/>
+      <x:c r="R53" s="162"/>
+      <x:c r="S53" s="28"/>
+      <x:c r="T53" s="160" t="str">
         <x:v>  공개자료 미확보</x:v>
       </x:c>
-      <x:c r="U53" s="126"/>
-      <x:c r="V53" s="126"/>
-      <x:c r="W53" s="127"/>
+      <x:c r="U53" s="161"/>
+      <x:c r="V53" s="161"/>
+      <x:c r="W53" s="162"/>
       <x:c r="X53" s="28"/>
     </x:row>
     <x:row r="54" ht="30" customHeight="1">
       <x:c r="A54" s="28"/>
-      <x:c r="B54" s="94" t="str">
+      <x:c r="B54" s="125" t="str">
         <x:v>  ■ 비공개 신청 원장 제외 · 공개된 승인 방법론으로 신청 건수·승인율·처리속도를 추정하지 않음</x:v>
       </x:c>
-      <x:c r="C54" s="95"/>
-      <x:c r="D54" s="95"/>
-      <x:c r="E54" s="95"/>
-      <x:c r="F54" s="95"/>
-      <x:c r="G54" s="95"/>
-      <x:c r="H54" s="95"/>
-      <x:c r="I54" s="95"/>
-      <x:c r="J54" s="95"/>
-      <x:c r="K54" s="95"/>
-      <x:c r="L54" s="95"/>
-      <x:c r="M54" s="95"/>
-      <x:c r="N54" s="95"/>
-      <x:c r="O54" s="95"/>
-      <x:c r="P54" s="95"/>
-      <x:c r="Q54" s="95"/>
-      <x:c r="R54" s="95"/>
-      <x:c r="S54" s="95"/>
-      <x:c r="T54" s="95"/>
-      <x:c r="U54" s="95"/>
-      <x:c r="V54" s="95"/>
-      <x:c r="W54" s="96"/>
+      <x:c r="C54" s="126"/>
+      <x:c r="D54" s="126"/>
+      <x:c r="E54" s="126"/>
+      <x:c r="F54" s="126"/>
+      <x:c r="G54" s="126"/>
+      <x:c r="H54" s="126"/>
+      <x:c r="I54" s="126"/>
+      <x:c r="J54" s="126"/>
+      <x:c r="K54" s="126"/>
+      <x:c r="L54" s="126"/>
+      <x:c r="M54" s="126"/>
+      <x:c r="N54" s="126"/>
+      <x:c r="O54" s="126"/>
+      <x:c r="P54" s="126"/>
+      <x:c r="Q54" s="126"/>
+      <x:c r="R54" s="126"/>
+      <x:c r="S54" s="126"/>
+      <x:c r="T54" s="126"/>
+      <x:c r="U54" s="126"/>
+      <x:c r="V54" s="126"/>
+      <x:c r="W54" s="127"/>
       <x:c r="X54" s="28"/>
     </x:row>
     <x:row r="55" ht="14" customHeight="1">
@@ -3189,86 +3415,86 @@
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" s="28"/>
-      <x:c r="B56" s="131" t="str">
+      <x:c r="B56" s="168" t="str">
         <x:v>출처 ORS 공개 이력(https://ors.gir.go.kr/home/orme010/activeList.do?menuId=12) · 2026-10-14 확인 · 공개자료만 포함하고 내부 신청·검토 메모·개인정보는 제외 · 유효시작일을 최초등록일로 대체하지 않음 · 산업부문 전수 통계 아님</x:v>
       </x:c>
-      <x:c r="C56" s="131"/>
-      <x:c r="D56" s="131"/>
-      <x:c r="E56" s="131"/>
-      <x:c r="F56" s="131"/>
-      <x:c r="G56" s="131"/>
-      <x:c r="H56" s="131"/>
-      <x:c r="I56" s="131"/>
-      <x:c r="J56" s="131"/>
-      <x:c r="K56" s="131"/>
-      <x:c r="L56" s="131"/>
-      <x:c r="M56" s="131"/>
-      <x:c r="N56" s="131"/>
-      <x:c r="O56" s="131"/>
-      <x:c r="P56" s="131"/>
-      <x:c r="Q56" s="131"/>
-      <x:c r="R56" s="131"/>
-      <x:c r="S56" s="131"/>
-      <x:c r="T56" s="131"/>
-      <x:c r="U56" s="131"/>
-      <x:c r="V56" s="131"/>
-      <x:c r="W56" s="131"/>
+      <x:c r="C56" s="168"/>
+      <x:c r="D56" s="168"/>
+      <x:c r="E56" s="168"/>
+      <x:c r="F56" s="168"/>
+      <x:c r="G56" s="168"/>
+      <x:c r="H56" s="168"/>
+      <x:c r="I56" s="168"/>
+      <x:c r="J56" s="168"/>
+      <x:c r="K56" s="168"/>
+      <x:c r="L56" s="168"/>
+      <x:c r="M56" s="168"/>
+      <x:c r="N56" s="168"/>
+      <x:c r="O56" s="168"/>
+      <x:c r="P56" s="168"/>
+      <x:c r="Q56" s="168"/>
+      <x:c r="R56" s="168"/>
+      <x:c r="S56" s="168"/>
+      <x:c r="T56" s="168"/>
+      <x:c r="U56" s="168"/>
+      <x:c r="V56" s="168"/>
+      <x:c r="W56" s="168"/>
       <x:c r="X56" s="28"/>
     </x:row>
     <x:row r="57" ht="18" customHeight="1">
       <x:c r="A57" s="28"/>
-      <x:c r="B57" s="132" t="str">
+      <x:c r="B57" s="169" t="str">
         <x:v>분석조건 → 통계 → 방법론 / 버전 시트에서 같은 수치와 공개 출처를 확인하세요.</x:v>
       </x:c>
-      <x:c r="C57" s="132"/>
-      <x:c r="D57" s="132"/>
-      <x:c r="E57" s="132"/>
-      <x:c r="F57" s="132"/>
-      <x:c r="G57" s="132"/>
-      <x:c r="H57" s="132"/>
-      <x:c r="I57" s="132"/>
-      <x:c r="J57" s="132"/>
-      <x:c r="K57" s="132"/>
-      <x:c r="L57" s="132"/>
-      <x:c r="M57" s="132"/>
-      <x:c r="N57" s="132"/>
-      <x:c r="O57" s="132"/>
-      <x:c r="P57" s="132"/>
-      <x:c r="Q57" s="132"/>
-      <x:c r="R57" s="132"/>
-      <x:c r="S57" s="132"/>
-      <x:c r="T57" s="132"/>
-      <x:c r="U57" s="132"/>
-      <x:c r="V57" s="132"/>
-      <x:c r="W57" s="132"/>
+      <x:c r="C57" s="169"/>
+      <x:c r="D57" s="169"/>
+      <x:c r="E57" s="169"/>
+      <x:c r="F57" s="169"/>
+      <x:c r="G57" s="169"/>
+      <x:c r="H57" s="169"/>
+      <x:c r="I57" s="169"/>
+      <x:c r="J57" s="169"/>
+      <x:c r="K57" s="169"/>
+      <x:c r="L57" s="169"/>
+      <x:c r="M57" s="169"/>
+      <x:c r="N57" s="169"/>
+      <x:c r="O57" s="169"/>
+      <x:c r="P57" s="169"/>
+      <x:c r="Q57" s="169"/>
+      <x:c r="R57" s="169"/>
+      <x:c r="S57" s="169"/>
+      <x:c r="T57" s="169"/>
+      <x:c r="U57" s="169"/>
+      <x:c r="V57" s="169"/>
+      <x:c r="W57" s="169"/>
       <x:c r="X57" s="28"/>
     </x:row>
     <x:row r="58" ht="16" customHeight="1">
       <x:c r="A58" s="28"/>
-      <x:c r="B58" s="133" t="str">
-        <x:v>디자인: 이너젠 블루(이너젠·이너캐리 통합 디자인 기준 v17·v22) · 노란 칸은 입력, 회색 열은 계산 · 웹에서 바꾼 조건은 이 파일에 자동 반영되지 않음</x:v>
-      </x:c>
-      <x:c r="C58" s="133"/>
-      <x:c r="D58" s="133"/>
-      <x:c r="E58" s="133"/>
-      <x:c r="F58" s="133"/>
-      <x:c r="G58" s="133"/>
-      <x:c r="H58" s="133"/>
-      <x:c r="I58" s="133"/>
-      <x:c r="J58" s="133"/>
-      <x:c r="K58" s="133"/>
-      <x:c r="L58" s="133"/>
-      <x:c r="M58" s="133"/>
-      <x:c r="N58" s="133"/>
-      <x:c r="O58" s="133"/>
-      <x:c r="P58" s="133"/>
-      <x:c r="Q58" s="133"/>
-      <x:c r="R58" s="133"/>
-      <x:c r="S58" s="133"/>
-      <x:c r="T58" s="133"/>
-      <x:c r="U58" s="133"/>
-      <x:c r="V58" s="133"/>
-      <x:c r="W58" s="133"/>
+      <x:c r="B58" s="135" t="str">
+        <x:v>디자인: 정부 KRDS 참고형(정부24 계열 색·표 규칙) · 정부·공단 로고와 공식 누리집 문구 미사용 · 노란 칸은 입력, 회색 열은 계산 · 웹에서 바꾼 조건은 이 파일에 자동 반영되지 않음</x:v>
+      </x:c>
+      <x:c r="C58" s="135"/>
+      <x:c r="D58" s="135"/>
+      <x:c r="E58" s="135"/>
+      <x:c r="F58" s="135"/>
+      <x:c r="G58" s="135"/>
+      <x:c r="H58" s="135"/>
+      <x:c r="I58" s="135"/>
+      <x:c r="J58" s="135"/>
+      <x:c r="K58" s="135"/>
+      <x:c r="L58" s="135"/>
+      <x:c r="M58" s="135"/>
+      <x:c r="N58" s="135"/>
+      <x:c r="O58" s="135"/>
+      <x:c r="P58" s="135"/>
+      <x:c r="Q58" s="135"/>
+      <x:c r="R58" s="135"/>
+      <x:c r="S58" s="135"/>
+      <x:c r="T58" s="135"/>
+      <x:c r="U58" s="135"/>
+      <x:c r="V58" s="135"/>
+      <x:c r="W58" s="135"/>
       <x:c r="X58" s="28"/>
     </x:row>
     <x:row r="59" ht="20" customHeight="1">
@@ -3406,14 +3632,14 @@
     <x:mergeCell ref="B58:W58"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c92552fbd14618"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5cb092905e84b9a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF7B9BF7"/>
+    <x:tabColor rgb="FF246BEB"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3428,7 +3654,7 @@
     <x:col min="10" max="10" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="3" customHeight="1">
+    <x:row r="1" ht="4.5" customHeight="1">
       <x:c r="A1" s="3"/>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3877,7 +4103,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF7B9BF7"/>
+    <x:tabColor rgb="FF246BEB"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3902,7 +4128,7 @@
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="3" customHeight="1">
+    <x:row r="1" ht="4.5" customHeight="1">
       <x:c r="A1" s="3"/>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -4012,42 +4238,42 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="15" t="str">
         <x:v>지표</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>값</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
-      <x:c r="D6" s="14" t="str">
+      <x:c r="D6" s="15" t="str">
         <x:v>유효시작 연도</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str">
+      <x:c r="E6" s="15" t="str">
         <x:v>최초 버전</x:v>
       </x:c>
-      <x:c r="F6" s="14" t="str">
+      <x:c r="F6" s="15" t="str">
         <x:v>개정 버전</x:v>
       </x:c>
-      <x:c r="G6" s="14" t="str">
+      <x:c r="G6" s="15" t="str">
         <x:v>누적 방법론</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="str">
+      <x:c r="H6" s="15" t="str">
         <x:v>연간 버전</x:v>
       </x:c>
-      <x:c r="I6" s="14" t="str">
+      <x:c r="I6" s="15" t="str">
         <x:v>분야 원문</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="str">
+      <x:c r="J6" s="15" t="str">
         <x:v>방법론</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="str">
+      <x:c r="K6" s="15" t="str">
         <x:v>비중</x:v>
       </x:c>
       <x:c r="L6" s="2"/>
-      <x:c r="M6" s="14" t="str">
+      <x:c r="M6" s="15" t="str">
         <x:v>최신 버전 경과</x:v>
       </x:c>
-      <x:c r="N6" s="14" t="str">
+      <x:c r="N6" s="15" t="str">
         <x:v>방법론</x:v>
       </x:c>
       <x:c r="O6" s="2"/>
@@ -4351,10 +4577,10 @@
         <x:v>0.18181818181818182</x:v>
       </x:c>
       <x:c r="L12" s="2"/>
-      <x:c r="M12" s="14" t="str">
+      <x:c r="M12" s="15" t="str">
         <x:v>최신 버전</x:v>
       </x:c>
-      <x:c r="N12" s="14" t="str">
+      <x:c r="N12" s="15" t="str">
         <x:v>방법론</x:v>
       </x:c>
       <x:c r="O12" s="2"/>
@@ -4618,10 +4844,10 @@
       <x:c r="J18" s="2"/>
       <x:c r="K18" s="2"/>
       <x:c r="L18" s="2"/>
-      <x:c r="M18" s="14" t="str">
+      <x:c r="M18" s="15" t="str">
         <x:v>등록형태</x:v>
       </x:c>
-      <x:c r="N18" s="14" t="str">
+      <x:c r="N18" s="15" t="str">
         <x:v>방법론</x:v>
       </x:c>
       <x:c r="O18" s="2"/>
@@ -5062,7 +5288,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF7B9BF7"/>
+    <x:tabColor rgb="FF246BEB"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5081,7 +5307,7 @@
     <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="3" customHeight="1">
+    <x:row r="1" ht="4.5" customHeight="1">
       <x:c r="A1" s="3"/>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -5162,46 +5388,46 @@
       <x:c r="M5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="15" t="str">
         <x:v>코드</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>방법론명</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="str">
+      <x:c r="C6" s="15" t="str">
         <x:v>분야 원문</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
+      <x:c r="D6" s="15" t="str">
         <x:v>등록형태</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str">
+      <x:c r="E6" s="15" t="str">
         <x:v>공개 출처</x:v>
       </x:c>
-      <x:c r="F6" s="14" t="str">
+      <x:c r="F6" s="15" t="str">
         <x:v>최신 유효시작일</x:v>
       </x:c>
-      <x:c r="G6" s="14" t="str">
+      <x:c r="G6" s="15" t="str">
         <x:v>최신 버전</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="str">
+      <x:c r="H6" s="15" t="str">
         <x:v>최초 버전 유효시작일</x:v>
       </x:c>
-      <x:c r="I6" s="14" t="str">
+      <x:c r="I6" s="15" t="str">
         <x:v>개정 이력 수</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="str">
+      <x:c r="J6" s="15" t="str">
         <x:v>확인 버전 수</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="str">
+      <x:c r="K6" s="15" t="str">
         <x:v>최신 버전 경과일</x:v>
       </x:c>
-      <x:c r="L6" s="14" t="str">
+      <x:c r="L6" s="15" t="str">
         <x:v>포함</x:v>
       </x:c>
-      <x:c r="M6" s="14" t="str">
+      <x:c r="M6" s="15" t="str">
         <x:v>장기 관찰</x:v>
       </x:c>
-      <x:c r="N6" s="24" t="str">
+      <x:c r="N6" s="25" t="str">
         <x:v>분석 대상 경과일</x:v>
       </x:c>
     </x:row>
@@ -5209,16 +5435,16 @@
       <x:c r="A7" s="2" t="str">
         <x:v>01A-001</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str">
+      <x:c r="B7" s="16" t="str">
         <x:v>목재펠릿을 활용한 연료전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C7" s="15" t="str">
+      <x:c r="C7" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E7" s="15" t="str">
+      <x:c r="E7" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=15&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F7" s="17" t="n">
@@ -5233,23 +5459,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A7,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A7,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I7" s="16" t="n">
+      <x:c r="I7" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A7,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J7" s="16" t="n">
+      <x:c r="J7" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A7,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K7" s="16" t="n">
+      <x:c r="K7" s="11" t="n">
         <x:f>IF(J7=0,"",'분석조건'!$B$5-F7)</x:f>
         <x:v>4194</x:v>
       </x:c>
-      <x:c r="L7" s="16" t="n">
+      <x:c r="L7" s="11" t="n">
         <x:f>IF(AND(J7&gt;0,OR('분석조건'!$B$7="all",C7='분석조건'!$B$7),OR('분석조건'!$B$8="all",D7='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I7&gt;0),AND('분석조건'!$B$9="unrevised",I7=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A7&amp;" "&amp;B7&amp;" "&amp;C7))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M7" s="16" t="n">
+      <x:c r="M7" s="11" t="n">
         <x:f>IF(AND(L7=1,K7&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5262,16 +5488,16 @@
       <x:c r="A8" s="2" t="str">
         <x:v>01A-006</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str">
+      <x:c r="B8" s="16" t="str">
         <x:v>가축분뇨 고체연료를 활용한 열/전력 생산 및 이용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="str">
+      <x:c r="C8" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D8" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="str">
+      <x:c r="E8" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=469&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F8" s="17" t="n">
@@ -5286,23 +5512,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A8,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A8,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="I8" s="16" t="n">
+      <x:c r="I8" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A8,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
+      <x:c r="J8" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A8,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="11" t="n">
         <x:f>IF(J8=0,"",'분석조건'!$B$5-F8)</x:f>
         <x:v>407</x:v>
       </x:c>
-      <x:c r="L8" s="16" t="n">
+      <x:c r="L8" s="11" t="n">
         <x:f>IF(AND(J8&gt;0,OR('분석조건'!$B$7="all",C8='분석조건'!$B$7),OR('분석조건'!$B$8="all",D8='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I8&gt;0),AND('분석조건'!$B$9="unrevised",I8=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A8&amp;" "&amp;B8&amp;" "&amp;C8))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M8" s="16" t="n">
+      <x:c r="M8" s="11" t="n">
         <x:f>IF(AND(L8=1,K8&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5315,16 +5541,16 @@
       <x:c r="A9" s="2" t="str">
         <x:v>01B-001</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="str">
+      <x:c r="B9" s="16" t="str">
         <x:v>재생에너지를 이용한 전력 생산 및 계통 연계 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="str">
+      <x:c r="C9" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="str">
+      <x:c r="E9" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=18&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F9" s="17" t="n">
@@ -5339,23 +5565,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A9,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A9,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I9" s="16" t="n">
+      <x:c r="I9" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A9,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A9,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K9" s="11" t="n">
         <x:f>IF(J9=0,"",'분석조건'!$B$5-F9)</x:f>
         <x:v>4194</x:v>
       </x:c>
-      <x:c r="L9" s="16" t="n">
+      <x:c r="L9" s="11" t="n">
         <x:f>IF(AND(J9&gt;0,OR('분석조건'!$B$7="all",C9='분석조건'!$B$7),OR('분석조건'!$B$8="all",D9='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I9&gt;0),AND('분석조건'!$B$9="unrevised",I9=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A9&amp;" "&amp;B9&amp;" "&amp;C9))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M9" s="16" t="n">
+      <x:c r="M9" s="11" t="n">
         <x:f>IF(AND(L9=1,K9&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5368,16 +5594,16 @@
       <x:c r="A10" s="2" t="str">
         <x:v>01B-003</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="str">
+      <x:c r="B10" s="16" t="str">
         <x:v>태양열에너지를 이용한 열에너지 생산 및 이용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="str">
+      <x:c r="C10" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D10" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="str">
+      <x:c r="E10" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=20&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F10" s="17" t="n">
@@ -5392,23 +5618,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A10,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A10,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I10" s="16" t="n">
+      <x:c r="I10" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A10,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A10,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" s="16" t="n">
+      <x:c r="K10" s="11" t="n">
         <x:f>IF(J10=0,"",'분석조건'!$B$5-F10)</x:f>
         <x:v>4194</x:v>
       </x:c>
-      <x:c r="L10" s="16" t="n">
+      <x:c r="L10" s="11" t="n">
         <x:f>IF(AND(J10&gt;0,OR('분석조건'!$B$7="all",C10='분석조건'!$B$7),OR('분석조건'!$B$8="all",D10='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I10&gt;0),AND('분석조건'!$B$9="unrevised",I10=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A10&amp;" "&amp;B10&amp;" "&amp;C10))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="n">
+      <x:c r="M10" s="11" t="n">
         <x:f>IF(AND(L10=1,K10&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5421,16 +5647,16 @@
       <x:c r="A11" s="2" t="str">
         <x:v>01B-004</x:v>
       </x:c>
-      <x:c r="B11" s="15" t="str">
+      <x:c r="B11" s="16" t="str">
         <x:v>재생에너지를 이용한 전력 생산 및 자가 사용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="C11" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D11" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=44&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F11" s="17" t="n">
@@ -5445,23 +5671,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A11,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A11,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42516</x:v>
       </x:c>
-      <x:c r="I11" s="16" t="n">
+      <x:c r="I11" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A11,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A11,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K11" s="16" t="n">
+      <x:c r="K11" s="11" t="n">
         <x:f>IF(J11=0,"",'분석조건'!$B$5-F11)</x:f>
         <x:v>3793</x:v>
       </x:c>
-      <x:c r="L11" s="16" t="n">
+      <x:c r="L11" s="11" t="n">
         <x:f>IF(AND(J11&gt;0,OR('분석조건'!$B$7="all",C11='분석조건'!$B$7),OR('분석조건'!$B$8="all",D11='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I11&gt;0),AND('분석조건'!$B$9="unrevised",I11=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A11&amp;" "&amp;B11&amp;" "&amp;C11))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="n">
+      <x:c r="M11" s="11" t="n">
         <x:f>IF(AND(L11=1,K11&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5474,16 +5700,16 @@
       <x:c r="A12" s="2" t="str">
         <x:v>01B-008</x:v>
       </x:c>
-      <x:c r="B12" s="15" t="str">
+      <x:c r="B12" s="16" t="str">
         <x:v>전력 자가사용 및 독립된 소규모 계통 연계를 위한 재생에너지 발전사업의 방법론</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="C12" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D12" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=353&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F12" s="17" t="n">
@@ -5498,23 +5724,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A12,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A12,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>43987</x:v>
       </x:c>
-      <x:c r="I12" s="16" t="n">
+      <x:c r="I12" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A12,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A12,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" s="16" t="n">
+      <x:c r="K12" s="11" t="n">
         <x:f>IF(J12=0,"",'분석조건'!$B$5-F12)</x:f>
         <x:v>2322</x:v>
       </x:c>
-      <x:c r="L12" s="16" t="n">
+      <x:c r="L12" s="11" t="n">
         <x:f>IF(AND(J12&gt;0,OR('분석조건'!$B$7="all",C12='분석조건'!$B$7),OR('분석조건'!$B$8="all",D12='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I12&gt;0),AND('분석조건'!$B$9="unrevised",I12=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A12&amp;" "&amp;B12&amp;" "&amp;C12))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="n">
+      <x:c r="M12" s="11" t="n">
         <x:f>IF(AND(L12=1,K12&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5527,16 +5753,16 @@
       <x:c r="A13" s="2" t="str">
         <x:v>01B-009</x:v>
       </x:c>
-      <x:c r="B13" s="15" t="str">
+      <x:c r="B13" s="16" t="str">
         <x:v>수소 연료전지를 이용한 전기 및 열생산 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="C13" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E13" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=532&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F13" s="17" t="n">
@@ -5551,23 +5777,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A13,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A13,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44834</x:v>
       </x:c>
-      <x:c r="I13" s="16" t="n">
+      <x:c r="I13" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A13,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A13,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K13" s="16" t="n">
+      <x:c r="K13" s="11" t="n">
         <x:f>IF(J13=0,"",'분석조건'!$B$5-F13)</x:f>
         <x:v>316</x:v>
       </x:c>
-      <x:c r="L13" s="16" t="n">
+      <x:c r="L13" s="11" t="n">
         <x:f>IF(AND(J13&gt;0,OR('분석조건'!$B$7="all",C13='분석조건'!$B$7),OR('분석조건'!$B$8="all",D13='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I13&gt;0),AND('분석조건'!$B$9="unrevised",I13=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A13&amp;" "&amp;B13&amp;" "&amp;C13))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="n">
+      <x:c r="M13" s="11" t="n">
         <x:f>IF(AND(L13=1,K13&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5580,16 +5806,16 @@
       <x:c r="A14" s="2" t="str">
         <x:v>01B-011</x:v>
       </x:c>
-      <x:c r="B14" s="15" t="str">
+      <x:c r="B14" s="16" t="str">
         <x:v>재생에너지를 통해 생산한 전력을 자가 사용 및/또는 계통 연계하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="C14" s="16" t="str">
         <x:v>에너지산업</x:v>
       </x:c>
       <x:c r="D14" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="E14" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=537&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F14" s="17" t="n">
@@ -5604,23 +5830,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A14,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A14,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45538</x:v>
       </x:c>
-      <x:c r="I14" s="16" t="n">
+      <x:c r="I14" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A14,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A14,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K14" s="16" t="n">
+      <x:c r="K14" s="11" t="n">
         <x:f>IF(J14=0,"",'분석조건'!$B$5-F14)</x:f>
         <x:v>42</x:v>
       </x:c>
-      <x:c r="L14" s="16" t="n">
+      <x:c r="L14" s="11" t="n">
         <x:f>IF(AND(J14&gt;0,OR('분석조건'!$B$7="all",C14='분석조건'!$B$7),OR('분석조건'!$B$8="all",D14='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I14&gt;0),AND('분석조건'!$B$9="unrevised",I14=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A14&amp;" "&amp;B14&amp;" "&amp;C14))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="n">
+      <x:c r="M14" s="11" t="n">
         <x:f>IF(AND(L14=1,K14&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5633,16 +5859,16 @@
       <x:c r="A15" s="2" t="str">
         <x:v>02A-001</x:v>
       </x:c>
-      <x:c r="B15" s="15" t="str">
+      <x:c r="B15" s="16" t="str">
         <x:v>자가발전을 통한 사업장 전력 대체 온실가스 감축 방법론</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="str">
+      <x:c r="C15" s="16" t="str">
         <x:v>에너지 공급</x:v>
       </x:c>
       <x:c r="D15" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=406&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F15" s="17" t="n">
@@ -5657,23 +5883,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A15,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A15,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45538</x:v>
       </x:c>
-      <x:c r="I15" s="16" t="n">
+      <x:c r="I15" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A15,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A15,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="16" t="n">
+      <x:c r="K15" s="11" t="n">
         <x:f>IF(J15=0,"",'분석조건'!$B$5-F15)</x:f>
         <x:v>771</x:v>
       </x:c>
-      <x:c r="L15" s="16" t="n">
+      <x:c r="L15" s="11" t="n">
         <x:f>IF(AND(J15&gt;0,OR('분석조건'!$B$7="all",C15='분석조건'!$B$7),OR('분석조건'!$B$8="all",D15='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I15&gt;0),AND('분석조건'!$B$9="unrevised",I15=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A15&amp;" "&amp;B15&amp;" "&amp;C15))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M15" s="16" t="n">
+      <x:c r="M15" s="11" t="n">
         <x:f>IF(AND(L15=1,K15&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5686,16 +5912,16 @@
       <x:c r="A16" s="2" t="str">
         <x:v>02B-001</x:v>
       </x:c>
-      <x:c r="B16" s="15" t="str">
+      <x:c r="B16" s="16" t="str">
         <x:v>열공급시설에서 목질계 바이오매스 연료를 이용하여 생산된 열에너지 공급을 통한 수용가의 화석연료 사용량 절감사업의 방법론</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
+      <x:c r="C16" s="16" t="str">
         <x:v>에너지 공급</x:v>
       </x:c>
       <x:c r="D16" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=332&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F16" s="17" t="n">
@@ -5710,23 +5936,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A16,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A16,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42810</x:v>
       </x:c>
-      <x:c r="I16" s="16" t="n">
+      <x:c r="I16" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A16,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
+      <x:c r="J16" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A16,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K16" s="16" t="n">
+      <x:c r="K16" s="11" t="n">
         <x:f>IF(J16=0,"",'분석조건'!$B$5-F16)</x:f>
         <x:v>2057</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="n">
+      <x:c r="L16" s="11" t="n">
         <x:f>IF(AND(J16&gt;0,OR('분석조건'!$B$7="all",C16='분석조건'!$B$7),OR('분석조건'!$B$8="all",D16='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I16&gt;0),AND('분석조건'!$B$9="unrevised",I16=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A16&amp;" "&amp;B16&amp;" "&amp;C16))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M16" s="16" t="n">
+      <x:c r="M16" s="11" t="n">
         <x:f>IF(AND(L16=1,K16&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5739,16 +5965,16 @@
       <x:c r="A17" s="2" t="str">
         <x:v>02B-002</x:v>
       </x:c>
-      <x:c r="B17" s="15" t="str">
+      <x:c r="B17" s="16" t="str">
         <x:v>섬유염색공정에서 증기 전용 텐터기 도입과 텐터기 전용 열 공급을 통한 수용가의 화석연료 사용량 절감사업의 방법론</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="str">
+      <x:c r="C17" s="16" t="str">
         <x:v>에너지 공급</x:v>
       </x:c>
       <x:c r="D17" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=438&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
@@ -5763,23 +5989,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A17,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A17,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="I17" s="16" t="n">
+      <x:c r="I17" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A17,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="n">
+      <x:c r="J17" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A17,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K17" s="16" t="n">
+      <x:c r="K17" s="11" t="n">
         <x:f>IF(J17=0,"",'분석조건'!$B$5-F17)</x:f>
         <x:v>407</x:v>
       </x:c>
-      <x:c r="L17" s="16" t="n">
+      <x:c r="L17" s="11" t="n">
         <x:f>IF(AND(J17&gt;0,OR('분석조건'!$B$7="all",C17='분석조건'!$B$7),OR('분석조건'!$B$8="all",D17='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I17&gt;0),AND('분석조건'!$B$9="unrevised",I17=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A17&amp;" "&amp;B17&amp;" "&amp;C17))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M17" s="16" t="n">
+      <x:c r="M17" s="11" t="n">
         <x:f>IF(AND(L17=1,K17&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5792,16 +6018,16 @@
       <x:c r="A18" s="2" t="str">
         <x:v>03A-001</x:v>
       </x:c>
-      <x:c r="B18" s="15" t="str">
+      <x:c r="B18" s="16" t="str">
         <x:v>미활용 열에너지 회수 및 이용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="str">
+      <x:c r="C18" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D18" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=40&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F18" s="17" t="n">
@@ -5816,23 +6042,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A18,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A18,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42405</x:v>
       </x:c>
-      <x:c r="I18" s="16" t="n">
+      <x:c r="I18" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A18,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
+      <x:c r="J18" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A18,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K18" s="16" t="n">
+      <x:c r="K18" s="11" t="n">
         <x:f>IF(J18=0,"",'분석조건'!$B$5-F18)</x:f>
         <x:v>3904</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="n">
+      <x:c r="L18" s="11" t="n">
         <x:f>IF(AND(J18&gt;0,OR('분석조건'!$B$7="all",C18='분석조건'!$B$7),OR('분석조건'!$B$8="all",D18='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I18&gt;0),AND('분석조건'!$B$9="unrevised",I18=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A18&amp;" "&amp;B18&amp;" "&amp;C18))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M18" s="16" t="n">
+      <x:c r="M18" s="11" t="n">
         <x:f>IF(AND(L18=1,K18&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5845,16 +6071,16 @@
       <x:c r="A19" s="2" t="str">
         <x:v>03A-002</x:v>
       </x:c>
-      <x:c r="B19" s="15" t="str">
+      <x:c r="B19" s="16" t="str">
         <x:v>연료 전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="str">
+      <x:c r="C19" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D19" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=466&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
@@ -5869,23 +6095,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A19,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A19,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I19" s="16" t="n">
+      <x:c r="I19" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A19,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="n">
+      <x:c r="J19" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A19,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K19" s="16" t="n">
+      <x:c r="K19" s="11" t="n">
         <x:f>IF(J19=0,"",'분석조건'!$B$5-F19)</x:f>
         <x:v>862</x:v>
       </x:c>
-      <x:c r="L19" s="16" t="n">
+      <x:c r="L19" s="11" t="n">
         <x:f>IF(AND(J19&gt;0,OR('분석조건'!$B$7="all",C19='분석조건'!$B$7),OR('분석조건'!$B$8="all",D19='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I19&gt;0),AND('분석조건'!$B$9="unrevised",I19=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A19&amp;" "&amp;B19&amp;" "&amp;C19))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M19" s="16" t="n">
+      <x:c r="M19" s="11" t="n">
         <x:f>IF(AND(L19=1,K19&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5898,16 +6124,16 @@
       <x:c r="A20" s="2" t="str">
         <x:v>03A-003</x:v>
       </x:c>
-      <x:c r="B20" s="15" t="str">
+      <x:c r="B20" s="16" t="str">
         <x:v>전력절감설비 설치사업의 방법론</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="C20" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="E20" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=22&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F20" s="17" t="n">
@@ -5922,23 +6148,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A20,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A20,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I20" s="16" t="n">
+      <x:c r="I20" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A20,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="n">
+      <x:c r="J20" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A20,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K20" s="16" t="n">
+      <x:c r="K20" s="11" t="n">
         <x:f>IF(J20=0,"",'분석조건'!$B$5-F20)</x:f>
         <x:v>4194</x:v>
       </x:c>
-      <x:c r="L20" s="16" t="n">
+      <x:c r="L20" s="11" t="n">
         <x:f>IF(AND(J20&gt;0,OR('분석조건'!$B$7="all",C20='분석조건'!$B$7),OR('분석조건'!$B$8="all",D20='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I20&gt;0),AND('분석조건'!$B$9="unrevised",I20=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A20&amp;" "&amp;B20&amp;" "&amp;C20))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M20" s="16" t="n">
+      <x:c r="M20" s="11" t="n">
         <x:f>IF(AND(L20=1,K20&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -5951,16 +6177,16 @@
       <x:c r="A21" s="2" t="str">
         <x:v>03A-004</x:v>
       </x:c>
-      <x:c r="B21" s="15" t="str">
+      <x:c r="B21" s="16" t="str">
         <x:v>고효율 설비 교체 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="str">
+      <x:c r="C21" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D21" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str">
+      <x:c r="E21" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=23&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
@@ -5975,23 +6201,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A21,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A21,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I21" s="16" t="n">
+      <x:c r="I21" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A21,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="n">
+      <x:c r="J21" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A21,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K21" s="16" t="n">
+      <x:c r="K21" s="11" t="n">
         <x:f>IF(J21=0,"",'분석조건'!$B$5-F21)</x:f>
         <x:v>4194</x:v>
       </x:c>
-      <x:c r="L21" s="16" t="n">
+      <x:c r="L21" s="11" t="n">
         <x:f>IF(AND(J21&gt;0,OR('분석조건'!$B$7="all",C21='분석조건'!$B$7),OR('분석조건'!$B$8="all",D21='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I21&gt;0),AND('분석조건'!$B$9="unrevised",I21=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A21&amp;" "&amp;B21&amp;" "&amp;C21))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M21" s="16" t="n">
+      <x:c r="M21" s="11" t="n">
         <x:f>IF(AND(L21=1,K21&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6004,16 +6230,16 @@
       <x:c r="A22" s="2" t="str">
         <x:v>03A-006</x:v>
       </x:c>
-      <x:c r="B22" s="15" t="str">
+      <x:c r="B22" s="16" t="str">
         <x:v>고효율 도로조명 설치 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="C22" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D22" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=25&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F22" s="17" t="n">
@@ -6028,23 +6254,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A22,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A22,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="I22" s="16" t="n">
+      <x:c r="I22" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A22,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="n">
+      <x:c r="J22" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A22,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K22" s="16" t="n">
+      <x:c r="K22" s="11" t="n">
         <x:f>IF(J22=0,"",'분석조건'!$B$5-F22)</x:f>
         <x:v>4194</x:v>
       </x:c>
-      <x:c r="L22" s="16" t="n">
+      <x:c r="L22" s="11" t="n">
         <x:f>IF(AND(J22&gt;0,OR('분석조건'!$B$7="all",C22='분석조건'!$B$7),OR('분석조건'!$B$8="all",D22='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I22&gt;0),AND('분석조건'!$B$9="unrevised",I22=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A22&amp;" "&amp;B22&amp;" "&amp;C22))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M22" s="16" t="n">
+      <x:c r="M22" s="11" t="n">
         <x:f>IF(AND(L22=1,K22&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6057,16 +6283,16 @@
       <x:c r="A23" s="2" t="str">
         <x:v>03A-008</x:v>
       </x:c>
-      <x:c r="B23" s="15" t="str">
+      <x:c r="B23" s="16" t="str">
         <x:v>미활용 열에너지 회수를 통한 전력생산 및 계통연게 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="str">
+      <x:c r="C23" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D23" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str">
+      <x:c r="E23" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=42&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F23" s="17" t="n">
@@ -6081,23 +6307,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A23,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A23,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>42405</x:v>
       </x:c>
-      <x:c r="I23" s="16" t="n">
+      <x:c r="I23" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A23,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="n">
+      <x:c r="J23" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A23,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K23" s="16" t="n">
+      <x:c r="K23" s="11" t="n">
         <x:f>IF(J23=0,"",'분석조건'!$B$5-F23)</x:f>
         <x:v>3904</x:v>
       </x:c>
-      <x:c r="L23" s="16" t="n">
+      <x:c r="L23" s="11" t="n">
         <x:f>IF(AND(J23&gt;0,OR('분석조건'!$B$7="all",C23='분석조건'!$B$7),OR('분석조건'!$B$8="all",D23='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I23&gt;0),AND('분석조건'!$B$9="unrevised",I23=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A23&amp;" "&amp;B23&amp;" "&amp;C23))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M23" s="16" t="n">
+      <x:c r="M23" s="11" t="n">
         <x:f>IF(AND(L23=1,K23&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6110,16 +6336,16 @@
       <x:c r="A24" s="2" t="str">
         <x:v>03A-013</x:v>
       </x:c>
-      <x:c r="B24" s="15" t="str">
+      <x:c r="B24" s="16" t="str">
         <x:v>주거용 시설의 심야 전기보일러에서 축열식 히트펌프 보일러로 교체 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="C24" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D24" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str">
+      <x:c r="E24" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=50&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F24" s="17" t="n">
@@ -6134,23 +6360,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A24,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A24,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>43081</x:v>
       </x:c>
-      <x:c r="I24" s="16" t="n">
+      <x:c r="I24" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A24,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="n">
+      <x:c r="J24" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A24,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K24" s="16" t="n">
+      <x:c r="K24" s="11" t="n">
         <x:f>IF(J24=0,"",'분석조건'!$B$5-F24)</x:f>
         <x:v>3228</x:v>
       </x:c>
-      <x:c r="L24" s="16" t="n">
+      <x:c r="L24" s="11" t="n">
         <x:f>IF(AND(J24&gt;0,OR('분석조건'!$B$7="all",C24='분석조건'!$B$7),OR('분석조건'!$B$8="all",D24='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I24&gt;0),AND('분석조건'!$B$9="unrevised",I24=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A24&amp;" "&amp;B24&amp;" "&amp;C24))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M24" s="16" t="n">
+      <x:c r="M24" s="11" t="n">
         <x:f>IF(AND(L24=1,K24&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6163,16 +6389,16 @@
       <x:c r="A25" s="2" t="str">
         <x:v>03A-016</x:v>
       </x:c>
-      <x:c r="B25" s="15" t="str">
+      <x:c r="B25" s="16" t="str">
         <x:v>LPG집단공급시설 설치를 통한 연료 전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="str">
+      <x:c r="C25" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D25" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str">
+      <x:c r="E25" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=337&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F25" s="17" t="n">
@@ -6187,23 +6413,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A25,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A25,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>43886</x:v>
       </x:c>
-      <x:c r="I25" s="16" t="n">
+      <x:c r="I25" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A25,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="n">
+      <x:c r="J25" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A25,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K25" s="16" t="n">
+      <x:c r="K25" s="11" t="n">
         <x:f>IF(J25=0,"",'분석조건'!$B$5-F25)</x:f>
         <x:v>2423</x:v>
       </x:c>
-      <x:c r="L25" s="16" t="n">
+      <x:c r="L25" s="11" t="n">
         <x:f>IF(AND(J25&gt;0,OR('분석조건'!$B$7="all",C25='분석조건'!$B$7),OR('분석조건'!$B$8="all",D25='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I25&gt;0),AND('분석조건'!$B$9="unrevised",I25=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A25&amp;" "&amp;B25&amp;" "&amp;C25))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M25" s="16" t="n">
+      <x:c r="M25" s="11" t="n">
         <x:f>IF(AND(L25=1,K25&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6216,16 +6442,16 @@
       <x:c r="A26" s="2" t="str">
         <x:v>03A-018</x:v>
       </x:c>
-      <x:c r="B26" s="15" t="str">
+      <x:c r="B26" s="16" t="str">
         <x:v>Single RAN 설비를 도입하여 legacy 전기통신설비를 대체하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="str">
+      <x:c r="C26" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D26" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str">
+      <x:c r="E26" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=333&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F26" s="17" t="n">
@@ -6240,23 +6466,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A26,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A26,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44120</x:v>
       </x:c>
-      <x:c r="I26" s="16" t="n">
+      <x:c r="I26" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A26,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="n">
+      <x:c r="J26" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A26,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K26" s="16" t="n">
+      <x:c r="K26" s="11" t="n">
         <x:f>IF(J26=0,"",'분석조건'!$B$5-F26)</x:f>
         <x:v>2189</x:v>
       </x:c>
-      <x:c r="L26" s="16" t="n">
+      <x:c r="L26" s="11" t="n">
         <x:f>IF(AND(J26&gt;0,OR('분석조건'!$B$7="all",C26='분석조건'!$B$7),OR('분석조건'!$B$8="all",D26='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I26&gt;0),AND('분석조건'!$B$9="unrevised",I26=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A26&amp;" "&amp;B26&amp;" "&amp;C26))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M26" s="16" t="n">
+      <x:c r="M26" s="11" t="n">
         <x:f>IF(AND(L26=1,K26&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6269,16 +6495,16 @@
       <x:c r="A27" s="2" t="str">
         <x:v>03A-027</x:v>
       </x:c>
-      <x:c r="B27" s="15" t="str">
+      <x:c r="B27" s="16" t="str">
         <x:v>미활용 LNG 기화 냉열 활용을 통한 전력 및 또는 화석연료 사용 절감 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="str">
+      <x:c r="C27" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D27" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str">
+      <x:c r="E27" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=440&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F27" s="17" t="n">
@@ -6293,23 +6519,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A27,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A27,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45359</x:v>
       </x:c>
-      <x:c r="I27" s="16" t="n">
+      <x:c r="I27" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A27,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="n">
+      <x:c r="J27" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A27,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K27" s="16" t="n">
+      <x:c r="K27" s="11" t="n">
         <x:f>IF(J27=0,"",'분석조건'!$B$5-F27)</x:f>
         <x:v>950</x:v>
       </x:c>
-      <x:c r="L27" s="16" t="n">
+      <x:c r="L27" s="11" t="n">
         <x:f>IF(AND(J27&gt;0,OR('분석조건'!$B$7="all",C27='분석조건'!$B$7),OR('분석조건'!$B$8="all",D27='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I27&gt;0),AND('분석조건'!$B$9="unrevised",I27=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A27&amp;" "&amp;B27&amp;" "&amp;C27))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M27" s="16" t="n">
+      <x:c r="M27" s="11" t="n">
         <x:f>IF(AND(L27=1,K27&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6322,16 +6548,16 @@
       <x:c r="A28" s="2" t="str">
         <x:v>03A-030</x:v>
       </x:c>
-      <x:c r="B28" s="15" t="str">
+      <x:c r="B28" s="16" t="str">
         <x:v>미활용 열에너지 회수 및 이용 또는 계통연계 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="str">
+      <x:c r="C28" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D28" s="2" t="str">
         <x:v>직권등록</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str">
+      <x:c r="E28" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=531&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F28" s="17" t="n">
@@ -6346,23 +6572,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A28,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A28,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45447</x:v>
       </x:c>
-      <x:c r="I28" s="16" t="n">
+      <x:c r="I28" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A28,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J28" s="16" t="n">
+      <x:c r="J28" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A28,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K28" s="16" t="n">
+      <x:c r="K28" s="11" t="n">
         <x:f>IF(J28=0,"",'분석조건'!$B$5-F28)</x:f>
         <x:v>316</x:v>
       </x:c>
-      <x:c r="L28" s="16" t="n">
+      <x:c r="L28" s="11" t="n">
         <x:f>IF(AND(J28&gt;0,OR('분석조건'!$B$7="all",C28='분석조건'!$B$7),OR('분석조건'!$B$8="all",D28='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I28&gt;0),AND('분석조건'!$B$9="unrevised",I28=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A28&amp;" "&amp;B28&amp;" "&amp;C28))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M28" s="16" t="n">
+      <x:c r="M28" s="11" t="n">
         <x:f>IF(AND(L28=1,K28&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6375,16 +6601,16 @@
       <x:c r="A29" s="2" t="str">
         <x:v>03A-033</x:v>
       </x:c>
-      <x:c r="B29" s="15" t="str">
+      <x:c r="B29" s="16" t="str">
         <x:v>공동 통신망 기술 적용에 따른 온실가스 감축사업의 방법론</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="str">
+      <x:c r="C29" s="16" t="str">
         <x:v>에너지 수요</x:v>
       </x:c>
       <x:c r="D29" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str">
+      <x:c r="E29" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=436&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F29" s="17" t="n">
@@ -6399,23 +6625,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A29,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A29,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>45721</x:v>
       </x:c>
-      <x:c r="I29" s="16" t="n">
+      <x:c r="I29" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A29,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J29" s="16" t="n">
+      <x:c r="J29" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A29,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K29" s="16" t="n">
+      <x:c r="K29" s="11" t="n">
         <x:f>IF(J29=0,"",'분석조건'!$B$5-F29)</x:f>
         <x:v>588</x:v>
       </x:c>
-      <x:c r="L29" s="16" t="n">
+      <x:c r="L29" s="11" t="n">
         <x:f>IF(AND(J29&gt;0,OR('분석조건'!$B$7="all",C29='분석조건'!$B$7),OR('분석조건'!$B$8="all",D29='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I29&gt;0),AND('분석조건'!$B$9="unrevised",I29=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A29&amp;" "&amp;B29&amp;" "&amp;C29))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M29" s="16" t="n">
+      <x:c r="M29" s="11" t="n">
         <x:f>IF(AND(L29=1,K29&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6428,16 +6654,16 @@
       <x:c r="A30" s="2" t="str">
         <x:v>04A-001</x:v>
       </x:c>
-      <x:c r="B30" s="15" t="str">
+      <x:c r="B30" s="16" t="str">
         <x:v>혼합시멘트 생산에서 원료의 부분적인 전환 및 혼합재 비율 증가를 통한 온실가스 감축</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="str">
+      <x:c r="C30" s="16" t="str">
         <x:v>제조업</x:v>
       </x:c>
       <x:c r="D30" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str">
+      <x:c r="E30" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=330&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F30" s="17" t="n">
@@ -6452,23 +6678,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A30,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A30,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44908</x:v>
       </x:c>
-      <x:c r="I30" s="16" t="n">
+      <x:c r="I30" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A30,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J30" s="16" t="n">
+      <x:c r="J30" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A30,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K30" s="16" t="n">
+      <x:c r="K30" s="11" t="n">
         <x:f>IF(J30=0,"",'분석조건'!$B$5-F30)</x:f>
         <x:v>1401</x:v>
       </x:c>
-      <x:c r="L30" s="16" t="n">
+      <x:c r="L30" s="11" t="n">
         <x:f>IF(AND(J30&gt;0,OR('분석조건'!$B$7="all",C30='분석조건'!$B$7),OR('분석조건'!$B$8="all",D30='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I30&gt;0),AND('분석조건'!$B$9="unrevised",I30=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A30&amp;" "&amp;B30&amp;" "&amp;C30))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M30" s="16" t="n">
+      <x:c r="M30" s="11" t="n">
         <x:f>IF(AND(L30=1,K30&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6481,16 +6707,16 @@
       <x:c r="A31" s="2" t="str">
         <x:v>04E-001</x:v>
       </x:c>
-      <x:c r="B31" s="15" t="str">
+      <x:c r="B31" s="16" t="str">
         <x:v>제지공정에서 침강성탄산칼슘 제조과정의 미활용 CO2 이용과 에너지절감 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="str">
+      <x:c r="C31" s="16" t="str">
         <x:v>제조업</x:v>
       </x:c>
       <x:c r="D31" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str">
+      <x:c r="E31" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=369&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F31" s="17" t="n">
@@ -6505,23 +6731,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A31,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A31,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44908</x:v>
       </x:c>
-      <x:c r="I31" s="16" t="n">
+      <x:c r="I31" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A31,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J31" s="16" t="n">
+      <x:c r="J31" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A31,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K31" s="16" t="n">
+      <x:c r="K31" s="11" t="n">
         <x:f>IF(J31=0,"",'분석조건'!$B$5-F31)</x:f>
         <x:v>1401</x:v>
       </x:c>
-      <x:c r="L31" s="16" t="n">
+      <x:c r="L31" s="11" t="n">
         <x:f>IF(AND(J31&gt;0,OR('분석조건'!$B$7="all",C31='분석조건'!$B$7),OR('분석조건'!$B$8="all",D31='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I31&gt;0),AND('분석조건'!$B$9="unrevised",I31=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A31&amp;" "&amp;B31&amp;" "&amp;C31))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M31" s="16" t="n">
+      <x:c r="M31" s="11" t="n">
         <x:f>IF(AND(L31=1,K31&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6534,16 +6760,16 @@
       <x:c r="A32" s="2" t="str">
         <x:v>05A-001</x:v>
       </x:c>
-      <x:c r="B32" s="15" t="str">
+      <x:c r="B32" s="16" t="str">
         <x:v>부생수소 활용을 통한 수소제조공정 대체사업의 방법론</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="str">
+      <x:c r="C32" s="16" t="str">
         <x:v>화학산업</x:v>
       </x:c>
       <x:c r="D32" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str">
+      <x:c r="E32" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=325&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F32" s="17" t="n">
@@ -6558,23 +6784,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A32,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A32,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44120</x:v>
       </x:c>
-      <x:c r="I32" s="16" t="n">
+      <x:c r="I32" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A32,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J32" s="16" t="n">
+      <x:c r="J32" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A32,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K32" s="16" t="n">
+      <x:c r="K32" s="11" t="n">
         <x:f>IF(J32=0,"",'분석조건'!$B$5-F32)</x:f>
         <x:v>2189</x:v>
       </x:c>
-      <x:c r="L32" s="16" t="n">
+      <x:c r="L32" s="11" t="n">
         <x:f>IF(AND(J32&gt;0,OR('분석조건'!$B$7="all",C32='분석조건'!$B$7),OR('분석조건'!$B$8="all",D32='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I32&gt;0),AND('분석조건'!$B$9="unrevised",I32=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A32&amp;" "&amp;B32&amp;" "&amp;C32))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M32" s="16" t="n">
+      <x:c r="M32" s="11" t="n">
         <x:f>IF(AND(L32=1,K32&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6587,16 +6813,16 @@
       <x:c r="A33" s="2" t="str">
         <x:v>06A-001</x:v>
       </x:c>
-      <x:c r="B33" s="15" t="str">
+      <x:c r="B33" s="16" t="str">
         <x:v>국내 중온 아스팔트 혼합물 생산을 통한 연료 및 온실가스 저감에 대한 방법론</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="str">
+      <x:c r="C33" s="16" t="str">
         <x:v>건설</x:v>
       </x:c>
       <x:c r="D33" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str">
+      <x:c r="E33" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=324&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F33" s="17" t="n">
@@ -6611,23 +6837,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A33,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A33,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44558</x:v>
       </x:c>
-      <x:c r="I33" s="16" t="n">
+      <x:c r="I33" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A33,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J33" s="16" t="n">
+      <x:c r="J33" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A33,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K33" s="16" t="n">
+      <x:c r="K33" s="11" t="n">
         <x:f>IF(J33=0,"",'분석조건'!$B$5-F33)</x:f>
         <x:v>1751</x:v>
       </x:c>
-      <x:c r="L33" s="16" t="n">
+      <x:c r="L33" s="11" t="n">
         <x:f>IF(AND(J33&gt;0,OR('분석조건'!$B$7="all",C33='분석조건'!$B$7),OR('분석조건'!$B$8="all",D33='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I33&gt;0),AND('분석조건'!$B$9="unrevised",I33=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A33&amp;" "&amp;B33&amp;" "&amp;C33))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M33" s="16" t="n">
+      <x:c r="M33" s="11" t="n">
         <x:f>IF(AND(L33=1,K33&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6640,16 +6866,16 @@
       <x:c r="A34" s="2" t="str">
         <x:v>11B-001</x:v>
       </x:c>
-      <x:c r="B34" s="15" t="str">
+      <x:c r="B34" s="16" t="str">
         <x:v>가스절연개폐장치 검사용 SF6 회수ㆍ정제 및 재사용을 통한 SF6 감축사업의 방법론</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="str">
+      <x:c r="C34" s="16" t="str">
         <x:v>할로겐화탄소, 육불화황 생산및소비로부터의 탈루배출</x:v>
       </x:c>
       <x:c r="D34" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str">
+      <x:c r="E34" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=49&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F34" s="17" t="n">
@@ -6664,23 +6890,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A34,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A34,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>43081</x:v>
       </x:c>
-      <x:c r="I34" s="16" t="n">
+      <x:c r="I34" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A34,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J34" s="16" t="n">
+      <x:c r="J34" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A34,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K34" s="16" t="n">
+      <x:c r="K34" s="11" t="n">
         <x:f>IF(J34=0,"",'분석조건'!$B$5-F34)</x:f>
         <x:v>3228</x:v>
       </x:c>
-      <x:c r="L34" s="16" t="n">
+      <x:c r="L34" s="11" t="n">
         <x:f>IF(AND(J34&gt;0,OR('분석조건'!$B$7="all",C34='분석조건'!$B$7),OR('분석조건'!$B$8="all",D34='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I34&gt;0),AND('분석조건'!$B$9="unrevised",I34=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A34&amp;" "&amp;B34&amp;" "&amp;C34))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M34" s="16" t="n">
+      <x:c r="M34" s="11" t="n">
         <x:f>IF(AND(L34=1,K34&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6693,16 +6919,16 @@
       <x:c r="A35" s="2" t="str">
         <x:v>11B-002</x:v>
       </x:c>
-      <x:c r="B35" s="15" t="str">
+      <x:c r="B35" s="16" t="str">
         <x:v>광전지 제조 공정의 SF6 가스 처리를 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="str">
+      <x:c r="C35" s="16" t="str">
         <x:v>할로겐화탄소, 육불화황 생산및소비로부터의 탈루배출</x:v>
       </x:c>
       <x:c r="D35" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="str">
+      <x:c r="E35" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=315&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F35" s="17" t="n">
@@ -6717,23 +6943,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A35,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A35,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44120</x:v>
       </x:c>
-      <x:c r="I35" s="16" t="n">
+      <x:c r="I35" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A35,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J35" s="16" t="n">
+      <x:c r="J35" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A35,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K35" s="16" t="n">
+      <x:c r="K35" s="11" t="n">
         <x:f>IF(J35=0,"",'분석조건'!$B$5-F35)</x:f>
         <x:v>2189</x:v>
       </x:c>
-      <x:c r="L35" s="16" t="n">
+      <x:c r="L35" s="11" t="n">
         <x:f>IF(AND(J35&gt;0,OR('분석조건'!$B$7="all",C35='분석조건'!$B$7),OR('분석조건'!$B$8="all",D35='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I35&gt;0),AND('분석조건'!$B$9="unrevised",I35=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A35&amp;" "&amp;B35&amp;" "&amp;C35))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M35" s="16" t="n">
+      <x:c r="M35" s="11" t="n">
         <x:f>IF(AND(L35=1,K35&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6746,16 +6972,16 @@
       <x:c r="A36" s="2" t="str">
         <x:v>11B-003</x:v>
       </x:c>
-      <x:c r="B36" s="15" t="str">
+      <x:c r="B36" s="16" t="str">
         <x:v>발포제로 사용되는 HFC-152a 회수·정제 및 재사용을 통한 HFC-152a 감축사업의 방법론</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="str">
+      <x:c r="C36" s="16" t="str">
         <x:v>할로겐화탄소, 육불화황 생산및소비로부터의 탈루배출</x:v>
       </x:c>
       <x:c r="D36" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="str">
+      <x:c r="E36" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=299&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F36" s="17" t="n">
@@ -6770,23 +6996,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A36,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A36,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44252</x:v>
       </x:c>
-      <x:c r="I36" s="16" t="n">
+      <x:c r="I36" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A36,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J36" s="16" t="n">
+      <x:c r="J36" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A36,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K36" s="16" t="n">
+      <x:c r="K36" s="11" t="n">
         <x:f>IF(J36=0,"",'분석조건'!$B$5-F36)</x:f>
         <x:v>2057</x:v>
       </x:c>
-      <x:c r="L36" s="16" t="n">
+      <x:c r="L36" s="11" t="n">
         <x:f>IF(AND(J36&gt;0,OR('분석조건'!$B$7="all",C36='분석조건'!$B$7),OR('분석조건'!$B$8="all",D36='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I36&gt;0),AND('분석조건'!$B$9="unrevised",I36=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A36&amp;" "&amp;B36&amp;" "&amp;C36))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M36" s="16" t="n">
+      <x:c r="M36" s="11" t="n">
         <x:f>IF(AND(L36=1,K36&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6799,16 +7025,16 @@
       <x:c r="A37" s="2" t="str">
         <x:v>11B-004</x:v>
       </x:c>
-      <x:c r="B37" s="15" t="str">
+      <x:c r="B37" s="16" t="str">
         <x:v>가스절연 전기기기의 시험에 따라 발생되는 육불화황(SF6) 가스의 회수 및 플라즈마 분해를 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="str">
+      <x:c r="C37" s="16" t="str">
         <x:v>할로겐화탄소, 육불화황 생산및소비로부터의 탈루배출</x:v>
       </x:c>
       <x:c r="D37" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="str">
+      <x:c r="E37" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=515&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F37" s="17" t="n">
@@ -6823,23 +7049,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A37,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A37,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44558</x:v>
       </x:c>
-      <x:c r="I37" s="16" t="n">
+      <x:c r="I37" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A37,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J37" s="16" t="n">
+      <x:c r="J37" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A37,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K37" s="16" t="n">
+      <x:c r="K37" s="11" t="n">
         <x:f>IF(J37=0,"",'분석조건'!$B$5-F37)</x:f>
         <x:v>134</x:v>
       </x:c>
-      <x:c r="L37" s="16" t="n">
+      <x:c r="L37" s="11" t="n">
         <x:f>IF(AND(J37&gt;0,OR('분석조건'!$B$7="all",C37='분석조건'!$B$7),OR('분석조건'!$B$8="all",D37='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I37&gt;0),AND('분석조건'!$B$9="unrevised",I37=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A37&amp;" "&amp;B37&amp;" "&amp;C37))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M37" s="16" t="n">
+      <x:c r="M37" s="11" t="n">
         <x:f>IF(AND(L37=1,K37&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6852,16 +7078,16 @@
       <x:c r="A38" s="2" t="str">
         <x:v>11B-005</x:v>
       </x:c>
-      <x:c r="B38" s="15" t="str">
+      <x:c r="B38" s="16" t="str">
         <x:v>전력계통내 폐기된 전기설비의 충진된 SF6를 회수 및 정제하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="C38" s="16" t="str">
         <x:v>할로겐화탄소, 육불화황 생산및소비로부터의 탈루배출</x:v>
       </x:c>
       <x:c r="D38" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="str">
+      <x:c r="E38" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=383&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F38" s="17" t="n">
@@ -6876,23 +7102,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A38,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A38,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44992</x:v>
       </x:c>
-      <x:c r="I38" s="16" t="n">
+      <x:c r="I38" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A38,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J38" s="16" t="n">
+      <x:c r="J38" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A38,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K38" s="16" t="n">
+      <x:c r="K38" s="11" t="n">
         <x:f>IF(J38=0,"",'분석조건'!$B$5-F38)</x:f>
         <x:v>1317</x:v>
       </x:c>
-      <x:c r="L38" s="16" t="n">
+      <x:c r="L38" s="11" t="n">
         <x:f>IF(AND(J38&gt;0,OR('분석조건'!$B$7="all",C38='분석조건'!$B$7),OR('분석조건'!$B$8="all",D38='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I38&gt;0),AND('분석조건'!$B$9="unrevised",I38=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A38&amp;" "&amp;B38&amp;" "&amp;C38))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M38" s="16" t="n">
+      <x:c r="M38" s="11" t="n">
         <x:f>IF(AND(L38=1,K38&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6905,16 +7131,16 @@
       <x:c r="A39" s="2" t="str">
         <x:v>11B-006</x:v>
       </x:c>
-      <x:c r="B39" s="15" t="str">
+      <x:c r="B39" s="16" t="str">
         <x:v>반도체 제조공정의 F-Gas 감축설비 도입을 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="str">
+      <x:c r="C39" s="16" t="str">
         <x:v>할로겐화탄소, 육불화황 생산및소비로부터의 탈루배출</x:v>
       </x:c>
       <x:c r="D39" s="2" t="str">
         <x:v>신청등록</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="str">
+      <x:c r="E39" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=404&amp;menuId=12</x:v>
       </x:c>
       <x:c r="F39" s="17" t="n">
@@ -6929,23 +7155,23 @@
         <x:f>IF(COUNTIFS('버전'!$B$7:$B$46,A39,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)=0,"",_xlfn.MINIFS('버전'!$E$7:$E$46,'버전'!$B$7:$B$46,A39,'버전'!$D$7:$D$46,"new",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5))</x:f>
         <x:v>44992</x:v>
       </x:c>
-      <x:c r="I39" s="16" t="n">
+      <x:c r="I39" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A39,'버전'!$D$7:$D$46,"revision",'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J39" s="16" t="n">
+      <x:c r="J39" s="11" t="n">
         <x:f>COUNTIFS('버전'!$B$7:$B$46,A39,'버전'!$E$7:$E$46,"&lt;="&amp;'분석조건'!$B$5)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K39" s="16" t="n">
+      <x:c r="K39" s="11" t="n">
         <x:f>IF(J39=0,"",'분석조건'!$B$5-F39)</x:f>
         <x:v>1317</x:v>
       </x:c>
-      <x:c r="L39" s="16" t="n">
+      <x:c r="L39" s="11" t="n">
         <x:f>IF(AND(J39&gt;0,OR('분석조건'!$B$7="all",C39='분석조건'!$B$7),OR('분석조건'!$B$8="all",D39='분석조건'!$B$8),OR('분석조건'!$B$9="all",AND('분석조건'!$B$9="revised",I39&gt;0),AND('분석조건'!$B$9="unrevised",I39=0)),ISNUMBER(SEARCH(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('분석조건'!$B$12,"~","~~"),"*","~*"),"?","~?"),A39&amp;" "&amp;B39&amp;" "&amp;C39))),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M39" s="16" t="n">
+      <x:c r="M39" s="11" t="n">
         <x:f>IF(AND(L39=1,K39&gt;'분석조건'!$B$10),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -6961,7 +7187,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5edfba3530b64b2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44de08af558448b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6969,7 +7195,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF7B9BF7"/>
+    <x:tabColor rgb="FF246BEB"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -6990,7 +7216,7 @@
     <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="3" customHeight="1">
+    <x:row r="1" ht="4.5" customHeight="1">
       <x:c r="A1" s="3"/>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -7080,49 +7306,49 @@
       <x:c r="O5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="15" t="str">
         <x:v>버전 ID</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>방법론 코드</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="str">
+      <x:c r="C6" s="15" t="str">
         <x:v>버전</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
+      <x:c r="D6" s="15" t="str">
         <x:v>구분</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str">
+      <x:c r="E6" s="15" t="str">
         <x:v>유효시작일</x:v>
       </x:c>
-      <x:c r="F6" s="14" t="str">
+      <x:c r="F6" s="15" t="str">
         <x:v>방법론명</x:v>
       </x:c>
-      <x:c r="G6" s="14" t="str">
+      <x:c r="G6" s="15" t="str">
         <x:v>공개 출처</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="str">
+      <x:c r="H6" s="15" t="str">
         <x:v>버전 번호</x:v>
       </x:c>
-      <x:c r="I6" s="14" t="str">
+      <x:c r="I6" s="15" t="str">
         <x:v>상한일 이내</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="str">
+      <x:c r="J6" s="15" t="str">
         <x:v>방법론 포함</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="str">
+      <x:c r="K6" s="15" t="str">
         <x:v>포함</x:v>
       </x:c>
-      <x:c r="L6" s="14" t="str">
+      <x:c r="L6" s="15" t="str">
         <x:v>유효시작 연도</x:v>
       </x:c>
-      <x:c r="M6" s="14" t="str">
+      <x:c r="M6" s="15" t="str">
         <x:v>최근 변경</x:v>
       </x:c>
-      <x:c r="N6" s="14" t="str">
+      <x:c r="N6" s="15" t="str">
         <x:v>선택연도 동기간</x:v>
       </x:c>
-      <x:c r="O6" s="14" t="str">
+      <x:c r="O6" s="15" t="str">
         <x:v>전년 동기간</x:v>
       </x:c>
     </x:row>
@@ -7142,40 +7368,40 @@
       <x:c r="E7" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F7" s="15" t="str">
+      <x:c r="F7" s="16" t="str">
         <x:v>목재펠릿을 활용한 연료전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G7" s="15" t="str">
+      <x:c r="G7" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=15&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H7" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I7" s="16" t="n">
+      <x:c r="H7" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="n">
         <x:f>IF(E7&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="16" t="n">
+      <x:c r="J7" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B7,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K7" s="16" t="n">
+      <x:c r="K7" s="11" t="n">
         <x:f>I7*J7</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L7" s="16" t="n">
+      <x:c r="L7" s="11" t="n">
         <x:f>YEAR(E7)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M7" s="16" t="n">
+      <x:c r="M7" s="11" t="n">
         <x:f>IF(AND(K7=1,'분석조건'!$B$5-E7&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N7" s="16" t="n">
+      <x:c r="N7" s="11" t="n">
         <x:f>IF(AND(K7=1,E7&gt;=DATE('분석조건'!$B$6,1,1),E7&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O7" s="16" t="n">
+      <x:c r="O7" s="11" t="n">
         <x:f>IF(AND(K7=1,E7&gt;=DATE('분석조건'!$B$6-1,1,1),E7&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7196,40 +7422,40 @@
       <x:c r="E8" s="9" t="n">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="str">
+      <x:c r="F8" s="16" t="str">
         <x:v>가축분뇨 고체연료를 활용한 열/전력 생산 및 이용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="str">
+      <x:c r="G8" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=469&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H8" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I8" s="16" t="n">
+      <x:c r="H8" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="n">
         <x:f>IF(E8&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
+      <x:c r="J8" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B8,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="11" t="n">
         <x:f>I8*J8</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L8" s="16" t="n">
+      <x:c r="L8" s="11" t="n">
         <x:f>YEAR(E8)</x:f>
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="M8" s="16" t="n">
+      <x:c r="M8" s="11" t="n">
         <x:f>IF(AND(K8=1,'분석조건'!$B$5-E8&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N8" s="16" t="n">
+      <x:c r="N8" s="11" t="n">
         <x:f>IF(AND(K8=1,E8&gt;=DATE('분석조건'!$B$6,1,1),E8&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O8" s="16" t="n">
+      <x:c r="O8" s="11" t="n">
         <x:f>IF(AND(K8=1,E8&gt;=DATE('분석조건'!$B$6-1,1,1),E8&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -7250,40 +7476,40 @@
       <x:c r="E9" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="str">
+      <x:c r="F9" s="16" t="str">
         <x:v>재생에너지를 이용한 전력 생산 및 계통 연계 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="str">
+      <x:c r="G9" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=18&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I9" s="16" t="n">
+      <x:c r="H9" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
         <x:f>IF(E9&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B9,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K9" s="11" t="n">
         <x:f>I9*J9</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L9" s="16" t="n">
+      <x:c r="L9" s="11" t="n">
         <x:f>YEAR(E9)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M9" s="16" t="n">
+      <x:c r="M9" s="11" t="n">
         <x:f>IF(AND(K9=1,'분석조건'!$B$5-E9&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N9" s="16" t="n">
+      <x:c r="N9" s="11" t="n">
         <x:f>IF(AND(K9=1,E9&gt;=DATE('분석조건'!$B$6,1,1),E9&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O9" s="16" t="n">
+      <x:c r="O9" s="11" t="n">
         <x:f>IF(AND(K9=1,E9&gt;=DATE('분석조건'!$B$6-1,1,1),E9&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7304,40 +7530,40 @@
       <x:c r="E10" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="str">
+      <x:c r="F10" s="16" t="str">
         <x:v>태양열에너지를 이용한 열에너지 생산 및 이용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="str">
+      <x:c r="G10" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=20&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I10" s="16" t="n">
+      <x:c r="H10" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="n">
         <x:f>IF(E10&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B10,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" s="16" t="n">
+      <x:c r="K10" s="11" t="n">
         <x:f>I10*J10</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L10" s="16" t="n">
+      <x:c r="L10" s="11" t="n">
         <x:f>YEAR(E10)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="n">
+      <x:c r="M10" s="11" t="n">
         <x:f>IF(AND(K10=1,'분석조건'!$B$5-E10&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N10" s="16" t="n">
+      <x:c r="N10" s="11" t="n">
         <x:f>IF(AND(K10=1,E10&gt;=DATE('분석조건'!$B$6,1,1),E10&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O10" s="16" t="n">
+      <x:c r="O10" s="11" t="n">
         <x:f>IF(AND(K10=1,E10&gt;=DATE('분석조건'!$B$6-1,1,1),E10&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7358,40 +7584,40 @@
       <x:c r="E11" s="9" t="n">
         <x:v>42516</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str">
+      <x:c r="F11" s="16" t="str">
         <x:v>재생에너지를 이용한 전력 생산 및 자가 사용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="str">
+      <x:c r="G11" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=44&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H11" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I11" s="16" t="n">
+      <x:c r="H11" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="n">
         <x:f>IF(E11&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B11,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K11" s="16" t="n">
+      <x:c r="K11" s="11" t="n">
         <x:f>I11*J11</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L11" s="16" t="n">
+      <x:c r="L11" s="11" t="n">
         <x:f>YEAR(E11)</x:f>
         <x:v>2016</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="n">
+      <x:c r="M11" s="11" t="n">
         <x:f>IF(AND(K11=1,'분석조건'!$B$5-E11&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N11" s="16" t="n">
+      <x:c r="N11" s="11" t="n">
         <x:f>IF(AND(K11=1,E11&gt;=DATE('분석조건'!$B$6,1,1),E11&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O11" s="16" t="n">
+      <x:c r="O11" s="11" t="n">
         <x:f>IF(AND(K11=1,E11&gt;=DATE('분석조건'!$B$6-1,1,1),E11&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7412,40 +7638,40 @@
       <x:c r="E12" s="9" t="n">
         <x:v>43987</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="str">
+      <x:c r="F12" s="16" t="str">
         <x:v>전력 자가사용 및 독립된 소규모 계통 연계를 위한 재생에너지 발전사업의 방법론</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="str">
+      <x:c r="G12" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=353&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I12" s="16" t="n">
+      <x:c r="H12" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
         <x:f>IF(E12&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B12,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" s="16" t="n">
+      <x:c r="K12" s="11" t="n">
         <x:f>I12*J12</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L12" s="16" t="n">
+      <x:c r="L12" s="11" t="n">
         <x:f>YEAR(E12)</x:f>
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="n">
+      <x:c r="M12" s="11" t="n">
         <x:f>IF(AND(K12=1,'분석조건'!$B$5-E12&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N12" s="16" t="n">
+      <x:c r="N12" s="11" t="n">
         <x:f>IF(AND(K12=1,E12&gt;=DATE('분석조건'!$B$6,1,1),E12&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O12" s="16" t="n">
+      <x:c r="O12" s="11" t="n">
         <x:f>IF(AND(K12=1,E12&gt;=DATE('분석조건'!$B$6-1,1,1),E12&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7466,40 +7692,40 @@
       <x:c r="E13" s="9" t="n">
         <x:v>44834</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str">
+      <x:c r="F13" s="16" t="str">
         <x:v>수소 연료전지를 이용한 전기 및 열생산 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="str">
+      <x:c r="G13" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=532&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I13" s="16" t="n">
+      <x:c r="H13" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
         <x:f>IF(E13&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B13,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" s="16" t="n">
+      <x:c r="K13" s="11" t="n">
         <x:f>I13*J13</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L13" s="16" t="n">
+      <x:c r="L13" s="11" t="n">
         <x:f>YEAR(E13)</x:f>
         <x:v>2022</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="n">
+      <x:c r="M13" s="11" t="n">
         <x:f>IF(AND(K13=1,'분석조건'!$B$5-E13&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N13" s="16" t="n">
+      <x:c r="N13" s="11" t="n">
         <x:f>IF(AND(K13=1,E13&gt;=DATE('분석조건'!$B$6,1,1),E13&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O13" s="16" t="n">
+      <x:c r="O13" s="11" t="n">
         <x:f>IF(AND(K13=1,E13&gt;=DATE('분석조건'!$B$6-1,1,1),E13&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7520,40 +7746,40 @@
       <x:c r="E14" s="9" t="n">
         <x:v>45993</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="str">
+      <x:c r="F14" s="16" t="str">
         <x:v>수소 연료전지를 이용한 전기 및 열생산 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="str">
+      <x:c r="G14" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=532&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H14" s="16" t="n">
+      <x:c r="H14" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I14" s="16" t="n">
+      <x:c r="I14" s="11" t="n">
         <x:f>IF(E14&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B14,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K14" s="16" t="n">
+      <x:c r="K14" s="11" t="n">
         <x:f>I14*J14</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L14" s="16" t="n">
+      <x:c r="L14" s="11" t="n">
         <x:f>YEAR(E14)</x:f>
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="n">
+      <x:c r="M14" s="11" t="n">
         <x:f>IF(AND(K14=1,'분석조건'!$B$5-E14&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N14" s="16" t="n">
+      <x:c r="N14" s="11" t="n">
         <x:f>IF(AND(K14=1,E14&gt;=DATE('분석조건'!$B$6,1,1),E14&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O14" s="16" t="n">
+      <x:c r="O14" s="11" t="n">
         <x:f>IF(AND(K14=1,E14&gt;=DATE('분석조건'!$B$6-1,1,1),E14&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7574,40 +7800,40 @@
       <x:c r="E15" s="9" t="n">
         <x:v>45538</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="str">
+      <x:c r="F15" s="16" t="str">
         <x:v>재생에너지를 통해 생산한 전력을 자가 사용 및/또는 계통 연계하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="str">
+      <x:c r="G15" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=537&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H15" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I15" s="16" t="n">
+      <x:c r="H15" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
         <x:f>IF(E15&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B15,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="16" t="n">
+      <x:c r="K15" s="11" t="n">
         <x:f>I15*J15</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L15" s="16" t="n">
+      <x:c r="L15" s="11" t="n">
         <x:f>YEAR(E15)</x:f>
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="M15" s="16" t="n">
+      <x:c r="M15" s="11" t="n">
         <x:f>IF(AND(K15=1,'분석조건'!$B$5-E15&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N15" s="16" t="n">
+      <x:c r="N15" s="11" t="n">
         <x:f>IF(AND(K15=1,E15&gt;=DATE('분석조건'!$B$6,1,1),E15&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O15" s="16" t="n">
+      <x:c r="O15" s="11" t="n">
         <x:f>IF(AND(K15=1,E15&gt;=DATE('분석조건'!$B$6-1,1,1),E15&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7628,40 +7854,40 @@
       <x:c r="E16" s="9" t="n">
         <x:v>46267</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str">
+      <x:c r="F16" s="16" t="str">
         <x:v>재생에너지를 통해 생산한 전력을 자가 사용 및/또는 계통 연계하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="str">
+      <x:c r="G16" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=537&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H16" s="16" t="n">
+      <x:c r="H16" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I16" s="16" t="n">
+      <x:c r="I16" s="11" t="n">
         <x:f>IF(E16&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
+      <x:c r="J16" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B16,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="16" t="n">
+      <x:c r="K16" s="11" t="n">
         <x:f>I16*J16</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="n">
+      <x:c r="L16" s="11" t="n">
         <x:f>YEAR(E16)</x:f>
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="M16" s="16" t="n">
+      <x:c r="M16" s="11" t="n">
         <x:f>IF(AND(K16=1,'분석조건'!$B$5-E16&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N16" s="16" t="n">
+      <x:c r="N16" s="11" t="n">
         <x:f>IF(AND(K16=1,E16&gt;=DATE('분석조건'!$B$6,1,1),E16&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O16" s="16" t="n">
+      <x:c r="O16" s="11" t="n">
         <x:f>IF(AND(K16=1,E16&gt;=DATE('분석조건'!$B$6-1,1,1),E16&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7682,40 +7908,40 @@
       <x:c r="E17" s="9" t="n">
         <x:v>45538</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="str">
+      <x:c r="F17" s="16" t="str">
         <x:v>자가발전을 통한 사업장 전력 대체 온실가스 감축 방법론</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="str">
+      <x:c r="G17" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=406&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H17" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I17" s="16" t="n">
+      <x:c r="H17" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
         <x:f>IF(E17&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="n">
+      <x:c r="J17" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B17,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K17" s="16" t="n">
+      <x:c r="K17" s="11" t="n">
         <x:f>I17*J17</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L17" s="16" t="n">
+      <x:c r="L17" s="11" t="n">
         <x:f>YEAR(E17)</x:f>
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="M17" s="16" t="n">
+      <x:c r="M17" s="11" t="n">
         <x:f>IF(AND(K17=1,'분석조건'!$B$5-E17&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N17" s="16" t="n">
+      <x:c r="N17" s="11" t="n">
         <x:f>IF(AND(K17=1,E17&gt;=DATE('분석조건'!$B$6,1,1),E17&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O17" s="16" t="n">
+      <x:c r="O17" s="11" t="n">
         <x:f>IF(AND(K17=1,E17&gt;=DATE('분석조건'!$B$6-1,1,1),E17&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7736,40 +7962,40 @@
       <x:c r="E18" s="9" t="n">
         <x:v>42810</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="str">
+      <x:c r="F18" s="16" t="str">
         <x:v>열공급시설에서 목질계 바이오매스 연료를 이용하여 생산된 열에너지 공급을 통한 수용가의 화석연료 사용량 절감사업의 방법론</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="str">
+      <x:c r="G18" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=332&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H18" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I18" s="16" t="n">
+      <x:c r="H18" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
         <x:f>IF(E18&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
+      <x:c r="J18" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B18,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K18" s="16" t="n">
+      <x:c r="K18" s="11" t="n">
         <x:f>I18*J18</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="n">
+      <x:c r="L18" s="11" t="n">
         <x:f>YEAR(E18)</x:f>
         <x:v>2017</x:v>
       </x:c>
-      <x:c r="M18" s="16" t="n">
+      <x:c r="M18" s="11" t="n">
         <x:f>IF(AND(K18=1,'분석조건'!$B$5-E18&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18" s="16" t="n">
+      <x:c r="N18" s="11" t="n">
         <x:f>IF(AND(K18=1,E18&gt;=DATE('분석조건'!$B$6,1,1),E18&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="16" t="n">
+      <x:c r="O18" s="11" t="n">
         <x:f>IF(AND(K18=1,E18&gt;=DATE('분석조건'!$B$6-1,1,1),E18&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7790,40 +8016,40 @@
       <x:c r="E19" s="9" t="n">
         <x:v>44252</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="str">
+      <x:c r="F19" s="16" t="str">
         <x:v>열공급시설에서 목질계 바이오매스 연료를 이용하여 생산된 열에너지 공급을 통한 수용가의 화석연료 사용량 절감사업의 방법론</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="str">
+      <x:c r="G19" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=332&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H19" s="16" t="n">
+      <x:c r="H19" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I19" s="16" t="n">
+      <x:c r="I19" s="11" t="n">
         <x:f>IF(E19&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="n">
+      <x:c r="J19" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B19,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K19" s="16" t="n">
+      <x:c r="K19" s="11" t="n">
         <x:f>I19*J19</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L19" s="16" t="n">
+      <x:c r="L19" s="11" t="n">
         <x:f>YEAR(E19)</x:f>
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="M19" s="16" t="n">
+      <x:c r="M19" s="11" t="n">
         <x:f>IF(AND(K19=1,'분석조건'!$B$5-E19&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N19" s="16" t="n">
+      <x:c r="N19" s="11" t="n">
         <x:f>IF(AND(K19=1,E19&gt;=DATE('분석조건'!$B$6,1,1),E19&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O19" s="16" t="n">
+      <x:c r="O19" s="11" t="n">
         <x:f>IF(AND(K19=1,E19&gt;=DATE('분석조건'!$B$6-1,1,1),E19&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7844,40 +8070,40 @@
       <x:c r="E20" s="9" t="n">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="str">
+      <x:c r="F20" s="16" t="str">
         <x:v>섬유염색공정에서 증기 전용 텐터기 도입과 텐터기 전용 열 공급을 통한 수용가의 화석연료 사용량 절감사업의 방법론</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="str">
+      <x:c r="G20" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=438&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H20" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I20" s="16" t="n">
+      <x:c r="H20" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
         <x:f>IF(E20&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="n">
+      <x:c r="J20" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B20,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K20" s="16" t="n">
+      <x:c r="K20" s="11" t="n">
         <x:f>I20*J20</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L20" s="16" t="n">
+      <x:c r="L20" s="11" t="n">
         <x:f>YEAR(E20)</x:f>
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="M20" s="16" t="n">
+      <x:c r="M20" s="11" t="n">
         <x:f>IF(AND(K20=1,'분석조건'!$B$5-E20&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N20" s="16" t="n">
+      <x:c r="N20" s="11" t="n">
         <x:f>IF(AND(K20=1,E20&gt;=DATE('분석조건'!$B$6,1,1),E20&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O20" s="16" t="n">
+      <x:c r="O20" s="11" t="n">
         <x:f>IF(AND(K20=1,E20&gt;=DATE('분석조건'!$B$6-1,1,1),E20&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -7898,40 +8124,40 @@
       <x:c r="E21" s="9" t="n">
         <x:v>42405</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="str">
+      <x:c r="F21" s="16" t="str">
         <x:v>미활용 열에너지 회수 및 이용 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="str">
+      <x:c r="G21" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=40&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H21" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I21" s="16" t="n">
+      <x:c r="H21" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="n">
         <x:f>IF(E21&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="n">
+      <x:c r="J21" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B21,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K21" s="16" t="n">
+      <x:c r="K21" s="11" t="n">
         <x:f>I21*J21</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L21" s="16" t="n">
+      <x:c r="L21" s="11" t="n">
         <x:f>YEAR(E21)</x:f>
         <x:v>2016</x:v>
       </x:c>
-      <x:c r="M21" s="16" t="n">
+      <x:c r="M21" s="11" t="n">
         <x:f>IF(AND(K21=1,'분석조건'!$B$5-E21&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N21" s="16" t="n">
+      <x:c r="N21" s="11" t="n">
         <x:f>IF(AND(K21=1,E21&gt;=DATE('분석조건'!$B$6,1,1),E21&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O21" s="16" t="n">
+      <x:c r="O21" s="11" t="n">
         <x:f>IF(AND(K21=1,E21&gt;=DATE('분석조건'!$B$6-1,1,1),E21&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7952,40 +8178,40 @@
       <x:c r="E22" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="str">
+      <x:c r="F22" s="16" t="str">
         <x:v>연료 전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="str">
+      <x:c r="G22" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=466&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H22" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I22" s="16" t="n">
+      <x:c r="H22" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
         <x:f>IF(E22&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="n">
+      <x:c r="J22" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B22,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K22" s="16" t="n">
+      <x:c r="K22" s="11" t="n">
         <x:f>I22*J22</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L22" s="16" t="n">
+      <x:c r="L22" s="11" t="n">
         <x:f>YEAR(E22)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M22" s="16" t="n">
+      <x:c r="M22" s="11" t="n">
         <x:f>IF(AND(K22=1,'분석조건'!$B$5-E22&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N22" s="16" t="n">
+      <x:c r="N22" s="11" t="n">
         <x:f>IF(AND(K22=1,E22&gt;=DATE('분석조건'!$B$6,1,1),E22&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O22" s="16" t="n">
+      <x:c r="O22" s="11" t="n">
         <x:f>IF(AND(K22=1,E22&gt;=DATE('분석조건'!$B$6-1,1,1),E22&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8006,40 +8232,40 @@
       <x:c r="E23" s="9" t="n">
         <x:v>44558</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="str">
+      <x:c r="F23" s="16" t="str">
         <x:v>연료 전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="str">
+      <x:c r="G23" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=466&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H23" s="16" t="n">
+      <x:c r="H23" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I23" s="16" t="n">
+      <x:c r="I23" s="11" t="n">
         <x:f>IF(E23&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="n">
+      <x:c r="J23" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B23,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K23" s="16" t="n">
+      <x:c r="K23" s="11" t="n">
         <x:f>I23*J23</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L23" s="16" t="n">
+      <x:c r="L23" s="11" t="n">
         <x:f>YEAR(E23)</x:f>
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="M23" s="16" t="n">
+      <x:c r="M23" s="11" t="n">
         <x:f>IF(AND(K23=1,'분석조건'!$B$5-E23&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N23" s="16" t="n">
+      <x:c r="N23" s="11" t="n">
         <x:f>IF(AND(K23=1,E23&gt;=DATE('분석조건'!$B$6,1,1),E23&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O23" s="16" t="n">
+      <x:c r="O23" s="11" t="n">
         <x:f>IF(AND(K23=1,E23&gt;=DATE('분석조건'!$B$6-1,1,1),E23&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8060,40 +8286,40 @@
       <x:c r="E24" s="9" t="n">
         <x:v>45447</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str">
+      <x:c r="F24" s="16" t="str">
         <x:v>연료 전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="str">
+      <x:c r="G24" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=466&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H24" s="16" t="n">
+      <x:c r="H24" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I24" s="16" t="n">
+      <x:c r="I24" s="11" t="n">
         <x:f>IF(E24&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="n">
+      <x:c r="J24" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B24,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K24" s="16" t="n">
+      <x:c r="K24" s="11" t="n">
         <x:f>I24*J24</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L24" s="16" t="n">
+      <x:c r="L24" s="11" t="n">
         <x:f>YEAR(E24)</x:f>
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="M24" s="16" t="n">
+      <x:c r="M24" s="11" t="n">
         <x:f>IF(AND(K24=1,'분석조건'!$B$5-E24&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N24" s="16" t="n">
+      <x:c r="N24" s="11" t="n">
         <x:f>IF(AND(K24=1,E24&gt;=DATE('분석조건'!$B$6,1,1),E24&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O24" s="16" t="n">
+      <x:c r="O24" s="11" t="n">
         <x:f>IF(AND(K24=1,E24&gt;=DATE('분석조건'!$B$6-1,1,1),E24&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8114,40 +8340,40 @@
       <x:c r="E25" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="str">
+      <x:c r="F25" s="16" t="str">
         <x:v>전력절감설비 설치사업의 방법론</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="str">
+      <x:c r="G25" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=22&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H25" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I25" s="16" t="n">
+      <x:c r="H25" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="n">
         <x:f>IF(E25&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="n">
+      <x:c r="J25" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B25,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K25" s="16" t="n">
+      <x:c r="K25" s="11" t="n">
         <x:f>I25*J25</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L25" s="16" t="n">
+      <x:c r="L25" s="11" t="n">
         <x:f>YEAR(E25)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M25" s="16" t="n">
+      <x:c r="M25" s="11" t="n">
         <x:f>IF(AND(K25=1,'분석조건'!$B$5-E25&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N25" s="16" t="n">
+      <x:c r="N25" s="11" t="n">
         <x:f>IF(AND(K25=1,E25&gt;=DATE('분석조건'!$B$6,1,1),E25&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O25" s="16" t="n">
+      <x:c r="O25" s="11" t="n">
         <x:f>IF(AND(K25=1,E25&gt;=DATE('분석조건'!$B$6-1,1,1),E25&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8168,40 +8394,40 @@
       <x:c r="E26" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="str">
+      <x:c r="F26" s="16" t="str">
         <x:v>고효율 설비 교체 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G26" s="15" t="str">
+      <x:c r="G26" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=23&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H26" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I26" s="16" t="n">
+      <x:c r="H26" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="n">
         <x:f>IF(E26&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="n">
+      <x:c r="J26" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B26,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K26" s="16" t="n">
+      <x:c r="K26" s="11" t="n">
         <x:f>I26*J26</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L26" s="16" t="n">
+      <x:c r="L26" s="11" t="n">
         <x:f>YEAR(E26)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M26" s="16" t="n">
+      <x:c r="M26" s="11" t="n">
         <x:f>IF(AND(K26=1,'분석조건'!$B$5-E26&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N26" s="16" t="n">
+      <x:c r="N26" s="11" t="n">
         <x:f>IF(AND(K26=1,E26&gt;=DATE('분석조건'!$B$6,1,1),E26&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O26" s="16" t="n">
+      <x:c r="O26" s="11" t="n">
         <x:f>IF(AND(K26=1,E26&gt;=DATE('분석조건'!$B$6-1,1,1),E26&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8222,40 +8448,40 @@
       <x:c r="E27" s="9" t="n">
         <x:v>42115</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="str">
+      <x:c r="F27" s="16" t="str">
         <x:v>고효율 도로조명 설치 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G27" s="15" t="str">
+      <x:c r="G27" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=25&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H27" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I27" s="16" t="n">
+      <x:c r="H27" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="n">
         <x:f>IF(E27&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="n">
+      <x:c r="J27" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B27,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K27" s="16" t="n">
+      <x:c r="K27" s="11" t="n">
         <x:f>I27*J27</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L27" s="16" t="n">
+      <x:c r="L27" s="11" t="n">
         <x:f>YEAR(E27)</x:f>
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="M27" s="16" t="n">
+      <x:c r="M27" s="11" t="n">
         <x:f>IF(AND(K27=1,'분석조건'!$B$5-E27&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N27" s="16" t="n">
+      <x:c r="N27" s="11" t="n">
         <x:f>IF(AND(K27=1,E27&gt;=DATE('분석조건'!$B$6,1,1),E27&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O27" s="16" t="n">
+      <x:c r="O27" s="11" t="n">
         <x:f>IF(AND(K27=1,E27&gt;=DATE('분석조건'!$B$6-1,1,1),E27&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8276,40 +8502,40 @@
       <x:c r="E28" s="9" t="n">
         <x:v>42405</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="str">
+      <x:c r="F28" s="16" t="str">
         <x:v>미활용 열에너지 회수를 통한 전력생산 및 계통연게 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G28" s="15" t="str">
+      <x:c r="G28" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=42&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H28" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I28" s="16" t="n">
+      <x:c r="H28" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="n">
         <x:f>IF(E28&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J28" s="16" t="n">
+      <x:c r="J28" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B28,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K28" s="16" t="n">
+      <x:c r="K28" s="11" t="n">
         <x:f>I28*J28</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L28" s="16" t="n">
+      <x:c r="L28" s="11" t="n">
         <x:f>YEAR(E28)</x:f>
         <x:v>2016</x:v>
       </x:c>
-      <x:c r="M28" s="16" t="n">
+      <x:c r="M28" s="11" t="n">
         <x:f>IF(AND(K28=1,'분석조건'!$B$5-E28&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N28" s="16" t="n">
+      <x:c r="N28" s="11" t="n">
         <x:f>IF(AND(K28=1,E28&gt;=DATE('분석조건'!$B$6,1,1),E28&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O28" s="16" t="n">
+      <x:c r="O28" s="11" t="n">
         <x:f>IF(AND(K28=1,E28&gt;=DATE('분석조건'!$B$6-1,1,1),E28&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8330,40 +8556,40 @@
       <x:c r="E29" s="9" t="n">
         <x:v>43081</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="str">
+      <x:c r="F29" s="16" t="str">
         <x:v>주거용 시설의 심야 전기보일러에서 축열식 히트펌프 보일러로 교체 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G29" s="15" t="str">
+      <x:c r="G29" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=50&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H29" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I29" s="16" t="n">
+      <x:c r="H29" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="n">
         <x:f>IF(E29&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J29" s="16" t="n">
+      <x:c r="J29" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B29,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K29" s="16" t="n">
+      <x:c r="K29" s="11" t="n">
         <x:f>I29*J29</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L29" s="16" t="n">
+      <x:c r="L29" s="11" t="n">
         <x:f>YEAR(E29)</x:f>
         <x:v>2017</x:v>
       </x:c>
-      <x:c r="M29" s="16" t="n">
+      <x:c r="M29" s="11" t="n">
         <x:f>IF(AND(K29=1,'분석조건'!$B$5-E29&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N29" s="16" t="n">
+      <x:c r="N29" s="11" t="n">
         <x:f>IF(AND(K29=1,E29&gt;=DATE('분석조건'!$B$6,1,1),E29&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O29" s="16" t="n">
+      <x:c r="O29" s="11" t="n">
         <x:f>IF(AND(K29=1,E29&gt;=DATE('분석조건'!$B$6-1,1,1),E29&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8384,40 +8610,40 @@
       <x:c r="E30" s="9" t="n">
         <x:v>43886</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="str">
+      <x:c r="F30" s="16" t="str">
         <x:v>LPG집단공급시설 설치를 통한 연료 전환 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G30" s="15" t="str">
+      <x:c r="G30" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=337&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H30" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I30" s="16" t="n">
+      <x:c r="H30" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="n">
         <x:f>IF(E30&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J30" s="16" t="n">
+      <x:c r="J30" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B30,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K30" s="16" t="n">
+      <x:c r="K30" s="11" t="n">
         <x:f>I30*J30</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L30" s="16" t="n">
+      <x:c r="L30" s="11" t="n">
         <x:f>YEAR(E30)</x:f>
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="M30" s="16" t="n">
+      <x:c r="M30" s="11" t="n">
         <x:f>IF(AND(K30=1,'분석조건'!$B$5-E30&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N30" s="16" t="n">
+      <x:c r="N30" s="11" t="n">
         <x:f>IF(AND(K30=1,E30&gt;=DATE('분석조건'!$B$6,1,1),E30&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O30" s="16" t="n">
+      <x:c r="O30" s="11" t="n">
         <x:f>IF(AND(K30=1,E30&gt;=DATE('분석조건'!$B$6-1,1,1),E30&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8438,40 +8664,40 @@
       <x:c r="E31" s="9" t="n">
         <x:v>44120</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="str">
+      <x:c r="F31" s="16" t="str">
         <x:v>Single RAN 설비를 도입하여 legacy 전기통신설비를 대체하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G31" s="15" t="str">
+      <x:c r="G31" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=333&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H31" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I31" s="16" t="n">
+      <x:c r="H31" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="n">
         <x:f>IF(E31&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J31" s="16" t="n">
+      <x:c r="J31" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B31,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K31" s="16" t="n">
+      <x:c r="K31" s="11" t="n">
         <x:f>I31*J31</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L31" s="16" t="n">
+      <x:c r="L31" s="11" t="n">
         <x:f>YEAR(E31)</x:f>
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="M31" s="16" t="n">
+      <x:c r="M31" s="11" t="n">
         <x:f>IF(AND(K31=1,'분석조건'!$B$5-E31&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N31" s="16" t="n">
+      <x:c r="N31" s="11" t="n">
         <x:f>IF(AND(K31=1,E31&gt;=DATE('분석조건'!$B$6,1,1),E31&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O31" s="16" t="n">
+      <x:c r="O31" s="11" t="n">
         <x:f>IF(AND(K31=1,E31&gt;=DATE('분석조건'!$B$6-1,1,1),E31&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8492,40 +8718,40 @@
       <x:c r="E32" s="9" t="n">
         <x:v>45359</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="str">
+      <x:c r="F32" s="16" t="str">
         <x:v>미활용 LNG 기화 냉열 활용을 통한 전력 및 또는 화석연료 사용 절감 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G32" s="15" t="str">
+      <x:c r="G32" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=440&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H32" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I32" s="16" t="n">
+      <x:c r="H32" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" s="11" t="n">
         <x:f>IF(E32&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J32" s="16" t="n">
+      <x:c r="J32" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B32,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K32" s="16" t="n">
+      <x:c r="K32" s="11" t="n">
         <x:f>I32*J32</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L32" s="16" t="n">
+      <x:c r="L32" s="11" t="n">
         <x:f>YEAR(E32)</x:f>
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="M32" s="16" t="n">
+      <x:c r="M32" s="11" t="n">
         <x:f>IF(AND(K32=1,'분석조건'!$B$5-E32&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N32" s="16" t="n">
+      <x:c r="N32" s="11" t="n">
         <x:f>IF(AND(K32=1,E32&gt;=DATE('분석조건'!$B$6,1,1),E32&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O32" s="16" t="n">
+      <x:c r="O32" s="11" t="n">
         <x:f>IF(AND(K32=1,E32&gt;=DATE('분석조건'!$B$6-1,1,1),E32&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8546,40 +8772,40 @@
       <x:c r="E33" s="9" t="n">
         <x:v>45447</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="str">
+      <x:c r="F33" s="16" t="str">
         <x:v>미활용 열에너지 회수 및 이용 또는  계통연계 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G33" s="15" t="str">
+      <x:c r="G33" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=531&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H33" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I33" s="16" t="n">
+      <x:c r="H33" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" s="11" t="n">
         <x:f>IF(E33&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J33" s="16" t="n">
+      <x:c r="J33" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B33,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K33" s="16" t="n">
+      <x:c r="K33" s="11" t="n">
         <x:f>I33*J33</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L33" s="16" t="n">
+      <x:c r="L33" s="11" t="n">
         <x:f>YEAR(E33)</x:f>
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="M33" s="16" t="n">
+      <x:c r="M33" s="11" t="n">
         <x:f>IF(AND(K33=1,'분석조건'!$B$5-E33&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N33" s="16" t="n">
+      <x:c r="N33" s="11" t="n">
         <x:f>IF(AND(K33=1,E33&gt;=DATE('분석조건'!$B$6,1,1),E33&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O33" s="16" t="n">
+      <x:c r="O33" s="11" t="n">
         <x:f>IF(AND(K33=1,E33&gt;=DATE('분석조건'!$B$6-1,1,1),E33&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8600,40 +8826,40 @@
       <x:c r="E34" s="9" t="n">
         <x:v>45993</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="str">
+      <x:c r="F34" s="16" t="str">
         <x:v>미활용 열에너지 회수 및 이용 또는 계통연계 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G34" s="15" t="str">
+      <x:c r="G34" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=531&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H34" s="16" t="n">
+      <x:c r="H34" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I34" s="16" t="n">
+      <x:c r="I34" s="11" t="n">
         <x:f>IF(E34&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J34" s="16" t="n">
+      <x:c r="J34" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B34,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K34" s="16" t="n">
+      <x:c r="K34" s="11" t="n">
         <x:f>I34*J34</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L34" s="16" t="n">
+      <x:c r="L34" s="11" t="n">
         <x:f>YEAR(E34)</x:f>
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="M34" s="16" t="n">
+      <x:c r="M34" s="11" t="n">
         <x:f>IF(AND(K34=1,'분석조건'!$B$5-E34&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N34" s="16" t="n">
+      <x:c r="N34" s="11" t="n">
         <x:f>IF(AND(K34=1,E34&gt;=DATE('분석조건'!$B$6,1,1),E34&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O34" s="16" t="n">
+      <x:c r="O34" s="11" t="n">
         <x:f>IF(AND(K34=1,E34&gt;=DATE('분석조건'!$B$6-1,1,1),E34&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8654,40 +8880,40 @@
       <x:c r="E35" s="9" t="n">
         <x:v>45721</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="str">
+      <x:c r="F35" s="16" t="str">
         <x:v>공동 통신망 기술 적용에 따른 온실가스 감축사업의 방법론</x:v>
       </x:c>
-      <x:c r="G35" s="15" t="str">
+      <x:c r="G35" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=436&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H35" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I35" s="16" t="n">
+      <x:c r="H35" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I35" s="11" t="n">
         <x:f>IF(E35&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J35" s="16" t="n">
+      <x:c r="J35" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B35,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K35" s="16" t="n">
+      <x:c r="K35" s="11" t="n">
         <x:f>I35*J35</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L35" s="16" t="n">
+      <x:c r="L35" s="11" t="n">
         <x:f>YEAR(E35)</x:f>
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="M35" s="16" t="n">
+      <x:c r="M35" s="11" t="n">
         <x:f>IF(AND(K35=1,'분석조건'!$B$5-E35&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N35" s="16" t="n">
+      <x:c r="N35" s="11" t="n">
         <x:f>IF(AND(K35=1,E35&gt;=DATE('분석조건'!$B$6,1,1),E35&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O35" s="16" t="n">
+      <x:c r="O35" s="11" t="n">
         <x:f>IF(AND(K35=1,E35&gt;=DATE('분석조건'!$B$6-1,1,1),E35&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -8708,40 +8934,40 @@
       <x:c r="E36" s="9" t="n">
         <x:v>44908</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="str">
+      <x:c r="F36" s="16" t="str">
         <x:v>혼합시멘트 생산에서 원료의 부분적인 전환 및 혼합재 비율 증가를 통한 온실가스 감축</x:v>
       </x:c>
-      <x:c r="G36" s="15" t="str">
+      <x:c r="G36" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=330&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H36" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I36" s="16" t="n">
+      <x:c r="H36" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I36" s="11" t="n">
         <x:f>IF(E36&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J36" s="16" t="n">
+      <x:c r="J36" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B36,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K36" s="16" t="n">
+      <x:c r="K36" s="11" t="n">
         <x:f>I36*J36</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L36" s="16" t="n">
+      <x:c r="L36" s="11" t="n">
         <x:f>YEAR(E36)</x:f>
         <x:v>2022</x:v>
       </x:c>
-      <x:c r="M36" s="16" t="n">
+      <x:c r="M36" s="11" t="n">
         <x:f>IF(AND(K36=1,'분석조건'!$B$5-E36&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N36" s="16" t="n">
+      <x:c r="N36" s="11" t="n">
         <x:f>IF(AND(K36=1,E36&gt;=DATE('분석조건'!$B$6,1,1),E36&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O36" s="16" t="n">
+      <x:c r="O36" s="11" t="n">
         <x:f>IF(AND(K36=1,E36&gt;=DATE('분석조건'!$B$6-1,1,1),E36&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8762,40 +8988,40 @@
       <x:c r="E37" s="9" t="n">
         <x:v>44908</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="str">
+      <x:c r="F37" s="16" t="str">
         <x:v>제지공정에서 침강성탄산칼슘 제조과정의 미활용 CO2 이용과 에너지절감 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G37" s="15" t="str">
+      <x:c r="G37" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=369&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H37" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I37" s="16" t="n">
+      <x:c r="H37" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I37" s="11" t="n">
         <x:f>IF(E37&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J37" s="16" t="n">
+      <x:c r="J37" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B37,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K37" s="16" t="n">
+      <x:c r="K37" s="11" t="n">
         <x:f>I37*J37</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L37" s="16" t="n">
+      <x:c r="L37" s="11" t="n">
         <x:f>YEAR(E37)</x:f>
         <x:v>2022</x:v>
       </x:c>
-      <x:c r="M37" s="16" t="n">
+      <x:c r="M37" s="11" t="n">
         <x:f>IF(AND(K37=1,'분석조건'!$B$5-E37&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N37" s="16" t="n">
+      <x:c r="N37" s="11" t="n">
         <x:f>IF(AND(K37=1,E37&gt;=DATE('분석조건'!$B$6,1,1),E37&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O37" s="16" t="n">
+      <x:c r="O37" s="11" t="n">
         <x:f>IF(AND(K37=1,E37&gt;=DATE('분석조건'!$B$6-1,1,1),E37&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8816,40 +9042,40 @@
       <x:c r="E38" s="9" t="n">
         <x:v>44120</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="str">
+      <x:c r="F38" s="16" t="str">
         <x:v>부생수소 활용을 통한 수소제조공정 대체사업의 방법론</x:v>
       </x:c>
-      <x:c r="G38" s="15" t="str">
+      <x:c r="G38" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=325&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H38" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I38" s="16" t="n">
+      <x:c r="H38" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I38" s="11" t="n">
         <x:f>IF(E38&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J38" s="16" t="n">
+      <x:c r="J38" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B38,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K38" s="16" t="n">
+      <x:c r="K38" s="11" t="n">
         <x:f>I38*J38</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L38" s="16" t="n">
+      <x:c r="L38" s="11" t="n">
         <x:f>YEAR(E38)</x:f>
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="M38" s="16" t="n">
+      <x:c r="M38" s="11" t="n">
         <x:f>IF(AND(K38=1,'분석조건'!$B$5-E38&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N38" s="16" t="n">
+      <x:c r="N38" s="11" t="n">
         <x:f>IF(AND(K38=1,E38&gt;=DATE('분석조건'!$B$6,1,1),E38&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O38" s="16" t="n">
+      <x:c r="O38" s="11" t="n">
         <x:f>IF(AND(K38=1,E38&gt;=DATE('분석조건'!$B$6-1,1,1),E38&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8870,40 +9096,40 @@
       <x:c r="E39" s="9" t="n">
         <x:v>44558</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="str">
+      <x:c r="F39" s="16" t="str">
         <x:v>국내 중온 아스팔트 혼합물 생산을 통한 연료 및 온실가스 저감에 대한 방법론</x:v>
       </x:c>
-      <x:c r="G39" s="15" t="str">
+      <x:c r="G39" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=324&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H39" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I39" s="16" t="n">
+      <x:c r="H39" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="n">
         <x:f>IF(E39&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J39" s="16" t="n">
+      <x:c r="J39" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B39,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K39" s="16" t="n">
+      <x:c r="K39" s="11" t="n">
         <x:f>I39*J39</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L39" s="16" t="n">
+      <x:c r="L39" s="11" t="n">
         <x:f>YEAR(E39)</x:f>
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="M39" s="16" t="n">
+      <x:c r="M39" s="11" t="n">
         <x:f>IF(AND(K39=1,'분석조건'!$B$5-E39&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N39" s="16" t="n">
+      <x:c r="N39" s="11" t="n">
         <x:f>IF(AND(K39=1,E39&gt;=DATE('분석조건'!$B$6,1,1),E39&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O39" s="16" t="n">
+      <x:c r="O39" s="11" t="n">
         <x:f>IF(AND(K39=1,E39&gt;=DATE('분석조건'!$B$6-1,1,1),E39&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8924,40 +9150,40 @@
       <x:c r="E40" s="9" t="n">
         <x:v>43081</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="str">
+      <x:c r="F40" s="16" t="str">
         <x:v>가스절연개폐장치 검사용 SF6 회수ㆍ정제 및 재사용을 통한 SF6 감축사업의 방법론</x:v>
       </x:c>
-      <x:c r="G40" s="15" t="str">
+      <x:c r="G40" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=49&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H40" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I40" s="16" t="n">
+      <x:c r="H40" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="n">
         <x:f>IF(E40&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J40" s="16" t="n">
+      <x:c r="J40" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B40,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K40" s="16" t="n">
+      <x:c r="K40" s="11" t="n">
         <x:f>I40*J40</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L40" s="16" t="n">
+      <x:c r="L40" s="11" t="n">
         <x:f>YEAR(E40)</x:f>
         <x:v>2017</x:v>
       </x:c>
-      <x:c r="M40" s="16" t="n">
+      <x:c r="M40" s="11" t="n">
         <x:f>IF(AND(K40=1,'분석조건'!$B$5-E40&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N40" s="16" t="n">
+      <x:c r="N40" s="11" t="n">
         <x:f>IF(AND(K40=1,E40&gt;=DATE('분석조건'!$B$6,1,1),E40&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O40" s="16" t="n">
+      <x:c r="O40" s="11" t="n">
         <x:f>IF(AND(K40=1,E40&gt;=DATE('분석조건'!$B$6-1,1,1),E40&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8978,40 +9204,40 @@
       <x:c r="E41" s="9" t="n">
         <x:v>44120</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="str">
+      <x:c r="F41" s="16" t="str">
         <x:v>광전지 제조 공정의 SF6 가스 처리를 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G41" s="15" t="str">
+      <x:c r="G41" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=315&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H41" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I41" s="16" t="n">
+      <x:c r="H41" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="n">
         <x:f>IF(E41&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J41" s="16" t="n">
+      <x:c r="J41" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B41,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K41" s="16" t="n">
+      <x:c r="K41" s="11" t="n">
         <x:f>I41*J41</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L41" s="16" t="n">
+      <x:c r="L41" s="11" t="n">
         <x:f>YEAR(E41)</x:f>
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="M41" s="16" t="n">
+      <x:c r="M41" s="11" t="n">
         <x:f>IF(AND(K41=1,'분석조건'!$B$5-E41&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N41" s="16" t="n">
+      <x:c r="N41" s="11" t="n">
         <x:f>IF(AND(K41=1,E41&gt;=DATE('분석조건'!$B$6,1,1),E41&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O41" s="16" t="n">
+      <x:c r="O41" s="11" t="n">
         <x:f>IF(AND(K41=1,E41&gt;=DATE('분석조건'!$B$6-1,1,1),E41&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -9032,40 +9258,40 @@
       <x:c r="E42" s="9" t="n">
         <x:v>44252</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="str">
+      <x:c r="F42" s="16" t="str">
         <x:v>발포제로 사용되는 HFC-152a 회수·정제 및 재사용을 통한 HFC-152a 감축사업의 방법론</x:v>
       </x:c>
-      <x:c r="G42" s="15" t="str">
+      <x:c r="G42" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=299&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H42" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I42" s="16" t="n">
+      <x:c r="H42" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="n">
         <x:f>IF(E42&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J42" s="16" t="n">
+      <x:c r="J42" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B42,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K42" s="16" t="n">
+      <x:c r="K42" s="11" t="n">
         <x:f>I42*J42</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L42" s="16" t="n">
+      <x:c r="L42" s="11" t="n">
         <x:f>YEAR(E42)</x:f>
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="M42" s="16" t="n">
+      <x:c r="M42" s="11" t="n">
         <x:f>IF(AND(K42=1,'분석조건'!$B$5-E42&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42" s="16" t="n">
+      <x:c r="N42" s="11" t="n">
         <x:f>IF(AND(K42=1,E42&gt;=DATE('분석조건'!$B$6,1,1),E42&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O42" s="16" t="n">
+      <x:c r="O42" s="11" t="n">
         <x:f>IF(AND(K42=1,E42&gt;=DATE('분석조건'!$B$6-1,1,1),E42&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -9086,40 +9312,40 @@
       <x:c r="E43" s="9" t="n">
         <x:v>44558</x:v>
       </x:c>
-      <x:c r="F43" s="15" t="str">
+      <x:c r="F43" s="16" t="str">
         <x:v>가스절연 전기기기의 시험에 따라 발생되는 육불화황(SF6) 가스의 회수 및 플라즈마 분해를 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G43" s="15" t="str">
+      <x:c r="G43" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=515&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H43" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I43" s="16" t="n">
+      <x:c r="H43" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="n">
         <x:f>IF(E43&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J43" s="16" t="n">
+      <x:c r="J43" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B43,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K43" s="16" t="n">
+      <x:c r="K43" s="11" t="n">
         <x:f>I43*J43</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L43" s="16" t="n">
+      <x:c r="L43" s="11" t="n">
         <x:f>YEAR(E43)</x:f>
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="M43" s="16" t="n">
+      <x:c r="M43" s="11" t="n">
         <x:f>IF(AND(K43=1,'분석조건'!$B$5-E43&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N43" s="16" t="n">
+      <x:c r="N43" s="11" t="n">
         <x:f>IF(AND(K43=1,E43&gt;=DATE('분석조건'!$B$6,1,1),E43&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O43" s="16" t="n">
+      <x:c r="O43" s="11" t="n">
         <x:f>IF(AND(K43=1,E43&gt;=DATE('분석조건'!$B$6-1,1,1),E43&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -9140,40 +9366,40 @@
       <x:c r="E44" s="9" t="n">
         <x:v>46175</x:v>
       </x:c>
-      <x:c r="F44" s="15" t="str">
+      <x:c r="F44" s="16" t="str">
         <x:v>가스절연 전기기기의 시험에 따라 발생되는 육불화황(SF6) 가스의 회수 및 플라즈마 분해를 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G44" s="15" t="str">
+      <x:c r="G44" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=515&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H44" s="16" t="n">
+      <x:c r="H44" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I44" s="16" t="n">
+      <x:c r="I44" s="11" t="n">
         <x:f>IF(E44&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J44" s="16" t="n">
+      <x:c r="J44" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B44,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K44" s="16" t="n">
+      <x:c r="K44" s="11" t="n">
         <x:f>I44*J44</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L44" s="16" t="n">
+      <x:c r="L44" s="11" t="n">
         <x:f>YEAR(E44)</x:f>
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="M44" s="16" t="n">
+      <x:c r="M44" s="11" t="n">
         <x:f>IF(AND(K44=1,'분석조건'!$B$5-E44&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N44" s="16" t="n">
+      <x:c r="N44" s="11" t="n">
         <x:f>IF(AND(K44=1,E44&gt;=DATE('분석조건'!$B$6,1,1),E44&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O44" s="16" t="n">
+      <x:c r="O44" s="11" t="n">
         <x:f>IF(AND(K44=1,E44&gt;=DATE('분석조건'!$B$6-1,1,1),E44&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -9194,40 +9420,40 @@
       <x:c r="E45" s="9" t="n">
         <x:v>44992</x:v>
       </x:c>
-      <x:c r="F45" s="15" t="str">
+      <x:c r="F45" s="16" t="str">
         <x:v>전력계통내 폐기된 전기설비의 충진된 SF6를 회수 및 정제하는 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G45" s="15" t="str">
+      <x:c r="G45" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=383&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H45" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I45" s="16" t="n">
+      <x:c r="H45" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="n">
         <x:f>IF(E45&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J45" s="16" t="n">
+      <x:c r="J45" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B45,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K45" s="16" t="n">
+      <x:c r="K45" s="11" t="n">
         <x:f>I45*J45</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L45" s="16" t="n">
+      <x:c r="L45" s="11" t="n">
         <x:f>YEAR(E45)</x:f>
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="M45" s="16" t="n">
+      <x:c r="M45" s="11" t="n">
         <x:f>IF(AND(K45=1,'분석조건'!$B$5-E45&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N45" s="16" t="n">
+      <x:c r="N45" s="11" t="n">
         <x:f>IF(AND(K45=1,E45&gt;=DATE('분석조건'!$B$6,1,1),E45&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O45" s="16" t="n">
+      <x:c r="O45" s="11" t="n">
         <x:f>IF(AND(K45=1,E45&gt;=DATE('분석조건'!$B$6-1,1,1),E45&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -9248,40 +9474,40 @@
       <x:c r="E46" s="9" t="n">
         <x:v>44992</x:v>
       </x:c>
-      <x:c r="F46" s="15" t="str">
+      <x:c r="F46" s="16" t="str">
         <x:v>반도체 제조공정의 F-Gas 감축설비 도입을 통한 온실가스 감축 사업의 방법론</x:v>
       </x:c>
-      <x:c r="G46" s="15" t="str">
+      <x:c r="G46" s="16" t="str">
         <x:v>https://ors.gir.go.kr/home/orme010/historyRead.do?methdSeq=404&amp;menuId=12</x:v>
       </x:c>
-      <x:c r="H46" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I46" s="16" t="n">
+      <x:c r="H46" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="n">
         <x:f>IF(E46&lt;='분석조건'!$B$5,1,0)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J46" s="16" t="n">
+      <x:c r="J46" s="11" t="n">
         <x:f>INDEX('방법론'!$L$7:$L$39,MATCH(B46,'방법론'!$A$7:$A$39,0))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K46" s="16" t="n">
+      <x:c r="K46" s="11" t="n">
         <x:f>I46*J46</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L46" s="16" t="n">
+      <x:c r="L46" s="11" t="n">
         <x:f>YEAR(E46)</x:f>
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="M46" s="16" t="n">
+      <x:c r="M46" s="11" t="n">
         <x:f>IF(AND(K46=1,'분석조건'!$B$5-E46&lt;'분석조건'!$B$11),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N46" s="16" t="n">
+      <x:c r="N46" s="11" t="n">
         <x:f>IF(AND(K46=1,E46&gt;=DATE('분석조건'!$B$6,1,1),E46&lt;='분석조건'!$B$14),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O46" s="16" t="n">
+      <x:c r="O46" s="11" t="n">
         <x:f>IF(AND(K46=1,E46&gt;=DATE('분석조건'!$B$6-1,1,1),E46&lt;='분석조건'!$B$15),1,0)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -9293,7 +9519,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d4eb13ecfd946c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc77aed407184ad9"/>
   </x:tableParts>
 </x:worksheet>
 </file>